--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,12 +517,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2036181530364489860</t>
+          <t>2036300027933433945</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -583,139 +583,140 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2036300027933433945</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2036300027933433945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@AlyahiaMoh مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
+أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1774326733000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2036181530364489860</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2036181530364489860</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46105.35570601852</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2036269961057018273</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2036180751201481057</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://x.com/saimas89/status/2036180751201481057</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>1774298296000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2036180751201481057</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEH3mXTaIAIZ2bz.jpg', 'type': 'photo', 'id': '2036180745010683906'}]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'name': 'Saima | صائمہ', 'screenName': 'saimas89', 'followersCount': 550, 'favouritesCount': 1122, 'friendsCount': 293, 'description': 'Active on 👉 @hey_saima 👩\u200d💻 #Communications and #Marketing Professional | #SocialMediaMarketing | #Foodie 🍔☕'}</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="2" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="n">
         <v>46105.02657407407</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2036269961057018273</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2036184567120597068</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/flyspicejet/status/2036184567120597068</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>@saimas89 Hi Saima, we have initated the full refund of AED 1,211.80 from our end towards the initial mode of payment (JusPay) dated 24th Mar'26 and the refund shall be credited within 07 working days. We sincerely regret the delay in the refund process.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1774299205000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2036180751201481057</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'name': 'SpiceJet', 'screenName': 'flyspicejet', 'followersCount': 310711, 'favouritesCount': 8683, 'friendsCount': 40, 'description': "From runways to memories! Fly SpiceJet – India’s most preferred airline. Let's create together – DM for collabs"}</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2036180751201481057</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46105.03709490741</v>
       </c>
     </row>
     <row r="5">
@@ -731,21 +732,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036184567120597068</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
+          <t>https://x.com/flyspicejet/status/2036184567120597068</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@flyspicejet Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
+          <t>@saimas89 Hi Saima, we have initated the full refund of AED 1,211.80 from our end towards the initial mode of payment (JusPay) dated 24th Mar'26 and the refund shall be credited within 07 working days. We sincerely regret the delay in the refund process.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1774319565000</v>
+        <v>1774299205000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -759,11 +760,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Saima | صائمہ', 'screenName': 'saimas89', 'followersCount': 550, 'favouritesCount': 1122, 'friendsCount': 293, 'description': 'Active on 👉 @hey_saima 👩\u200d💻 #Communications and #Marketing Professional | #SocialMediaMarketing | #Foodie 🍔☕'}</t>
+          <t>{'name': 'SpiceJet', 'screenName': 'flyspicejet', 'followersCount': 310711, 'favouritesCount': 8683, 'friendsCount': 40, 'description': "From runways to memories! Fly SpiceJet – India’s most preferred airline. Let's create together – DM for collabs"}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -776,16 +777,16 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2036184567120597068</t>
+          <t>2036180751201481057</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46105.27274305555</v>
+        <v>46105.03709490741</v>
       </c>
     </row>
     <row r="6">
@@ -801,21 +802,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2036278233273090130</t>
+          <t>2036269961057018273</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/flyspicejet/status/2036278233273090130</t>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@saimas89 We have already initiated the refund towards the same mode of payment (Juspay) dated 24th Mar'26. We'd request you to wait for the stipulated time period.</t>
+          <t>@flyspicejet Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1774321537000</v>
+        <v>1774319565000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -829,11 +830,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'SpiceJet', 'screenName': 'flyspicejet', 'followersCount': 310711, 'favouritesCount': 8683, 'friendsCount': 40, 'description': "From runways to memories! Fly SpiceJet – India’s most preferred airline. Let's create together – DM for collabs"}</t>
+          <t>{'name': 'Saima | صائمہ', 'screenName': 'saimas89', 'followersCount': 550, 'favouritesCount': 1122, 'friendsCount': 293, 'description': 'Active on 👉 @hey_saima 👩\u200d💻 #Communications and #Marketing Professional | #SocialMediaMarketing | #Foodie 🍔☕'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -846,65 +847,64 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036184567120597068</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46105.29556712963</v>
+        <v>46105.27274305555</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2036140802057896269</t>
+          <t>2036269961057018273</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2036130140510449946</t>
+          <t>2036278233273090130</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
+          <t>https://x.com/flyspicejet/status/2036278233273090130</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
+          <t>@saimas89 We have already initiated the refund towards the same mode of payment (Juspay) dated 24th Mar'26. We'd request you to wait for the stipulated time period.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1774286229000</v>
+        <v>1774321537000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2036130140510449946</t>
+          <t>2036180751201481057</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEHJkccW4AA79UL.jpg', 'type': 'photo', 'id': '2036130134495780864'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Mohammed Alyahia', 'screenName': 'AlyahiaMoh', 'followersCount': 2, 'favouritesCount': 14, 'friendsCount': 27, 'description': ''}</t>
+          <t>{'name': 'SpiceJet', 'screenName': 'flyspicejet', 'followersCount': 310711, 'favouritesCount': 8683, 'friendsCount': 40, 'description': "From runways to memories! Fly SpiceJet – India’s most preferred airline. Let's create together – DM for collabs"}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -917,177 +917,40 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2036269961057018273</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n">
-        <v>46104.88690972222</v>
+        <v>46105.29556712963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
+          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2036140802057896269</t>
+          <t>2036171018964713797</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2036140802057896269</t>
+          <t>2035516933039079770</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
+          <t>https://x.com/RotanaLive/status/2035516933039079770</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>@AlyahiaMoh مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1774288771000</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2036130140510449946</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173955, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2036130140510449946</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>46104.91633101852</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2036140802057896269</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2036176545543266757</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
-فيه احد يتواصل معي؟</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1774297293000</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2036130140510449946</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'name': 'Mohammed Alyahia', 'screenName': 'AlyahiaMoh', 'followersCount': 2, 'favouritesCount': 14, 'friendsCount': 27, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2036140802057896269</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>46105.01496527778</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2036171018964713797</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2035516933039079770</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/RotanaLive/status/2035516933039079770</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>الصقر بعد ختام حفلة الليلة🦅
 انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
@@ -1103,90 +966,231 @@
 @EmiratesNBD_KSA https://t.co/X1Ds9wmkXZ</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F8" t="n">
         <v>1774140029000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2035516933039079770</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035516741824954368/img/ZDss9Sr7RSWoML93.jpg', 'type': 'video', 'id': '2035516741824954368'}]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193284, 'favouritesCount': 7048, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193282, 'favouritesCount': 7048, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L8" t="n">
         <v>24</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M8" t="n">
         <v>148</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>33284</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>33490</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="n">
         <v>46103.19478009259</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>https://x.com/Pjnw0/status/2036171018964713797</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2036171018964713797</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2036079925136949553</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/Sadziz13/status/2036079925136949553</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>@RotanaLive @Turki_alalshikh @RabehSaqer @salhendi @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA حبيبنا بو شليل والله 
 كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
 خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>1774274257000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2035516933039079770</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'name': 'مَ. سعـد عبدالعزيز', 'screenName': 'Sadziz13', 'followersCount': 1566, 'favouritesCount': 13203, 'friendsCount': 328, 'description': '@Rabehsaqer @alhilal_fc 🎶💙🎶'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2035516933039079770</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>46104.74834490741</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2036171018964713797</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2036171018964713797</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>@Sadziz13 @RotanaLive @Turki_alalshikh @RabehSaqer @salhendi @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA ما الومه يسال بيكمل سنه من الاعلان</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1774295975000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2035516933039079770</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'name': 'ًً', 'screenName': 'Pjnw0', 'followersCount': 134, 'favouritesCount': 17775, 'friendsCount': 715, 'description': 'أول خطوة للتصالح مع الذات هو ان يبقى الشخص ممتنًّا للأخطاء التي أوصلته لمرحلة الوعي'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2036079925136949553</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46104.99971064815</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2036176545543266757</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2036130140510449946</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
+        </is>
+      </c>
       <c r="F11" t="n">
-        <v>1774274257000</v>
+        <v>1774286229000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2035516933039079770</t>
+          <t>2036130140510449946</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEHJkccW4AA79UL.jpg', 'type': 'photo', 'id': '2036130134495780864'}]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'مَ. سعـد عبدالعزيز', 'screenName': 'Sadziz13', 'followersCount': 1566, 'favouritesCount': 13203, 'friendsCount': 328, 'description': '@Rabehsaqer @alhilal_fc 🎶💙🎶'}</t>
+          <t>{'name': 'Mohammed Alyahia', 'screenName': 'AlyahiaMoh', 'followersCount': 2, 'favouritesCount': 14, 'friendsCount': 27, 'description': ''}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1199,54 +1203,50 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2035516933039079770</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>46104.74834490741</v>
+        <v>46104.88690972222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2036171018964713797</t>
+          <t>2036176545543266757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2036171018964713797</t>
+          <t>2036140802057896269</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@Sadziz13 @RotanaLive @Turki_alalshikh @RabehSaqer @salhendi @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA ما الومه يسال بيكمل سنه من الاعلان</t>
+          <t>@AlyahiaMoh مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1774295975000</v>
+        <v>1774288771000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2035516933039079770</t>
+          <t>2036130140510449946</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1256,11 +1256,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'ًً', 'screenName': 'Pjnw0', 'followersCount': 134, 'favouritesCount': 17774, 'friendsCount': 715, 'description': 'أول خطوة للتصالح مع الذات هو ان يبقى الشخص ممتنًّا للأخطاء التي أوصلته لمرحلة الوعي'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1273,40 +1273,111 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2036079925136949553</t>
+          <t>2036130140510449946</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46104.99971064815</v>
+        <v>46104.91633101852</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2036176545543266757</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2036176545543266757</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
+فيه احد يتواصل معي؟</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1774297293000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2036130140510449946</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohammed Alyahia', 'screenName': 'AlyahiaMoh', 'followersCount': 2, 'favouritesCount': 14, 'friendsCount': 27, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2036140802057896269</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>46105.01496527778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2036136587390533632</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2036136587390533632</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1315,177 +1386,111 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻 https://t.co/SxESBo3MLg</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>1774287766000</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2036136587390533632</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEHPPPOXkAANcUG.jpg', 'type': 'photo', 'id': '2036136367239958528'}]</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>{'name': 'CASTest2050001283', 'screenName': 'cas_2050001283', 'followersCount': 475, 'favouritesCount': 0, 'friendsCount': 1, 'description': ''}</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" s="2" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="n">
         <v>46104.90469907408</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2036136587390533632</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2036265077356072960</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/cas_2050001283/status/2036265077356072960</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>C&amp;lt;t7👩🏿‍🔧Ff
 s Zx I2oahuoB</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>1774318401000</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2036265077356072960</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{'name': 'CASTest2050001283', 'screenName': 'cas_2050001283', 'followersCount': 475, 'favouritesCount': 0, 'friendsCount': 1, 'description': ''}</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" s="2" t="n">
-        <v>46105.25927083333</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036086151656636693</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2036086151656636693</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2036081518607749454</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/mridulrb/status/2036081518607749454</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1774274637000</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2036081518607749454</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{'name': 'Mridul Bhandari', 'screenName': 'mridulrb', 'followersCount': 437, 'favouritesCount': 3777, 'friendsCount': 3222, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>46104.75274305556</v>
+        <v>46105.25927083333</v>
       </c>
     </row>
     <row r="16">
@@ -1501,15 +1506,81 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2036081518607749454</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/mridulrb/status/2036081518607749454</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1774274637000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2036081518607749454</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'name': 'Mridul Bhandari', 'screenName': 'mridulrb', 'followersCount': 437, 'favouritesCount': 3777, 'friendsCount': 3222, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="n">
+        <v>46104.75274305556</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036086151656636693</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>2036086151656636693</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2036086151656636693</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036086151656636693</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>@mridulrb We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to
 social@emiratesnbd.com
@@ -1517,141 +1588,141 @@
  We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>1774275741000</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2036081518607749454</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173961, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>2036081518607749454</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>46104.76552083333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2036080525308252666</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2036080525308252666</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Double click and instantly.
-Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/VIYiv3iBPu</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1774274400000</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2036080525308252666</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEF2NOXWcAAgLT0.jpg', 'type': 'photo', 'id': '2036038476114587648'}]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2955, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" s="2" t="n">
-        <v>46104.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2036080525308252666</t>
+          <t>2036080525299925460</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2036080525299925460</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>اضغط مرتين وادفع فورًا.
+استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204 https://t.co/gwVMTmxlJs</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1774274400000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2036080525299925460</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEF-bu3WYAAJd5w.jpg', 'type': 'photo', 'id': '2036047521449926656'}]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2955, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>46104.75</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2036080525299925460</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>2035431246810042738</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2035431246810042738</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>تسوق  هدايا عيد الأم .. وادفع بطريقتك.
 اكتشف أشهر البراندات في مكان واحد في Jlood ب 0% مقدم، 0% فوائد  و0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني عند الدفع باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
@@ -1660,156 +1731,91 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1774119600000</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2035431246810042738</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HD43z0vWkAAKp9I.jpg', 'type': 'photo', 'id': '2035125445088153600'}]</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2955, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" s="2" t="n">
-        <v>46102.95833333334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2036058390850654260</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2035966414339944745</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/NalinisKitchen/status/2035966414339944745</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
-Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
-For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1774247194000</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2035966414339944745</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEE0YYNagAEn7Jt.jpg', 'type': 'photo', 'id': '2035966099968393217'}]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'name': 'Nalini Unagar', 'screenName': 'NalinisKitchen', 'followersCount': 181719, 'favouritesCount': 4758, 'friendsCount': 88508, 'description': 'Passionate about equality, women’s rights, climate action &amp; animal welfare. Here for bold ideas, real talk &amp; change that matters.'}</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>53</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>78</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>25664</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>46104.43511574074</v>
+        <v>46102.95833333334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2036058390850654260</t>
+          <t>2036080525308252666</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2036058390850654260</t>
+          <t>2036080525308252666</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@NalinisKitchen Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp;amp; Conditions Apply.
+Tax registration number: 204-897-319 https://t.co/VIYiv3iBPu</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1774269123000</v>
+        <v>1774274400000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2035966414339944745</t>
+          <t>2036080525308252666</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEF2NOXWcAAgLT0.jpg', 'type': 'photo', 'id': '2036038476114587648'}]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Sovereign Alpha', 'screenName': 'soviergn', 'followersCount': 3, 'favouritesCount': 5, 'friendsCount': 6, 'description': 'Debunking Myths'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2954, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1826,63 +1832,57 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2035966414339944745</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46104.68892361111</v>
+        <v>46104.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2036080525299925460</t>
+          <t>2036055087643042221</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2036080525299925460</t>
+          <t>2036055087643042221</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204 https://t.co/gwVMTmxlJs</t>
+          <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
+https://t.co/5AGiLcfQH8 https://t.co/mcRsbVQhL1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1774274400000</v>
+        <v>1774268335000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2036080525299925460</t>
+          <t>2036055087643042221</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEF-bu3WYAAJd5w.jpg', 'type': 'photo', 'id': '2036047521449926656'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2036055034719293440/img/OziDe-MRVaGwCZPq.jpg', 'type': 'video', 'id': '2036055034719293440'}]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2955, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1895,16 +1895,16 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>664</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46104.75</v>
+        <v>46104.67980324074</v>
       </c>
     </row>
     <row r="22">
@@ -1920,82 +1920,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2036055087643042221</t>
+          <t>2035627541105348902</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2035627541105348902</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
-https://t.co/5AGiLcfQH8 https://t.co/mcRsbVQhL1</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1774268335000</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2036055087643042221</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2036055034719293440/img/OziDe-MRVaGwCZPq.jpg', 'type': 'video', 'id': '2036055034719293440'}]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
-        <v>46104.67980324074</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2036055087643042221</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2035627541105348902</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035627541105348902</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>Don’t click unfamiliar links.
 Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
@@ -2003,68 +1936,206 @@
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>1774166400000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2035627541105348902</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>46103.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2036058390850654260</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2035966414339944745</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/NalinisKitchen/status/2035966414339944745</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+        </is>
+      </c>
       <c r="F23" t="n">
-        <v>1774166400000</v>
+        <v>1774247194000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2035627541105348902</t>
+          <t>2035966414339944745</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEE0YYNagAEn7Jt.jpg', 'type': 'photo', 'id': '2035966099968393217'}]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Nalini Unagar', 'screenName': 'NalinisKitchen', 'followersCount': 181770, 'favouritesCount': 4761, 'friendsCount': 88507, 'description': 'Passionate about equality, women’s rights, climate action &amp; animal welfare. Here for bold ideas, real talk &amp; change that matters.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46103.5</v>
+        <v>46104.43511574074</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2036058390850654260</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2036058390850654260</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>@NalinisKitchen Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1774269123000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2035966414339944745</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'Sovereign Alpha', 'screenName': 'soviergn', 'followersCount': 3, 'favouritesCount': 5, 'friendsCount': 6, 'description': 'Debunking Myths'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2035966414339944745</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>46104.68892361111</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>https://x.com/li_yxe/status/2036035724667974026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2036035724667974026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2035481992142139753</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://x.com/RotanaLive/status/2035481992142139753</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>نسفة الإقلاع🦅
 وأقلعنا مع الصقر❤️‍🔥👏🏻
@@ -2079,138 +2150,138 @@
 @EmiratesNBD_KSA https://t.co/UVb6tMol4M</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>1774131699000</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2035481992142139753</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035480489968984064/img/AF2QFyySfnMoZ8E5.jpg', 'type': 'video', 'id': '2035480489968984064'}]</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193284, 'favouritesCount': 7048, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193282, 'favouritesCount': 7048, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>18</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L25" t="n">
+        <v>19</v>
+      </c>
+      <c r="M25" t="n">
         <v>122</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>20357</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
         <v>46103.09836805556</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://x.com/li_yxe/status/2036035724667974026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2036035724667974026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2036035724667974026</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/li_yxe/status/2036035724667974026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA غلطة العمر دخولك على الفن</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1774263719000</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2035481992142139753</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'محب موسس نادي الجاليات احمد البربري💛💙', 'screenName': 'li_yxe', 'followersCount': 115, 'favouritesCount': 3653, 'friendsCount': 173, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2035481992142139753</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>46104.62637731482</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>https://x.com/li_yxe/status/2036035724667974026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2036035724667974026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2036035724667974026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/li_yxe/status/2036035724667974026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA غلطة العمر دخولك على الفن</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1774263719000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2035481992142139753</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'محب موسس نادي الجاليات احمد البربري💛💙', 'screenName': 'li_yxe', 'followersCount': 115, 'favouritesCount': 3653, 'friendsCount': 173, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2035481992142139753</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>46104.62637731482</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2036029459585781847</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2036029459585781847</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -2224,92 +2295,26 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>1774262225000</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2036029459585781847</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>{'name': 'PragmaticWatcher', 'screenName': 'Prahmatic17', 'followersCount': 61, 'favouritesCount': 125, 'friendsCount': 33, 'description': 'I don’t believe anything. Facts. Figures. No agenda. Verified before posted. Corrections published publicly.'}</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" s="2" t="n">
-        <v>46104.60908564815</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2035995575489909048</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2035983374574059838</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1774251237000</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2035983374574059838</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Muhammad Kashif Ashraf', 'screenName': 'netdiscussion', 'followersCount': 27, 'favouritesCount': 14, 'friendsCount': 39, 'description': ''}</t>
-        </is>
-      </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2322,46 +2327,48 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>423</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46104.48190972222</v>
+        <v>46104.60908564815</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2035995575489909048</t>
+          <t>2036034615769518550</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2035984966622879907</t>
+          <t>2035265155689251255</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2035265155689251255</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@netdiscussion Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1774251617000</v>
+        <v>1774080001000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2035983374574059838</t>
+          <t>2035265155689251255</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2371,67 +2378,63 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2035983374574059838</t>
-        </is>
-      </c>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46104.48630787037</v>
+        <v>46102.50001157408</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2035995575489909048</t>
+          <t>2036034615769518550</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2035990013700157483</t>
+          <t>2036027630722617585</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2035990013700157483</t>
+          <t>https://x.com/Nightowl263/status/2036027630722617585</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Same message receiving multiple times with zero response</t>
+          <t>@EmiratesNBD_AE I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1774252820000</v>
+        <v>1774261789000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2035983374574059838</t>
+          <t>2035265155689251255</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2441,7 +2444,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Muhammad Kashif Ashraf', 'screenName': 'netdiscussion', 'followersCount': 27, 'favouritesCount': 14, 'friendsCount': 39, 'description': ''}</t>
+          <t>{'name': 'Priya George', 'screenName': 'Nightowl263', 'followersCount': 107, 'favouritesCount': 910, 'friendsCount': 110, 'description': 'MELIORATE'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2458,50 +2461,50 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2035984966622879907</t>
+          <t>2035265155689251255</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46104.50023148148</v>
+        <v>46104.60403935185</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2035995575489909048</t>
+          <t>2036034615769518550</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2035995575489909048</t>
+          <t>2036034615769518550</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@netdiscussion we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
+          <t>@Nightowl263 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1774254146000</v>
+        <v>1774263454000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2035983374574059838</t>
+          <t>2035265155689251255</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2511,7 +2514,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2528,16 +2531,16 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2035990013700157483</t>
+          <t>2036027630722617585</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46104.5155787037</v>
+        <v>46104.62331018518</v>
       </c>
     </row>
     <row r="31">
@@ -2585,7 +2588,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2602,7 +2605,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -2668,7 +2671,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2683,35 +2686,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2035964468413493475</t>
+          <t>2035984966622879907</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2035964468413493475</t>
+          <t>2035983374574059838</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
+          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1774246730000</v>
+        <v>1774251237000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2035964468413493475</t>
+          <t>2035983374574059838</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2721,11 +2724,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Eugene H Krabs', 'screenName': 'Mr__Krabs___', 'followersCount': 289, 'favouritesCount': 6312, 'friendsCount': 90, 'description': 'Entrepreneur | Diligent Saver | Prominent Businessman | Single Parent | Elementary School Graduate'}</t>
+          <t>{'name': 'Muhammad Kashif Ashraf', 'screenName': 'netdiscussion', 'followersCount': 27, 'favouritesCount': 14, 'friendsCount': 39, 'description': ''}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2738,46 +2741,46 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46104.42974537037</v>
+        <v>46104.48190972222</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2035964468413493475</t>
+          <t>2035984966622879907</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2036243538225274912</t>
+          <t>2035984966622879907</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___/status/2036243538225274912</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ignoring the noise, breadth was weaker today than Friday. Still not seeing institutional buyers step in on an index level. Dealer positioning having a guiding hand lately. Even if things open today; couple months to normalize not great for stagflation narrative/tarriffs. 🫩</t>
+          <t>@netdiscussion Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1774313265000</v>
+        <v>1774251617000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2036243538225274912</t>
+          <t>2035983374574059838</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2787,11 +2790,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Eugene H Krabs', 'screenName': 'Mr__Krabs___', 'followersCount': 289, 'favouritesCount': 6312, 'friendsCount': 90, 'description': 'Entrepreneur | Diligent Saver | Prominent Businessman | Single Parent | Elementary School Graduate'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2800,183 +2803,191 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2035983374574059838</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n">
-        <v>46105.19982638889</v>
+        <v>46104.48630787037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2035984966622879907</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2035990013700157483</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/netdiscussion/status/2035990013700157483</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Same message receiving multiple times with zero response</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1774252820000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2035983374574059838</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'Muhammad Kashif Ashraf', 'screenName': 'netdiscussion', 'followersCount': 27, 'favouritesCount': 14, 'friendsCount': 39, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2035984966622879907</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46104.50023148148</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/netdiscussion/status/2035990013700157483</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2035990013700157483</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2035995575489909048</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@netdiscussion we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1774254146000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2035983374574059838</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2035990013700157483</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46104.5155787037</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2035976151764549748</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>2032450113100984492</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://x.com/RakshtVaghasiya/status/2032450113100984492</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>1773408842000</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2032450113100984492</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" s="2" t="n">
-        <v>46094.73196759259</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2035976151764549748</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2032452730443256247</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1773409466000</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2032450113100984492</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2032450113100984492</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>46094.73918981481</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2035976151764549748</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2032457337122791694</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 0561891252</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1773410565000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3007,16 +3018,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2032452730443256247</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46094.75190972222</v>
+        <v>46094.73196759259</v>
       </c>
     </row>
     <row r="38">
@@ -3032,21 +3039,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2032458133151342720</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
+          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1773410754000</v>
+        <v>1773409466000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3060,7 +3067,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3070,23 +3077,23 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2032457337122791694</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46094.75409722222</v>
+        <v>46094.73918981481</v>
       </c>
     </row>
     <row r="39">
@@ -3102,21 +3109,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
+          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
+          <t>@EmiratesNBD_KSA 0561891252</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1774246823000</v>
+        <v>1773410565000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3147,16 +3154,16 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2032458133151342720</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46104.43082175926</v>
+        <v>46094.75190972222</v>
       </c>
     </row>
     <row r="40">
@@ -3172,21 +3179,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1774249515000</v>
+        <v>1773410754000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3200,67 +3207,67 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>53</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46104.46197916667</v>
+        <v>46094.75409722222</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2035957091601657909</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2035957091601657909</t>
+          <t>2035964859116879927</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
+          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
+          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1774244971000</v>
+        <v>1774246823000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3270,11 +3277,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3287,40 +3294,328 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46104.40938657407</v>
+        <v>46104.43082175926</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2035976151764549748</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2035976151764549748</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1774249515000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2032450113100984492</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2035964859116879927</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46104.46197916667</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035957508989444417</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2035957508989444417</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>حلّ فزورة رمضان واربح 10,000 درهم.
+من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
+ما اسم هذا البرنامج؟
+للمشاركة:
+1.تابع حساب بنك الإمارات دبي الوطني
+2.قم بالإشارة إلى 3 من أصدقائك
+3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1772260745000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>356</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>150</v>
+      </c>
+      <c r="M43" t="n">
+        <v>178</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>10365</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
+        <v>46081.44380787037</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035957508989444417</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2035957508989444417</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Solve this Ramadan riddle and win AED 10,000.
+From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
+What is the name of the program?
+To participate:
+1.Follow Emirates NBD
+2.Tag 3 friends
+3.Drop your answer below https://t.co/PDRSppGlrJ</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1772260777000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>84</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>36</v>
+      </c>
+      <c r="M44" t="n">
+        <v>44</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>46081.44417824074</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035957508989444417</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2035957508989444417</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2035957508989444417</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035957508989444417</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @skrana111 @krahman_4 @Shilpa4669</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1774245071000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>46104.41054398148</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2035957290990498203</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3332,366 +3627,78 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F46" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
         <v>57</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>26</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M46" t="n">
         <v>44</v>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="2" t="n">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
         <v>46099.63238425926</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957290990498203</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2035957290990498203</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2035957290990498203</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957290990498203</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App.  @Shilpa4669 @mnsadiq84 @FazilAnas</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1774245019000</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>46104.40994212963</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957508989444417</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2035957508989444417</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>حلّ فزورة رمضان واربح 10,000 درهم.
-من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
-ما اسم هذا البرنامج؟
-للمشاركة:
-1.تابع حساب بنك الإمارات دبي الوطني
-2.قم بالإشارة إلى 3 من أصدقائك
-3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1772260745000</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173959, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>356</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" t="n">
-        <v>150</v>
-      </c>
-      <c r="M44" t="n">
-        <v>178</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>10359</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="2" t="n">
-        <v>46081.44380787037</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957508989444417</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2035957508989444417</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2027634776555872373</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Solve this Ramadan riddle and win AED 10,000.
-From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
-What is the name of the program?
-To participate:
-1.Follow Emirates NBD
-2.Tag 3 friends
-3.Drop your answer below https://t.co/PDRSppGlrJ</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1772260777000</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173959, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>84</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>36</v>
-      </c>
-      <c r="M45" t="n">
-        <v>44</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>46081.44417824074</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957508989444417</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2035957508989444417</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2035957508989444417</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035957508989444417</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @skrana111 @krahman_4 @Shilpa4669</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1774245071000</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2027634776555872373</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>46104.41054398148</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
+          <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2035956939956642179</t>
+          <t>2035957290990498203</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2035956939956642179</t>
+          <t>2035957290990498203</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
+          <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App.  @Shilpa4669 @mnsadiq84 @FazilAnas</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1774244935000</v>
+        <v>1774245019000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3701,7 +3708,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -3718,50 +3725,50 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46104.40896990741</v>
+        <v>46104.40994212963</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
+          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2035956997238165721</t>
+          <t>2035964468413493475</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2035956997238165721</t>
+          <t>2035964468413493475</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
+          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
+          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1774244949000</v>
+        <v>1774246730000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2035964468413493475</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3771,7 +3778,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Eugene H Krabs', 'screenName': 'Mr__Krabs___', 'followersCount': 289, 'favouritesCount': 6312, 'friendsCount': 90, 'description': 'Entrepreneur | Diligent Saver | Prominent Businessman | Single Parent | Elementary School Graduate'}</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -3788,50 +3795,46 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" s="2" t="n">
-        <v>46104.40913194444</v>
+        <v>46104.42974537037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
+          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2035956878518460827</t>
+          <t>2035964468413493475</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2035956878518460827</t>
+          <t>2036243538225274912</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
+          <t>https://x.com/Mr__Krabs___/status/2036243538225274912</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>Ignoring the noise, breadth was weaker today than Friday. Still not seeing institutional buyers step in on an index level. Dealer positioning having a guiding hand lately. Even if things open today; couple months to normalize not great for stagflation narrative/tarriffs. 🫩</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1774244920000</v>
+        <v>1774313265000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2036243538225274912</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3841,7 +3844,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Eugene H Krabs', 'screenName': 'Mr__Krabs___', 'followersCount': 289, 'favouritesCount': 6312, 'friendsCount': 90, 'description': 'Entrepreneur | Diligent Saver | Prominent Businessman | Single Parent | Elementary School Graduate'}</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3854,54 +3857,50 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" s="2" t="n">
-        <v>46104.40879629629</v>
+        <v>46105.19982638889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2035956707604705316</t>
+          <t>2035956997238165721</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2035956707604705316</t>
+          <t>2035956997238165721</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1774244879000</v>
+        <v>1774244949000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3928,46 +3927,46 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46104.40832175926</v>
+        <v>46104.40913194444</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956681939828984</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2035956681939828984</t>
+          <t>2035956939956642179</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2035956681939828984</t>
+          <t>2035956939956642179</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956681939828984</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1774244873000</v>
+        <v>1774244935000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3981,7 +3980,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3998,7 +3997,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4007,41 +4006,41 @@
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46104.40825231482</v>
+        <v>46104.40896990741</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2035956572711710976</t>
+          <t>2035956878518460827</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2035956572711710976</t>
+          <t>2035956878518460827</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1774244847000</v>
+        <v>1774244920000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4068,46 +4067,46 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>46104.40795138889</v>
+        <v>46104.40879629629</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2035956637853421634</t>
+          <t>2035956707604705316</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2035956637853421634</t>
+          <t>2035956707604705316</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1774244863000</v>
+        <v>1774244879000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4138,7 +4137,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4147,41 +4146,41 @@
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>46104.40813657407</v>
+        <v>46104.40832175926</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
+          <t>https://x.com/parulghalout/status/2035956681939828984</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2035956407212925393</t>
+          <t>2035956681939828984</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2035956407212925393</t>
+          <t>2035956681939828984</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
+          <t>https://x.com/parulghalout/status/2035956681939828984</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
+          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1774244808000</v>
+        <v>1774244873000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4191,7 +4190,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -4213,35 +4212,175 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>46104.4075</v>
+        <v>46104.40825231482</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2035956637853421634</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2035956637853421634</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1774244863000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46104.40813657407</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2035956477169631536</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2035956477169631536</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1774244825000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46104.40769675926</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>https://x.com/parulghalout/status/2035956416520069280</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>2035956416520069280</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -4268,218 +4407,78 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F57" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>112</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
         <v>39</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M57" t="n">
         <v>51</v>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" s="2" t="n">
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
         <v>46092.58871527778</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035956416520069280</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2035956416520069280</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2035956416520069280</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2035956416520069280</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1774244810000</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46104.40752314815</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2035956477169631536</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2035956477169631536</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1774244825000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46104.40769675926</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
+          <t>https://x.com/parulghalout/status/2035956416520069280</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2035956342763258332</t>
+          <t>2035956416520069280</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2035956342763258332</t>
+          <t>2035956416520069280</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
+          <t>https://x.com/parulghalout/status/2035956416520069280</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1774244793000</v>
+        <v>1774244810000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4489,7 +4488,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'parul ghalout', 'screenName': 'parulghalout', 'followersCount': 1796, 'favouritesCount': 13856, 'friendsCount': 2528, 'description': ''}</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -4506,50 +4505,50 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46104.40732638889</v>
+        <v>46104.40752314815</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2035956152442449955</t>
+          <t>2035956342763258332</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2035956152442449955</t>
+          <t>2035956342763258332</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1774244747000</v>
+        <v>1774244793000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4576,50 +4575,50 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46104.40679398148</v>
+        <v>46104.40732638889</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2035956075355361747</t>
+          <t>2035956407212925393</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2035956075355361747</t>
+          <t>2035956407212925393</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1774244729000</v>
+        <v>1774244808000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4646,46 +4645,46 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46104.40658564815</v>
+        <v>46104.4075</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2035956001279775104</t>
+          <t>2035956152442449955</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2035956001279775104</t>
+          <t>2035956152442449955</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1774244711000</v>
+        <v>1774244747000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4716,7 +4715,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4725,31 +4724,171 @@
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>46104.40637731482</v>
+        <v>46104.40679398148</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2035955684098163029</t>
+          <t>2035956075355361747</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>2035956075355361747</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1774244729000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>46104.40658564815</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2035956001279775104</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2035956001279775104</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1774244711000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>46104.40637731482</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2035955834002501721</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -4761,218 +4900,78 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F64" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173959, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>75</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K64" t="n">
         <v>1</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L64" t="n">
         <v>37</v>
       </c>
-      <c r="M62" t="n">
-        <v>47</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>2423</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
+      <c r="M64" t="n">
+        <v>46</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" s="2" t="n">
         <v>46099.63233796296</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2035955684098163029</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2035955684098163029</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1774244635000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46104.40549768518</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2035955759859834985</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2035955759859834985</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1774244654000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>46104.40571759259</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2035955485564936537</t>
+          <t>2035955834002501721</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2035955485564936537</t>
+          <t>2035955834002501721</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1774244588000</v>
+        <v>1774244671000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2034225964863893587</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4999,50 +4998,50 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2034225964863893587</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>46104.40495370371</v>
+        <v>46104.40591435185</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2035955401255235904</t>
+          <t>2035955759859834985</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2035955401255235904</t>
+          <t>2035955759859834985</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1774244568000</v>
+        <v>1774244654000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2034225964863893587</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5074,59 +5073,59 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2034225964863893587</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>46104.40472222222</v>
+        <v>46104.40571759259</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2035937800336384350</t>
+          <t>2035955579966173454</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2033483915512484120</t>
+          <t>2035955579966173454</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2033483915512484120</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1773655320000</v>
+        <v>1774244611000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2033483915512484120</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDdm0s2WsAAhe1i.jpg', 'type': 'photo', 'id': '2033206812359438336'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5135,50 +5134,54 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>1763</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="n">
-        <v>46097.58472222222</v>
+        <v>46104.40521990741</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2035937800336384350</t>
+          <t>2035955684098163029</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2035789123034751105</t>
+          <t>2035955684098163029</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://x.com/c65kg/status/2035789123034751105</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى ترجع تفتح باقي الفروع بعد العيد ؟</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1774204924000</v>
+        <v>1774244635000</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2033483915512484120</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5188,11 +5191,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{'name': 'عبدالله', 'screenName': 'c65kg', 'followersCount': 9, 'favouritesCount': 359, 'friendsCount': 371, 'description': ''}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5205,119 +5208,115 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2033483915512484120</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P68" s="2" t="n">
-        <v>46103.94587962963</v>
+        <v>46104.40549768518</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2035937800336384350</t>
+          <t>2035947184114344234</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2035937800336384350</t>
+          <t>2035879255176093818</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>@c65kg مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
-https://t.co/dBzYUMz7u2</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1774240372000</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2033483915512484120</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17224, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2035789123034751105</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>46104.3561574074</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2035947184114344234</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2035879255176093818</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hi Team , 
 I'm in India , Unable to transfer money to myself. Payment getting declined . 
 Please check .</t>
         </is>
       </c>
+      <c r="F69" t="n">
+        <v>1774226413000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2035879255176093818</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'Shagil Shams', 'screenName': 'ShagilShams', 'followersCount': 0, 'favouritesCount': 22, 'friendsCount': 20, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>46104.19459490741</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2035947184114344234</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2035947184114344234</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
+Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>1774226413000</v>
+        <v>1774242609000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5331,11 +5330,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{'name': 'Shagil Shams', 'screenName': 'ShagilShams', 'followersCount': 0, 'favouritesCount': 22, 'friendsCount': 20, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5348,47 +5347,50 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2035879255176093818</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="n">
-        <v>46104.19459490741</v>
+        <v>46104.38204861111</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2035947184114344234</t>
+          <t>2035955401255235904</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2035947184114344234</t>
+          <t>2035955401255235904</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
-Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1774242609000</v>
+        <v>1774244568000</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2035879255176093818</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5398,7 +5400,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173956, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 343, 'favouritesCount': 22175, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -5415,16 +5417,16 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2035879255176093818</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="P71" s="2" t="n">
-        <v>46104.38204861111</v>
+        <v>46104.40472222222</v>
       </c>
     </row>
     <row r="72">
@@ -5470,7 +5472,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173959, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 173958, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -5487,7 +5489,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>778</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -5553,7 +5555,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5568,25 +5570,368 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2035937800336384350</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2033483915512484120</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2033483915512484120</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1773655320000</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2033483915512484120</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDdm0s2WsAAhe1i.jpg', 'type': 'photo', 'id': '2033206812359438336'}]</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" s="2" t="n">
+        <v>46097.58472222222</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2035937800336384350</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2035789123034751105</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://x.com/c65kg/status/2035789123034751105</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA متى ترجع تفتح باقي الفروع بعد العيد ؟</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1774204924000</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2033483915512484120</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالله', 'screenName': 'c65kg', 'followersCount': 9, 'favouritesCount': 359, 'friendsCount': 371, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2033483915512484120</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>46103.94587962963</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2035937800336384350</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2035937800336384350</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>@c65kg مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
+https://t.co/dBzYUMz7u2</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1774240372000</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2033483915512484120</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17225, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2035789123034751105</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>46104.3561574074</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2034756691150217623</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://x.com/Ben252024/status/2034756691150217623</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1773958773000</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2034756691150217623</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>{'name': 'Ben', 'screenName': 'Ben252024', 'followersCount': 48, 'favouritesCount': 204, 'friendsCount': 5, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>46101.09690972222</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>@Ben252024 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1774254360000</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2034756691150217623</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2034756691150217623</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>46104.51805555556</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -5595,313 +5940,177 @@
 تُطبق الشروط والأحكام. https://t.co/0ixzmktjGV</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F79" t="n">
         <v>1774266066000</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEF8qB6WkAAHVos.jpg', 'type': 'photo', 'id': '2036045568057708544'}]</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
         <v>46104.65354166667</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>2035989928291488100</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F80" t="n">
         <v>1774252800000</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>2035989928291488100</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" s="2" t="n">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" s="2" t="n">
         <v>46104.5</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://x.com/Ben252024/status/2034756691150217623</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1773958773000</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>{'name': 'Ben', 'screenName': 'Ben252024', 'followersCount': 48, 'favouritesCount': 204, 'friendsCount': 5, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>46101.09690972222</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>@Ben252024 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1774254360000</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>2034756691150217623</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="n">
-        <v>46104.51805555556</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2035989928291488100</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2035989927905693845</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2035989927905693845</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2035989927905693845</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
 Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
-      <c r="F78" t="n">
+      <c r="F81" t="n">
         <v>1774252800000</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>2035989927905693845</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
         <v>46104.5</v>
       </c>
     </row>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,189 +517,189 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1774596664000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>46108.47990740741</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1774667679000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 45, 'favouritesCount': 1803, 'friendsCount': 22, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46109.30184027777</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2037590379881472140</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2037585240823058713</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus/status/2037585240823058713</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم
 هل شحن المحافظ الالكترونية عليه رسوم ؟ 
 مثل محفظة STCBANK ؟</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" t="n">
         <v>1774633152000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2037585240823058713</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
-        <v>46108.90222222222</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2037590379881472140</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2037590379881472140</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>@Talal_Hus عليكم السلام ورحمه الله وبركاته مرحبا طلال شكرا لتواصلك معنا يرجي العلم ان شحن المحافظ الإلكترونيه لا تطبق عليه رسوم في الوقت الحالي</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1774634377000</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2037585240823058713</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2037585240823058713</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46108.91640046296</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1774596664000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
@@ -707,50 +707,50 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46108.47990740741</v>
+        <v>46108.90222222222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037590379881472140</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037590379881472140</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>@Talal_Hus عليكم السلام ورحمه الله وبركاته مرحبا طلال شكرا لتواصلك معنا يرجي العلم ان شحن المحافظ الإلكترونيه لا تطبق عليه رسوم في الوقت الحالي</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1774667679000</v>
+        <v>1774634377000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2037585240823058713</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 45, 'favouritesCount': 1802, 'friendsCount': 22, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -777,16 +777,16 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2037585240823058713</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46109.30184027777</v>
+        <v>46108.91640046296</v>
       </c>
     </row>
     <row r="6">
@@ -853,7 +853,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -922,7 +922,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -937,207 +937,207 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>https://x.com/Talal_Hus/status/2037585240823058713</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2037585240823058713</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2037587904961118424</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/Talal_Hus/status/2037587904961118424</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>وكيف اقدر استفيد من الخصم بسعر الكاش سواء من جرير او غيره حسب العروض اللي عندكم ؟</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1774633787000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2037585240823058713</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2037585240823058713</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>46108.90957175926</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>https://x.com/GCCBusinessNews/status/2037566177971667423</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2037566177971667423</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2037566177971667423</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/GCCBusinessNews/status/2037566177971667423</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>UAE-based brokerage firm International Securities has gone live on Emirates NBD Pay, utilizing Visa’s Account Funding Transaction (AFT) model.
 https://t.co/4HI6PNXgLf
 #EmiratesNBD #InternationalSecurities #EmiratesNBDPay  #GCCBusinessNews @EmiratesNBD_AE  @IntlSecurities https://t.co/OPZ72BFWNQ</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" t="n">
         <v>1774628607000</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2037566177971667423</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEbjn_2a8AAzMNb.jpg', 'type': 'photo', 'id': '2037566157725822976'}]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 468, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="2" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
         <v>46108.84961805555</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>https://x.com/GCCBusinessNews/status/2037566177971667423</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2037566177971667423</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2037544454459122043</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://x.com/GCCBusinessNews/status/2037544454459122043</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ADNOC and OMV reveal the executive leadership team and Supervisory Board of the global polyolefins leader, Borouge Group International AG.
 https://t.co/b2EHo7k3cg
 #BorougeGroup #ADNOC #OMV #Polyolefins #LeadershipTeam #GlobalExpansion #GCCBusinessNews @ADNOCGroup @omv @Borouge https://t.co/pYHZ1Gmopv</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" t="n">
         <v>1774623428000</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2037544454459122043</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEbP37iaMAA8TjD.jpg', 'type': 'photo', 'id': '2037544441213497344'}]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 468, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" s="2" t="n">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="n">
         <v>46108.78967592592</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://x.com/Talal_Hus/status/2037585240823058713</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2037585240823058713</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2037587904961118424</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/Talal_Hus/status/2037587904961118424</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>وكيف اقدر استفيد من الخصم بسعر الكاش سواء من جرير او غيره حسب العروض اللي عندكم ؟</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1774633787000</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2037585240823058713</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2037585240823058713</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>46108.90957175926</v>
       </c>
     </row>
     <row r="11">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12471, 'favouritesCount': 442918, 'friendsCount': 8659, 'description': 'Roman Catholic, MAGA Conservatives republican, Honest woman that say what on her mind , MAGA constitution . Researcher on the global monitor system.'}</t>
+          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12468, 'favouritesCount': 442918, 'friendsCount': 8658, 'description': 'Roman Catholic, MAGA Conservatives republican, Honest woman that say what on her mind , MAGA constitution . Researcher on the global monitor system.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12471, 'favouritesCount': 442918, 'friendsCount': 8659, 'description': 'Roman Catholic, MAGA Conservatives republican, Honest woman that say what on her mind , MAGA constitution . Researcher on the global monitor system.'}</t>
+          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12468, 'favouritesCount': 442918, 'friendsCount': 8658, 'description': 'Roman Catholic, MAGA Conservatives republican, Honest woman that say what on her mind , MAGA constitution . Researcher on the global monitor system.'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>797</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2883, 'favouritesCount': 124231, 'friendsCount': 6501, 'description': '🗺️'}</t>
+          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2881, 'favouritesCount': 124230, 'friendsCount': 6501, 'description': '🗺️'}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>513</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1973,39 +1973,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/HomszRami/status/2037511645971583026</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037507103892341213</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2037511645971583026</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2037511645971583026</t>
-        </is>
-      </c>
+          <t>2037507103892341213</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/HomszRami/status/2037511645971583026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Mutual fund/ Investment Fund
-#ENBDRiddleOfTheWeek 
-#financialwellbeing</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1774615606000</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2037171731865931987</t>
-        </is>
-      </c>
+        <v>1774678819194</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2013,33 +1999,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Rami Almsri', 'screenName': 'HomszRami', 'followersCount': 0, 'favouritesCount': 146, 'friendsCount': 30, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2037171731865931987</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46108.69914351852</v>
+        <v>46109.43077770833</v>
       </c>
     </row>
     <row r="24">
@@ -2053,17 +2023,29 @@
           <t>2037507103892341213</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2037502674548015413</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>https://x.com/EmiratesNBD_AE/status/2037502674548015413</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>@Ibn_3ali مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
+        </is>
+      </c>
       <c r="F24" t="n">
-        <v>1774670835785</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>1774613467000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2037501728149668348</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2071,17 +2053,33 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2037501728149668348</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="n">
-        <v>46109.3383771412</v>
+        <v>46108.67438657407</v>
       </c>
     </row>
     <row r="25">
@@ -2097,21 +2095,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2037502674548015413</t>
+          <t>2037502797097361735</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037502674548015413</t>
+          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@Ibn_3ali مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
+          <t>@EmiratesNBD_AE كنت عايز أقفل حسابي</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1774613467000</v>
+        <v>1774613496000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2125,7 +2123,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Ahmed Ali', 'screenName': 'Ibn_3ali', 'followersCount': 1450, 'favouritesCount': 3489, 'friendsCount': 175, 'description': 'Nubia, football &amp; some digital marketing stuff - Trying to be a Guru'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2142,16 +2140,16 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2037501728149668348</t>
+          <t>2037502674548015413</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46108.67438657407</v>
+        <v>46108.67472222223</v>
       </c>
     </row>
     <row r="26">
@@ -2167,61 +2165,61 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2037505623932199158</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037505623932199158</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>@Ibn_3ali نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1774614170000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2037501728149668348</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>2037502797097361735</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE كنت عايز أقفل حسابي</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1774613496000</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2037501728149668348</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{'name': 'Ahmed Ali', 'screenName': 'Ibn_3ali', 'followersCount': 1450, 'favouritesCount': 3489, 'friendsCount': 175, 'description': 'Nubia, football &amp; some digital marketing stuff - Trying to be a Guru'}</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2037502674548015413</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="n">
-        <v>46108.67472222223</v>
+        <v>46108.68252314815</v>
       </c>
     </row>
     <row r="27">
@@ -2237,85 +2235,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2037505623932199158</t>
+          <t>2037507103892341213</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037505623932199158</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037507103892341213</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>@Ibn_3ali نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1774614170000</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2037501728149668348</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2037502797097361735</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>46108.68252314815</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037507103892341213</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2037507103892341213</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2037507103892341213</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037507103892341213</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>من عنوان بريده الإلكتروني المسجل، مع كتابة "طلب إغلاق الحساب" في خانة
  الموضوع.
@@ -2325,72 +2253,72 @@
 في حال عدم وجود أي مخالفات، سيتم إغلاق طلب إغلاق الحساب عبر البريد الإلكتروني خلال 7 أيام عمل</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F27" t="n">
         <v>1774614523000</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2037501728149668348</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>2037505706405040176</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P27" s="2" t="n">
         <v>46108.6866087963</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037507063501275362</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2037507063501275362</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2037507063501275362</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037507063501275362</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>@Ibn_3ali الرجاء القيام بما يلي قبل إغلاق الحساب: 
 سحب جميع الأموال من الحساب
@@ -2399,72 +2327,72 @@
  requests@emiratesnbd.com</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F28" t="n">
         <v>1774614513000</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2037501728149668348</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>2037505706405040176</t>
         </is>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>46108.68649305555</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2037505175750054028</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2036328892919685283</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036328892919685283</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>شهر جديد مع المزيد من الفائزين.
 تهانينا للفائز بالجائزة الكبرى وهي سيارة ROX 01، وللفائزين أيضًا بجائزة القطعة الذهبية بوزن 10 غرامات وذلك لاشتراكهم في حملة "حان وقت ربح جوائز كبرى" المقدمة من الخدمات المصرفية للأعمال لشهر يناير 2026.
@@ -2472,76 +2400,146 @@
 يسري العرض حتى 31 مارس 2026.</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F29" t="n">
         <v>1774333615000</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2036328892919685283</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2036328726942699520/img/TbNnGhuWK4s8W3CF.jpg', 'type': 'video', 'id': '2036328726942699520'}]</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>8</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" s="2" t="n">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
         <v>46105.4353587963</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2037505175750054028</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2036430572923609589</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan/status/2036430572923609589</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hello @EmiratesNBD_AE 
 URGENT: Resolution Required for Case #983058 - Medical Emergency &amp;amp; Travel Restrictions case no : #983058
 Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>1774357858000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2036328892919685283</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2036328892919685283</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46105.71594907407</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2037505175750054028</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2036438860737982775</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036438860737982775</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>@HimanshuMotiyan We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+        </is>
+      </c>
       <c r="F31" t="n">
-        <v>1774357858000</v>
+        <v>1774359834000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2555,11 +2553,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2572,16 +2570,16 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2036328892919685283</t>
+          <t>2036430572923609589</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46105.71594907407</v>
+        <v>46105.73881944444</v>
       </c>
     </row>
     <row r="32">
@@ -2597,61 +2595,61 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2037491991504998834</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1774610920000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2036328892919685283</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>2036438860737982775</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036438860737982775</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>@HimanshuMotiyan We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1774359834000</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2036328892919685283</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2036430572923609589</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="n">
-        <v>46105.73881944444</v>
+        <v>46108.6449074074</v>
       </c>
     </row>
     <row r="33">
@@ -2667,21 +2665,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2037491991504998834</t>
+          <t>2037495447351087452</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037495447351087452</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+          <t>@HimanshuMotiyan We sincerely regret for the inconvenience, please note that we have replied to your email</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1774610920000</v>
+        <v>1774611744000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2695,7 +2693,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2712,16 +2710,16 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2036438860737982775</t>
+          <t>2037491991504998834</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46108.6449074074</v>
+        <v>46108.65444444444</v>
       </c>
     </row>
     <row r="34">
@@ -2737,95 +2735,96 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2037505175750054028</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1774614063000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2036328892919685283</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
           <t>2037495447351087452</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037495447351087452</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>@HimanshuMotiyan We sincerely regret for the inconvenience, please note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1774611744000</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2036328892919685283</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2037491991504998834</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="n">
-        <v>46108.65444444444</v>
+        <v>46108.68128472222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
+          <t>https://x.com/Ldyheart/status/2037488851749409129</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2037505175750054028</t>
+          <t>2037488851749409129</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2037505175750054028</t>
+          <t>2037488851749409129</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
+          <t>https://x.com/Ldyheart/status/2037488851749409129</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
+          <t>Emirates NBD enables instant trading account top-ups for UAE investors
+New system lets UAE investors fund trading accounts in near real time https://t.co/cFjr79kcqn</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1774614063000</v>
+        <v>1774610171000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2036328892919685283</t>
+          <t>2037488851749409129</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2835,7 +2834,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Himanshu Motiyani', 'screenName': 'HimanshuMotiyan', 'followersCount': 1, 'favouritesCount': 3, 'friendsCount': 66, 'description': ''}</t>
+          <t>{'name': 'RV Global Reset', 'screenName': 'Ldyheart', 'followersCount': 247, 'favouritesCount': 12084, 'friendsCount': 329, 'description': 'WWG1WGA https://t.co/5V16q1MN7j'}</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2852,16 +2851,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2037495447351087452</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" s="2" t="n">
-        <v>46108.68128472222</v>
+        <v>46108.63623842593</v>
       </c>
     </row>
     <row r="36">
@@ -2877,26 +2872,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2037488851749409129</t>
+          <t>2037581533863645627</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/Ldyheart/status/2037488851749409129</t>
+          <t>https://x.com/Ldyheart/status/2037581533863645627</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Emirates NBD enables instant trading account top-ups for UAE investors
-New system lets UAE investors fund trading accounts in near real time https://t.co/cFjr79kcqn</t>
+          <t>Nasdaq 100 Enters Correction As 30-Year Yields Near 5%: What's Moving Markets Friday? https://t.co/hsdPKDGVVr</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1774610171000</v>
+        <v>1774632268000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2037488851749409129</t>
+          <t>2037581533863645627</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2923,46 +2917,46 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46108.63623842593</v>
+        <v>46108.89199074074</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/Ldyheart/status/2037488851749409129</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037487764074008675</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2037488851749409129</t>
+          <t>2037487764074008675</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2037507586799345908</t>
+          <t>2037476568159727811</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/Ldyheart/status/2037507586799345908</t>
+          <t>https://x.com/abumusab999/status/2037476568159727811</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>US ITC opens Section 337 probe into global TOPCon supply chain https://t.co/EB1fmme6hI</t>
+          <t>@EmiratesNBD_KSA كيف طريقة استخراج بطاقة مزيد الائتمانيه ؟</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1774614638000</v>
+        <v>1774607242000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2037507586799345908</t>
+          <t>2037476568159727811</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2972,11 +2966,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'RV Global Reset', 'screenName': 'Ldyheart', 'followersCount': 247, 'favouritesCount': 12084, 'friendsCount': 329, 'description': 'WWG1WGA https://t.co/5V16q1MN7j'}</t>
+          <t>{'name': 'SMAMRI', 'screenName': 'abumusab999', 'followersCount': 1276, 'favouritesCount': 1873, 'friendsCount': 1441, 'description': 'لا اله الا انت سبحانك اني كنت من الظالمين'}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2985,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46108.68793981482</v>
+        <v>46108.60233796296</v>
       </c>
     </row>
     <row r="38">
@@ -3010,27 +3004,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>2037481371753443331</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037481371753443331</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@abumusab999 مرحبا شكرا لتواصلك معنا برجاء التوضيح هل ترغب في التقديم علي بطاقه جديده أو أستبدال بطاقه حاليه</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1774608388000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>2037476568159727811</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/abumusab999/status/2037476568159727811</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA كيف طريقة استخراج بطاقة مزيد الائتمانيه ؟</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1774607242000</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2037476568159727811</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3038,7 +3032,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'SMAMRI', 'screenName': 'abumusab999', 'followersCount': 1276, 'favouritesCount': 1873, 'friendsCount': 1441, 'description': 'لا اله الا انت سبحانك اني كنت من الظالمين'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3055,12 +3049,16 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2037476568159727811</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="n">
-        <v>46108.60233796296</v>
+        <v>46108.61560185185</v>
       </c>
     </row>
     <row r="39">
@@ -3076,21 +3074,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2037481371753443331</t>
+          <t>2037486145496387811</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037481371753443331</t>
+          <t>https://x.com/abumusab999/status/2037486145496387811</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@abumusab999 مرحبا شكرا لتواصلك معنا برجاء التوضيح هل ترغب في التقديم علي بطاقه جديده أو أستبدال بطاقه حاليه</t>
+          <t>@EmiratesNBD_KSA جديده</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1774608388000</v>
+        <v>1774609526000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3104,7 +3102,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'SMAMRI', 'screenName': 'abumusab999', 'followersCount': 1276, 'favouritesCount': 1873, 'friendsCount': 1441, 'description': 'لا اله الا انت سبحانك اني كنت من الظالمين'}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3121,16 +3119,16 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2037476568159727811</t>
+          <t>2037481371753443331</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46108.61560185185</v>
+        <v>46108.62877314815</v>
       </c>
     </row>
     <row r="40">
@@ -3146,96 +3144,96 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>2037487764074008675</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037487764074008675</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>@abumusab999 مرحباً بك, يمكنك الأن معرفة المزيد والتقديم من خلال الضغط على الرابط ادناه.
+https://t.co/qD6MpG7T1A</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1774609912000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2037476568159727811</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
           <t>2037486145496387811</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/abumusab999/status/2037486145496387811</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA جديده</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1774609526000</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2037476568159727811</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>{'name': 'SMAMRI', 'screenName': 'abumusab999', 'followersCount': 1276, 'favouritesCount': 1873, 'friendsCount': 1441, 'description': 'لا اله الا انت سبحانك اني كنت من الظالمين'}</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2037481371753443331</t>
-        </is>
-      </c>
       <c r="P40" s="2" t="n">
-        <v>46108.62877314815</v>
+        <v>46108.63324074074</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037487764074008675</t>
+          <t>https://x.com/DubaiTradersHub/status/2037486509704761575</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2037487764074008675</t>
+          <t>2037486509704761575</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2037487764074008675</t>
+          <t>2037486509704761575</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037487764074008675</t>
+          <t>https://x.com/DubaiTradersHub/status/2037486509704761575</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@abumusab999 مرحباً بك, يمكنك الأن معرفة المزيد والتقديم من خلال الضغط على الرابط ادناه.
-https://t.co/qD6MpG7T1A</t>
+          <t>UAE Market: The Golden Opportunity After War Dislocation -  https://t.co/zEkCcFPlpV</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1774609912000</v>
+        <v>1774609613000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2037476568159727811</t>
+          <t>2037486509704761575</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3245,7 +3243,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17243, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Dubai Traders Hub', 'screenName': 'DubaiTradersHub', 'followersCount': 144, 'favouritesCount': 115, 'friendsCount': 49, 'description': 'Join our vibrant community for signals, Social gathering, webinars &amp; step-by-step guides to financial freedom.'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3258,64 +3256,62 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2037486145496387811</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46108.63324074074</v>
+        <v>46108.62978009259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/DubaiTradersHub/status/2037486509704761575</t>
+          <t>https://x.com/livemint/status/2037484492445848044</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2037486509704761575</t>
+          <t>2037484492445848044</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2037486509704761575</t>
+          <t>2037484492445848044</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/DubaiTradersHub/status/2037486509704761575</t>
+          <t>https://x.com/livemint/status/2037484492445848044</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UAE Market: The Golden Opportunity After War Dislocation -  https://t.co/zEkCcFPlpV</t>
+          <t>#MintIIS2026 | India is predominantly family-owned. For society to accept M&amp;amp;As, there had to be behavioural change: Alok Malpani, Emirates NBD Capital India
+Watch live 📺  https://t.co/LpbhUczG5d
+@Priyamouli1812 | @JSALawIndia @SAEL_India @PFRDAOfficial @equirusgroup https://t.co/o2QiCS0nWQ</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1774609613000</v>
+        <v>1774609132000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2037486509704761575</t>
+          <t>2037484492445848044</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2037484316788445184/img/WCZODF-176KDIpyk.jpg', 'type': 'video', 'id': '2037484316788445184'}]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Traders Hub', 'screenName': 'DubaiTradersHub', 'followersCount': 144, 'favouritesCount': 115, 'friendsCount': 49, 'description': 'Join our vibrant community for signals, Social gathering, webinars &amp; step-by-step guides to financial freedom.'}</t>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027887, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3328,40 +3324,248 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>919</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46108.62978009259</v>
+        <v>46108.62421296296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>https://x.com/livemint/status/2037484492445848044</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2037484492445848044</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2037740701203780080</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037740701203780080</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>The Russian government announced that it will impose a ban on gasoline exports starting 1 April,
+Here's what the Putin government said 👇
+https://t.co/ysJKhdplMr https://t.co/hSVIDcSkHb</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1774670217000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2037740701203780080</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEeCXKcasAA9_Gj.jpg', 'type': 'photo', 'id': '2037740690860584960'}]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027887, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
+        <v>46109.33121527778</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2037484780925644991</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2037484780925644991</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
+قدم الان بتسهيلات خاصة لعملاء المجموعة.
+مع بعض .. تفرق.
+تطبق الشروط والأحكام
+رقم التسجيل الضريبي: 319-897-204 https://t.co/ABhnylgeTj</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1774609201000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2037484780925644991</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEXsVt2XUAAgb1M.jpg', 'type': 'video', 'id': '2037294237855645696'}]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2972, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="n">
+        <v>46108.62501157408</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2037484780925644991</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2037243186066686460</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037243186066686460</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Plan your vacation now!
+Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY
+Offer valid until 30th of March 2026.
+Terms and conditions apply.
+Tax registration number: 204-897-319 https://t.co/RR0ArWOU9A</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1774551600000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2037243186066686460</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEV1yF9XwAApaiO.jpg', 'type': 'video', 'id': '2037163879621406720'}]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2972, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>46107.95833333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2037484781038862844</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2037484781038862844</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
 Apply now and benefit from a dedicated program for TMG clients.
@@ -3370,344 +3574,68 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F46" t="n">
         <v>1774609201000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2037484781038862844</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEWl4QwWkAElitt.jpg', 'type': 'video', 'id': '2037216722512424960'}]</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2972, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="2" t="n">
-        <v>46108.62501157408</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2037484781038862844</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2037243186066686460</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037243186066686460</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Plan your vacation now!
-Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY
-Offer valid until 30th of March 2026.
-Terms and conditions apply.
-Tax registration number: 204-897-319 https://t.co/RR0ArWOU9A</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1774551600000</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2037243186066686460</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEV1yF9XwAApaiO.jpg', 'type': 'video', 'id': '2037163879621406720'}]</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2972, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="2" t="n">
-        <v>46107.95833333334</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037484492445848044</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2037484492445848044</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2037484492445848044</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037484492445848044</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | India is predominantly family-owned. For society to accept M&amp;amp;As, there had to be behavioural change: Alok Malpani, Emirates NBD Capital India
-Watch live 📺  https://t.co/LpbhUczG5d
-@Priyamouli1812 | @JSALawIndia @SAEL_India @PFRDAOfficial @equirusgroup https://t.co/o2QiCS0nWQ</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1774609132000</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2037484492445848044</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2037484316788445184/img/WCZODF-176KDIpyk.jpg', 'type': 'video', 'id': '2037484316788445184'}]</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" s="2" t="n">
-        <v>46108.62421296296</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037484492445848044</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2037484492445848044</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2037541938484879640</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037541938484879640</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Nifty at 19x PE: Valuations cool to Asian peer levels, but is it ‘fair’ enough to bring FPIs back?
-(@MayurBhalerao1 reports)
-https://t.co/taflTADXD6</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1774622828000</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2037541938484879640</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46108.78273148148</v>
+        <v>46108.62501157408</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2037484780925644991</t>
+          <t>2037483796837380338</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2037484780925644991</t>
+          <t>2037407607351292299</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+          <t>https://x.com/livemint/status/2037407607351292299</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204 https://t.co/ABhnylgeTj</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1774609201000</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2037484780925644991</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEXsVt2XUAAgb1M.jpg', 'type': 'video', 'id': '2037294237855645696'}]</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2972, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" s="2" t="n">
-        <v>46108.62501157408</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037407607351292299</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
         <is>
           <t>#MintIIS2026 | What will define the next wave of investment opportunities in India? 📊
 📺 Tune into Day 2 of the Mint India Investment Summit &amp; Awards 2026 for insights on growth sectors, innovation, and market strategies - ending with the prestigious awards night 🏆✨
@@ -3716,8 +3644,82 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
+      <c r="F47" t="n">
+        <v>1774590801000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZTUi6b0AAypIz.jpg', 'type': 'photo', 'id': '2037407493866115072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZTUjjboAAkoQC.jpg', 'type': 'photo', 'id': '2037407494038069248'}]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="2" t="n">
+        <v>46108.41204861111</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2037410551131951539</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037410551131951539</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MintIIS2026 | Jay Kotak, EVP &amp; Co-Head, @kotak811 on disruption, scale &amp; strategy 💡.
+⚡️ The idea of a zero-balance bank account was disruptive when it was first launched
+⚡️ Its less about what our competition thinks, and more about our business model and what our customers think
+⚡️ Scalability in India depends on the products. India is a price-sensitive market, and products need to be tailored to what customers want
+⚡️ There is a place for building tech, and a place for buying tech
+⚡️ When we think of our customers, we prefer building rather than buying if we think the product can be substantially scaled
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+ @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @jay_kotakone</t>
+        </is>
+      </c>
       <c r="F48" t="n">
-        <v>1774590801000</v>
+        <v>1774591503000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3726,12 +3728,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZTUi6b0AAypIz.jpg', 'type': 'photo', 'id': '2037407493866115072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZTUjjboAAkoQC.jpg', 'type': 'photo', 'id': '2037407494038069248'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZV_15aoAACAo0.png', 'type': 'photo', 'id': '2037410436719747072'}]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -3744,16 +3746,20 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1667</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="n">
-        <v>46108.41204861111</v>
+        <v>46108.42017361111</v>
       </c>
     </row>
     <row r="49">
@@ -3769,15 +3775,765 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2037412016697290775</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037412016697290775</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MintIIS2026 | Jay Kotak, EVP &amp; Co-Head, @kotak811
+ on building with purpose &amp; scale.
+⚡️ Entire kotak group has a team of in-house engineers. The thought product is always to strategically trade off the build vs buy scenarios
+⚡️ We don't seek customer numbers for the vanity of it. We want real, tangible, engaged customers
+⚡️ The goal is for every Indian to have a bank account
+⚡️ We are very mission-oriented at 811 
+⚡️ I spend time on the main Kotak banking app, with the idea of bringing the best features of 811 to this app
+⚡️ I spent some time with Kotak's wholesale businesses too
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+ @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @jay_kotakone</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1774591852000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZXaV5bUAAc6SC.jpg', 'type': 'photo', 'id': '2037411991497953280'}]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2037410551131951539</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46108.42421296296</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2037414140453716370</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037414140453716370</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 | Jay Kotak, EVP &amp; Co-Head, @kotak811 on regulation, performance &amp; digital banking.
+⚡️ Kotak is a regulated, listed entity. We take that very seriously
+⚡️ I am evaluated as a professional based on my business' P&amp;L statement
+⚡️ Nubank and revolut are businesses we greatly admire and track
+⚡️ Digital banking depends on the target customer and the market regulation
+⚡️ Making banking digital is extremely necessary and important in India
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit  | @jay_kotakone</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1774592359000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZZFwrbQAAajEr.jpg', 'type': 'photo', 'id': '2037413836932988928'}]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2037412016697290775</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46108.43008101852</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2037415831320268911</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037415831320268911</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 | Jay Kotak, EVP &amp; Co-Head, @kotak811 on banking &amp; customer experience.
+⚡️ Banking industry in India is well-regulated and well-capitalised
+⚡️ We as banks need to be better at interacting with our customers
+⚡️ We need to improve the way our customers interact with us for something as important as managing their money
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @jay_kotakone</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1774592762000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZa1CNawAAXAK2.jpg', 'type': 'photo', 'id': '2037415748604444672'}]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2037414140453716370</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46108.43474537037</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2037417484438098342</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037417484438098342</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 | Saurabh Chatterjee, Managing Director, ChrysCap on evolving investment strategy 📊
+We've been doing more control investments over the past two or three fund cycles, not because we think every control deal is better than every minority deal. We are involving in conjunction with the market.
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1774593156000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZcFg5bIAAaBa7.jpg', 'type': 'photo', 'id': '2037417131231617024'}]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2037415831320268911</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46108.43930555556</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2037418584906068341</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037418584906068341</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 |  Hari Gopalakrishnan,  Partner, Deputy Co-Head of Private Capital Asia, Head of India and Global Co-Head of Services for EQT on India’s evolving buyout landscape
+We started doing buyouts in 2013. Overall our platform is very focused on buyouts and that has worked well for us. 
+But over time, more Indian founders are open to the idea of finding a good home for their businesses. We still think we are scratching the surface. 
+I still think that buyouts are going to grow much more than in the past.
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @eqt</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1774593418000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZdHHLakAASR6O.jpg', 'type': 'photo', 'id': '2037418258199121920'}]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2037417484438098342</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46108.44233796297</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2037419775010476362</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037419775010476362</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 |  Mayank Bajpai, partner, TPG Growth and Rise says for good companies, capital has become a commodity. So they're asking a lot more from the Capital Partners as to, how can they help value add during the journey of investment.
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @tpg</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1774593702000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZeQhHakAAFEbv.jpg', 'type': 'photo', 'id': '2037419519292116992'}]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2037418584906068341</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46108.445625</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2037420958357594161</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037420958357594161</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 |  "I think while financial services, healthcare, all of these will continue, we will see a lot of investments in the entire AI space going forward": Vikram Raghani, Partner, JSA  Advocates &amp; Solicitors.
+Watch live 🔴 https://t.co/dCIYKz2kzi
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1774593984000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZfURdbAAA9CMB.jpg', 'type': 'photo', 'id': '2037420683320557568'}]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2037419775010476362</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46108.44888888889</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2037425124023120121</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037425124023120121</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 |  Hari Gopalakrishnan, Partner, Deputy Co-Head of Private Capital Asia, Head of India and Global Co-Head of Services for EQT on exits &amp; market evolution.
+"Having a vibrant capital market is important for the growth of private equity. But I'm also conscious that for buyouts, if you buy 100% of a company, it's also not easy to sell down completely. But as the market matures, that will happen over time as well, and we'll see more private equity firms take a company from 100 to zero".
+Watch live 🔴 https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit  | @eqt</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1774594977000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZjOihawAAx7AY.jpg', 'type': 'photo', 'id': '2037424982868017152'}]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2037420958357594161</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46108.46038194445</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2037428102012469311</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037428102012469311</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 | Saurabh Chatterjee, Managing Director, ChrysCap on future deal structures
+"I think you will see more single asset continuation vehicles in the future, single asset CV just depends on how strong that one single asset. There are other companies in our portfolio right now that eventually could be single assets. So obviously, we'll take that call as when it happens".
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+ @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia | @MProfit</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1774595687000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZmDRnaMAARCYf.jpg', 'type': 'photo', 'id': '2037428087886065664'}]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2037425124023120121</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46108.46859953704</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2037430456938106907</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037430456938106907</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>#MintIIS2026 | @nikunjbiyani, Co-founder, Superyou on the idea behind SuperYou
+“The idea of Superyou came from the basketball court where Ranveer [Singh] and I were playing. That’s when we thought of building a better-for-you product. When we started, we had a very strong conviction about the first product and we thought it would give us the focus and land well with the consumer in a world that’s void of attention.”
+Watch live 🔴
+https://t.co/dCIYKz2SoQ
+@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1774596249000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2037407607351292299</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZn_1kaIAAG49_.jpg', 'type': 'photo', 'id': '2037430227840933888'}]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2037428102012469311</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46108.47510416667</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/livemint/status/2037483796837380338</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2037483796837380338</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>2037432527229792675</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037432527229792675</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Vimarsh Razdan, Co-founder &amp; CEO, Underneat on building in a changing media landscape
 “I’m a fourth-time builder now and I know that the fundamentals of the business will remain the same. But if businesses have to keep up with the evolution of media. Earlier, promotions were about television, radio and print. Today, it’s about creators and social media. Founders have to observe how the pillars are moving.”
@@ -3786,72 +4542,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F59" t="n">
         <v>1774596742000</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpOBKbMAAZgW8.jpg', 'type': 'photo', 'id': '2037431570982973440'}]</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>2037430456938106907</t>
         </is>
       </c>
-      <c r="P49" s="2" t="n">
+      <c r="P59" s="2" t="n">
         <v>46108.48081018519</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>2037439563832995941</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037439563832995941</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Shirish Godbole, CEO, Knowledge Realty Trust (REIT) on talent &amp; workplaces.
 "I think talent acquisition and getting the best people to work for you is a very very important criteria for all companies now. Obviously giving them the best space is one of the reasons, besides paying them obviously, but making them comfortable, giving them the best space is getting them excited about coming to work I think is another reason".
@@ -3860,72 +4616,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F60" t="n">
         <v>1774598420000</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZwE58acAAlKQP.jpg', 'type': 'photo', 'id': '2037439111007727616'}]</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>2037432527229792675</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P60" s="2" t="n">
         <v>46108.50023148148</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>2037441300233126013</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037441300233126013</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Shirish Godbole, CEO, Knowledge Realty Trust (REIT) says If you look at a large BFSIs, whether it's JP Morgan, whether it's a Morgan Stanley or a Google or Amazon, if you go inside their spaces, the amount of money that they spend on their space today is dramatically higher. It costs X Rupee per square foot, but it is not uncommon to have 10-15 thousand Rupees per square foot spend in fit-outs by the tenant after getting in.
 Watch live 🔴
@@ -3933,72 +4689,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F61" t="n">
         <v>1774598834000</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZx7zva8AADfIh.jpg', 'type': 'photo', 'id': '2037441153747054592'}]</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>2037439563832995941</t>
         </is>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P61" s="2" t="n">
         <v>46108.50502314815</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>2037442033573576984</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037442033573576984</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Vivek Chandy, Joint Managing Partner, JSA Advocates &amp; Solicitors says I think it's a lot about the money that's there in the market. Today, it's much easier to access funds. Earlier, ECBs were not permitted in the real estate space. Today, you can get money from abroad in the form of ECBs. Also, acquisition finance is available, so even if you are acquiring a company, earlier you couldn't use it and acquire on borrowed funds, you can do it now. All this has brought more money into the market, and people are able to have better quality, premium residential spaces and office spaces.
 Watch live 🔴
@@ -4006,72 +4762,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F62" t="n">
         <v>1774599009000</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZysfAb0AAaHiu.jpg', 'type': 'photo', 'id': '2037441989994860544'}]</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>2037441300233126013</t>
         </is>
       </c>
-      <c r="P52" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>46108.50704861111</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>2037443833588510843</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037443833588510843</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Harmohan Sahni, Managing Director &amp; CEO, @RaymondRealtyIN says Our chosen strategy is that we want to stay in deep markets and that necessitates that we are not looking at either the bottom of the pyramid because that market has not been doing well for the last almost even pre-Covid it was not doing well and after Covid it suffered even more. And we are not looking at luxury also, we are not looking at ₹80, ₹100, ₹50 crore worth apartments. We want to address the largest segment in the market which is ranging between ₹2 crores going all the way up to ₹10, ₹12, even ₹15 crores. The products are always going to be in line with the brand ethos. So Raymond stands for Trust, Quality, and Excellence. So quality is a given; that's something we are never going to compromise on.
 Watch live 🔴
@@ -4079,72 +4835,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F63" t="n">
         <v>1774599438000</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZz9ZibUAApdkV.jpg', 'type': 'photo', 'id': '2037443380096225280'}]</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>2037442033573576984</t>
         </is>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P63" s="2" t="n">
         <v>46108.51201388889</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>2037446136881910132</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037446136881910132</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Shirish Godbole, CEO, Knowledge Realty Trust (REIT) says global capability centers are really changing how much demand there has been for offices and that has also had a trickle-down effect on every other part of India, including the 2-10 crore purchases. While there has been high wealth which is spending more than 10 crores, the people buying the 2-4 crore apartments are typically service-oriented economies. 
 Watch live 🔴
@@ -4152,72 +4908,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F64" t="n">
         <v>1774599987000</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZ2aTWbcAARNSm.jpg', 'type': 'photo', 'id': '2037446075674750976'}]</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t>2037443833588510843</t>
         </is>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>46108.51836805556</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>2037447541843972418</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037447541843972418</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>#MintIIS2026 | REITs are very careful about what they buy. They typically, even if there's a fully let-out office building with very high rents, they won't touch it if, for instance, it's significant overbuilding or the zoning is wrong-even if they've got a great tenant: Vivek Chandy, Joint Managing Partner, JSA Advocates &amp; Solicitors
 Watch live 🔴
@@ -4225,72 +4981,72 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F65" t="n">
         <v>1774600322000</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZ3c_WaUAAW60P.jpg', 'type': 'photo', 'id': '2037447221357203456'}]</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>2037446136881910132</t>
         </is>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="P65" s="2" t="n">
         <v>46108.52224537037</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>2037462110511473081</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037462110511473081</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Nikhil Aggarwal, Founder &amp; CEO, @gripinvest on bond market access
 So a ticket size of transaction of bonds, earlier used to be Rs 10 lakh in 2023. Today it is Rs 10,000. So SEBI reduced it by 99% in two years.
@@ -4300,754 +5056,22 @@
 @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F66" t="n">
         <v>1774603796000</v>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>2037407607351292299</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaD1i8bAAAeBtg.jpg', 'type': 'photo', 'id': '2037460837368266752'}]</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2037447541843972418</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46108.5624537037</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2037463827743453367</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037463827743453367</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Where human element becomes relevant is more about the human psychology. How do you ensure  the client holds the portfolio and doesn't give up to the volatility we see in the market? Like for example, what we have seen over the last few months or so: Dipak Daga of Jio Financial Services.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1774604205000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaGV_saAAIJp8X.jpg', 'type': 'photo', 'id': '2037463593864790018'}]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2037462110511473081</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46108.5671875</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2037464683402432711</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037464683402432711</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Vineet Malhotra, Co-founder and CEO, Compoundexpress says India is hybrid. We like to take the best of everything and bring it here. So we've got all types of models.  So tier 2 city MFDs today have one very important thing which nobody has and that is the client's trust. And anybody who can enable that trust will be a winner. The other thing is products. Their availability of products.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @vamdirect</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1774604409000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaHNXRbsAAwLvf.jpg', 'type': 'photo', 'id': '2037464545086910464'}]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2037463827743453367</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>46108.56954861111</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2037466422683853091</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037466422683853091</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Vineet Malhotra, Co-founder and CEO, Compoundexpress says Bond market is like a vitamin, right? You can't substitute vitamin for a healthy lifestyle.  -So the first fundamental thing is people should follow healthy lifestyle, the right mix of ingredients. And bond should become part of our stable diet. Once that happens, you can infuse things with campaigns, awareness, etc, but the crux of it all, I feel is data and the transparency that you can provide and that can only come through tech.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit | @vamdirect</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1774604824000</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaI4jaa8AAFA6S.jpg', 'type': 'photo', 'id': '2037466386591838208'}]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>1</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2037464683402432711</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>46108.57435185185</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2037467774482633199</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037467774482633199</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | In the last five years, drawdowns have been quite low compared to previous cycles when it used to be 30-40% to not more than 15-17%, which has given comfort to people: Sushant Bhansali, CEO, Ambit Asset Management.
-Watch live 🔴
-https://t.co/dCIYKz2kzi
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1774605146000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaKHdtbsAAmSQy.jpg', 'type': 'photo', 'id': '2037467742270631936'}]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2037466422683853091</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>46108.5780787037</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2037469037345874220</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037469037345874220</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Shravan Sreenivasula, ED &amp; Head, Investment Solutions, @Avendus Wealth Management says Today the toughest part is to build a fixed income investors and people don’t need more than 20-30% of allocation towards fixed income. Most of the risk is being taken in listed equities and private equity and VC funds. So there’s a sizable shift in risk taking, especially among HNI investors.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1774605447000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaK83KagAAlZqA.jpg', 'type': 'photo', 'id': '2037468659636142080'}]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2037467774482633199</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>46108.5815625</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2037474309309128793</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037474309309128793</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Vipul Roongta, Managing Director &amp; CEO, HDFC Capital Advisors on housing demand trends.
-“Residential real estate accounts for nearly 75% of India’s real estate market today. To understand where demand is coming from, it is clear that the market is consolidating towards the top 10–12% of each region. This tapering indicates that demand for capital is significantly higher in these regions.”
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1774606704000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaQAnubwAAFFMR.jpg', 'type': 'photo', 'id': '2037474221769867264'}]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2037469037345874220</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>46108.59611111111</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2037475343511302202</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037475343511302202</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Ankur Gupta, Deputy Global CIO, Head of APAC and Middle East, Real Estate,  @Brookfield: “Real estate investments are about growth, scale, and housing the economy—whether through the residential sector or commercial real estate. To put India in a global context, the sector is worth about $60 trillion globally, while in India it stands at roughly $0.5 trillion. Our fair share of built, rent-producing real estate should be closer to $5 trillion, but we are currently at about a tenth of that. The fact is, we need significant capital to build out real capital infrastructure and push the economy further.”
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1774606951000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaQ8wYa4AA603v.jpg', 'type': 'photo', 'id': '2037475254885605376'}]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2037474309309128793</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46108.59896990741</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2037479577556267383</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037479577556267383</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Vipul Roongta, Managing Director &amp; CEO, HDFC Capital Advisors: Globally, private credit is going through one of its toughest phases, with many funds that were earlier focused on pure equity shifting towards private credit. But in India, the story is different. In the Western world, private credit is often structured with leverage at the asset level or in other ways. In India, however, leverage is not allowed at the fund level, structures are largely unlevered, and investments are senior secured."
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1774607960000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaUOmpawAATY2b.jpg', 'type': 'photo', 'id': '2037478860045074432'}]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2037475343511302202</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>46108.61064814815</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2037481117738311889</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037481117738311889</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | Devarajan Nambakam, managing director, investment banking co-head, India, @GoldmanSachs says It’s safe to say there is almost no pool of capital that is not available in India…today the quantum of capital that is available is higher than we’ve seen.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1774608327000</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaVkrrawAAU6O5.jpg', 'type': 'photo', 'id': '2037480338864390144'}]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2037479577556267383</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>46108.61489583334</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2037483796837380338</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2037482043056251285</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://x.com/livemint/status/2037482043056251285</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>#MintIIS2026 | A lot has changed in a period of time - several new sectors like real estate, EMS coming up, we’ve seen healthcare and Pharma become far deeper. So when you look at the type of deal making which has happened in the last five years it's been very, very distributed: Ashish Jhaveri, Managing Director and Head of India Investment Banking, @Jefferies.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
-@JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1774608548000</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2037407607351292299</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaWy-IakAAnHg8.jpg', 'type': 'photo', 'id': '2037481683847647232'}]</t>
-        </is>
-      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027891, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -5064,63 +5088,60 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>318</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2037481117738311889</t>
+          <t>2037447541843972418</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>46108.6174537037</v>
+        <v>46108.5624537037</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2037483796837380338</t>
+          <t>2037480800703086596</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2037483796837380338</t>
+          <t>2037464657695563894</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://x.com/livemint/status/2037483796837380338</t>
+          <t>https://x.com/harrissayoub/status/2037464657695563894</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>#MintIIS2026 | Alok Malpani, CEO, Emirates NBD Capital India Pvt Ltd: India, predominantly, is family owned. Even the conglomerates are family owned, the decision makers are individuals…for society to accept m&amp;as there has to be behavioural change. The real m&amp;a activity started in 2005 where India went on a shopping spree…Post-Covid the structural behaviour saw a change and we saw evolution in domestic deal making.
-Watch live 🔴
-https://t.co/dCIYKz2SoQ
- @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
+          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1774608966000</v>
+        <v>1774604403000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2037407607351292299</t>
+          <t>2037464657695563894</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaYqRqaQAAK6vz.jpg', 'type': 'photo', 'id': '2037483733494939648'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'Mint', 'screenName': 'livemint', 'followersCount': 2027882, 'favouritesCount': 453, 'friendsCount': 109, 'description': 'Latest in business, finance and stock markets, now on WhatsApp 🔔 Join here: https://t.co/EBclvJNqL8  Download the app for real-time updates'}</t>
+          <t>{'name': 'Harris', 'screenName': 'harrissayoub', 'followersCount': 5, 'favouritesCount': 19, 'friendsCount': 12, 'description': ''}</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -5137,544 +5158,551 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2037482043056251285</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" s="2" t="n">
-        <v>46108.62229166667</v>
+        <v>46108.56947916667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2037480800703086596</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2037465040018940100</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://x.com/harrissayoub/status/2037465040018940100</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Watch them auto-reply to this with a generic support email.</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1774604494000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2037464657695563894</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'Harris', 'screenName': 'harrissayoub', 'followersCount': 5, 'favouritesCount': 19, 'friendsCount': 12, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2037464657695563894</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>46108.57053240741</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2037480800703086596</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2037480800703086596</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>@harrissayoub We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
+social@emiratesnbd.com
+Quoting case #989304 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1774608252000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2037464657695563894</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2037465040018940100</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>46108.61402777778</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>https://x.com/EntAlArabiya/status/2037475105203507641</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>2037475105203507641</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>2037475105203507641</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://x.com/EntAlArabiya/status/2037475105203507641</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>الدولية للأوراق المالية تنضم إلى منصة بنك الإمارات دبي الوطني باي @EmiratesNBD_AE 
 #بنك_الإمارات_دبي_الوطني #الدولية_للأوراق_المالية #فيزا #المدفوعات #الاستثمار  #entalarabiya
 https://t.co/FYrC3lWQ0f</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F70" t="n">
         <v>1774606894000</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>2037475105203507641</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15666, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15665, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
         <v>46108.59831018518</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>https://x.com/EntAlArabiya/status/2037475105203507641</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>2037475105203507641</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>2037518681706750166</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>https://x.com/EntAlArabiya/status/2037518681706750166</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>لجنة التكامل الاقتصادي تتابع مستجدات بيئة الأعمال والاستثمار في الإمارات
 #الإمارات #اقتصاد #الاستثمار #بيئة_الأعمال #شركات #رواد_الأعمال #وزارة_الاقتصاد #أبوظبي #دبي #التنمية_الاقتصادية #القوانين #entalarabiya
 https://t.co/EOd6Ttaxvn</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F71" t="n">
         <v>1774617283000</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>2037518681706750166</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15666, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" s="2" t="n">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15665, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
         <v>46108.71855324074</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2037480800703086596</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2037464657695563894</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/harrissayoub/status/2037464657695563894</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1774604403000</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2037464657695563894</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>{'name': 'Harris', 'screenName': 'harrissayoub', 'followersCount': 5, 'favouritesCount': 19, 'friendsCount': 12, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>46108.56947916667</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2037480800703086596</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2037465040018940100</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://x.com/harrissayoub/status/2037465040018940100</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Watch them auto-reply to this with a generic support email.</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1774604494000</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2037464657695563894</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>{'name': 'Harris', 'screenName': 'harrissayoub', 'followersCount': 5, 'favouritesCount': 19, 'friendsCount': 12, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2037464657695563894</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>46108.57053240741</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2037480800703086596</t>
+          <t>2037466808576266477</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2037480800703086596</t>
+          <t>2037020028265021863</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037020028265021863</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
-        <is>
-          <t>@harrissayoub We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
-social@emiratesnbd.com
-Quoting case #989304 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1774608252000</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2037464657695563894</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2037465040018940100</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="n">
-        <v>46108.61402777778</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2037470129664196764</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2037470129664196764</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Emirates NBD has announced that UAE-based brokerage International Securities is now live on Emirates NBD Pay, enabling fast and secure trading account funding through Visa’s AFT model.
-#EmiratesNBD #Fintech #DigitalPayments #Trading #UAE #Visa #Innovation #Finance https://t.co/RYU0A5fEhv</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1774605707000</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2037470129664196764</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaMRlLWMAALsmR.jpg', 'type': 'photo', 'id': '2037470115097096192'}]</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 10, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>46108.58457175926</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2037470129664196764</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2037471491001143357</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2037471491001143357</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>https://t.co/cKb9N2OlKA, an AI company leveraging synthetic data for smarter financial decision-making, has raised $5.5 million at an $80 million valuation, backed by Carbide Ventures and investor Shukhrat Ibragimov.
-#AI #Fintech #StartupFunding #UAE #Innovation #SyntheticData https://t.co/O4nXkt0aaB</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1774606032000</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2037471491001143357</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaNeatXwAAxu-k.jpg', 'type': 'photo', 'id': '2037471435136942080'}]</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 10, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
-        <v>46108.58833333333</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2037466808576266477</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2037020028265021863</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037020028265021863</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
         <is>
           <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
 livsocialconnect@liv.me
 Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
+      <c r="F72" t="n">
+        <v>1774498395000</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2036904371360063835</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2036904371360063835</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>46107.34253472222</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2037466808576266477</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2037444623359217754</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://x.com/xlcsp/status/2037444623359217754</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE No answer for my email or change on my name</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1774599626000</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2036904371360063835</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{'name': '♥ Gisele ♥', 'screenName': 'xlcsp', 'followersCount': 83, 'favouritesCount': 2660, 'friendsCount': 96, 'description': '!♥ .. sometimes I check it here'}</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2037020028265021863</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>46108.51418981481</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2037466808576266477</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2037466808576266477</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>@xlcsp Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1774604916000</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2036904371360063835</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2037444623359217754</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>46108.57541666667</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2037470129664196764</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2037470129664196764</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Emirates NBD has announced that UAE-based brokerage International Securities is now live on Emirates NBD Pay, enabling fast and secure trading account funding through Visa’s AFT model.
+#EmiratesNBD #Fintech #DigitalPayments #Trading #UAE #Visa #Innovation #Finance https://t.co/RYU0A5fEhv</t>
+        </is>
+      </c>
       <c r="F75" t="n">
-        <v>1774498395000</v>
+        <v>1774605707000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2036904371360063835</t>
+          <t>2037470129664196764</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaMRlLWMAALsmR.jpg', 'type': 'photo', 'id': '2037470115097096192'}]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 10, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -5683,64 +5711,61 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>2036904371360063835</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" s="2" t="n">
-        <v>46107.34253472222</v>
+        <v>46108.58457175926</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+          <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2037466808576266477</t>
+          <t>2037470129664196764</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2037444623359217754</t>
+          <t>2037471491001143357</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://x.com/xlcsp/status/2037444623359217754</t>
+          <t>https://x.com/ForumRemittance/status/2037471491001143357</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE No answer for my email or change on my name</t>
+          <t>https://t.co/cKb9N2OlKA, an AI company leveraging synthetic data for smarter financial decision-making, has raised $5.5 million at an $80 million valuation, backed by Carbide Ventures and investor Shukhrat Ibragimov.
+#AI #Fintech #StartupFunding #UAE #Innovation #SyntheticData https://t.co/O4nXkt0aaB</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1774599626000</v>
+        <v>1774606032000</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2036904371360063835</t>
+          <t>2037471491001143357</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaNeatXwAAxu-k.jpg', 'type': 'photo', 'id': '2037471435136942080'}]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>{'name': '♥ Gisele ♥', 'screenName': 'xlcsp', 'followersCount': 83, 'favouritesCount': 2660, 'friendsCount': 96, 'description': '!♥ .. sometimes I check it here'}</t>
+          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 10, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -5753,122 +5778,118 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>2037020028265021863</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" s="2" t="n">
-        <v>46108.51418981481</v>
+        <v>46108.58833333333</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+          <t>https://x.com/Dharmen86931771/status/2037455548719968567</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2037466808576266477</t>
+          <t>2037455548719968567</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2037466808576266477</t>
+          <t>2037455548719968567</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+          <t>https://x.com/Dharmen86931771/status/2037455548719968567</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
-        <is>
-          <t>@xlcsp Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1774604916000</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2036904371360063835</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>2037444623359217754</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="n">
-        <v>46108.57541666667</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://x.com/Dharmen86931771/status/2037455548719968567</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2037455548719968567</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2037455548719968567</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://x.com/Dharmen86931771/status/2037455548719968567</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Mutual fund 
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
       </c>
+      <c r="F77" t="n">
+        <v>1774602231000</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2037171731865931987</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>{'name': 'Dharmendra', 'screenName': 'Dharmen86931771', 'followersCount': 26, 'favouritesCount': 3896, 'friendsCount': 247, 'description': 'Love UAE'}</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2037171731865931987</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>46108.54434027777</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://x.com/jazrawia15/status/2037427832348082374</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2037427832348082374</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2037427832348082374</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://x.com/jazrawia15/status/2037427832348082374</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE صناديق الاستثمار المشتركة (Mutual Funds)</t>
+        </is>
+      </c>
       <c r="F78" t="n">
-        <v>1774602231000</v>
+        <v>1774595623000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5882,7 +5903,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>{'name': 'Dharmendra', 'screenName': 'Dharmen86931771', 'followersCount': 26, 'favouritesCount': 3896, 'friendsCount': 247, 'description': 'Love UAE'}</t>
+          <t>{'name': 'مريم ❤ MBZ', 'screenName': 'jazrawia15', 'followersCount': 1799, 'favouritesCount': 2251, 'friendsCount': 628, 'description': 'ﻋﻨﺪﻣﺎ ﻻ\u200c ﺗﻌﺮﻑ ﻣﺎ اﻗﺼﺪه ﻻ\u200c ﺗﻔﺴﺮ ﻣﺎ ﺗﺮﻳﺪه ... جزراوية حتى النخاع ... player 🏐⚽️'}</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -5899,7 +5920,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -5908,51 +5929,51 @@
         </is>
       </c>
       <c r="P78" s="2" t="n">
-        <v>46108.54434027777</v>
+        <v>46108.4678587963</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://x.com/jazrawia15/status/2037427832348082374</t>
+          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2037427832348082374</t>
+          <t>2037414318078120348</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2037427832348082374</t>
+          <t>2037414318078120348</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://x.com/jazrawia15/status/2037427832348082374</t>
+          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE صناديق الاستثمار المشتركة (Mutual Funds)</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting https://t.co/w2yAiSn6ht or the App https://t.co/MNACzihONn</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1774595623000</v>
+        <v>1774592401000</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2037171731865931987</t>
+          <t>2037414318078120348</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZZhqNXcAA4hLq.jpg', 'type': 'photo', 'id': '2037414316232634368'}]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>{'name': 'مريم ❤ MBZ', 'screenName': 'jazrawia15', 'followersCount': 1799, 'favouritesCount': 2251, 'friendsCount': 628, 'description': 'ﻋﻨﺪﻣﺎ ﻻ\u200c ﺗﻌﺮﻑ ﻣﺎ اﻗﺼﺪه ﻻ\u200c ﺗﻔﺴﺮ ﻣﺎ ﺗﺮﻳﺪه ... جزراوية حتى النخاع ... player 🏐⚽️'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18779, 'favouritesCount': 2502, 'friendsCount': 1474, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -5969,178 +5990,102 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>2037171731865931987</t>
-        </is>
-      </c>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" s="2" t="n">
-        <v>46108.4678587963</v>
+        <v>46108.43056712963</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
+          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2037427668879286533</t>
+          <t>2037414318078120348</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2037171768117314043</t>
+          <t>2037515075234267398</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037171768117314043</t>
+          <t>https://x.com/NovoCinemas/status/2037515075234267398</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>الأمر كله يتعلق بعدم وضع كل البيض في سلة واحدة.
-هل يمكنك تخمين نوع الاستثمار؟ اكتب إجابتك في التعليقات أدناه.
-#لغز_الأسبوع_ENBD #العافية_المالية #استثمر_بذكاء #أساسيات_المال https://t.co/vTM1HJze72</t>
+          <t>Yeh kahani seedha dil pe lagegi 🔥The Urdu drama #AagLagayBastiMein brings raw emotions, strong relationships and moments that feel real. No drama for the sake of it… bas sachai. Now Playing at Novo Cinemas. Book your tickets 🎟️ on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/yuyHcap5gY</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1774534572000</v>
+        <v>1774616423000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2037171768117314043</t>
+          <t>2037515075234267398</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEV87XMWgAANwm8.jpg', 'type': 'photo', 'id': '2037171765734965248'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEa1Kb2XEAA7jhI.jpg', 'type': 'photo', 'id': '2037515072310808576'}]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174034, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18779, 'favouritesCount': 2502, 'friendsCount': 1474, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>55</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" s="2" t="n">
-        <v>46107.76125</v>
+        <v>46108.70859953704</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
+          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2037427668879286533</t>
+          <t>2037394759174799528</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2037427668879286533</t>
+          <t>2037394759174799528</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
+          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE صناديق الاستثمار المشتركة (Mutual Funds)</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1774595584000</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2037171768117314043</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>{'name': 'مريم ❤ MBZ', 'screenName': 'jazrawia15', 'followersCount': 1799, 'favouritesCount': 2251, 'friendsCount': 628, 'description': 'ﻋﻨﺪﻣﺎ ﻻ\u200c ﺗﻌﺮﻑ ﻣﺎ اﻗﺼﺪه ﻻ\u200c ﺗﻔﺴﺮ ﻣﺎ ﺗﺮﻳﺪه ... جزراوية حتى النخاع ... player 🏐⚽️'}</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>2037171768117314043</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="n">
-        <v>46108.46740740741</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2037394759174799528</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2037394759174799528</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
         <is>
           <t>Great to see UAE banks like Emirates NBD waiving ATM fees due to current situation.
 ​But honestly, where are the money transfer apps?
@@ -6148,8 +6093,74 @@
 @dutweets @Botim_Official @remitly @remitlysupport @eandmoney</t>
         </is>
       </c>
+      <c r="F81" t="n">
+        <v>1774587738000</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2037394759174799528</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>{'name': 'Raja Tahoor Ahmad', 'screenName': 'Tahoor500', 'followersCount': 8225, 'favouritesCount': 99997, 'friendsCount': 8127, 'description': 'There is none worthy of worship except God (Allah) and Muhammad (SAW) is the messenger of God.'}</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" s="2" t="n">
+        <v>46108.37659722222</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2037394759174799528</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2037406913911210191</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://x.com/Botim_Official/status/2037406913911210191</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>@Tahoor500 Our team hears the community's voice. Support and reliability are at the core of what we strive for every day. We appreciate this perspective as we continue to look for ways to best serve our users and the community 💙</t>
+        </is>
+      </c>
       <c r="F82" t="n">
-        <v>1774587738000</v>
+        <v>1774590636000</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -6163,11 +6174,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>{'name': 'Raja Tahoor Ahmad', 'screenName': 'Tahoor500', 'followersCount': 8225, 'favouritesCount': 100003, 'friendsCount': 8127, 'description': 'There is none worthy of worship except God (Allah) and Muhammad (SAW) is the messenger of God.'}</t>
+          <t>{'name': 'botim', 'screenName': 'Botim_Official', 'followersCount': 946, 'favouritesCount': 21, 'friendsCount': 1, 'description': 'simplified by design.'}</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -6180,12 +6191,16 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2037394759174799528</t>
+        </is>
+      </c>
       <c r="P82" s="2" t="n">
-        <v>46108.37659722222</v>
+        <v>46108.41013888889</v>
       </c>
     </row>
     <row r="83">
@@ -6201,39 +6216,39 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2037406913911210191</t>
+          <t>2037381565576040908</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://x.com/Botim_Official/status/2037406913911210191</t>
+          <t>https://x.com/Tahoor500/status/2037381565576040908</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>@Tahoor500 Our team hears the community's voice. Support and reliability are at the core of what we strive for every day. We appreciate this perspective as we continue to look for ways to best serve our users and the community 💙</t>
+          <t>Good morning! The weather in Sharjah, UAE looks lovely after the rain  🇦🇪 🌥️ https://t.co/9C4tnXBQe1</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1774590636000</v>
+        <v>1774584592000</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2037394759174799528</t>
+          <t>2037381565576040908</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEY7qbpbsAAFHhi.jpg', 'type': 'photo', 'id': '2037381481593810944'}]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>{'name': 'botim', 'screenName': 'Botim_Official', 'followersCount': 946, 'favouritesCount': 21, 'friendsCount': 1, 'description': 'simplified by design.'}</t>
+          <t>{'name': 'Raja Tahoor Ahmad', 'screenName': 'Tahoor500', 'followersCount': 8225, 'favouritesCount': 99997, 'friendsCount': 8127, 'description': 'There is none worthy of worship except God (Allah) and Muhammad (SAW) is the messenger of God.'}</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -6242,130 +6257,128 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2037394759174799528</t>
-        </is>
-      </c>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" s="2" t="n">
-        <v>46108.41013888889</v>
+        <v>46108.34018518519</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://x.com/Tahoor500/status/2037394759174799528</t>
+          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2037394759174799528</t>
+          <t>2037427668879286533</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2037381565576040908</t>
+          <t>2037171768117314043</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://x.com/Tahoor500/status/2037381565576040908</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037171768117314043</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Good morning! The weather in Sharjah, UAE looks lovely after the rain  🇦🇪 🌥️ https://t.co/9C4tnXBQe1</t>
+          <t>الأمر كله يتعلق بعدم وضع كل البيض في سلة واحدة.
+هل يمكنك تخمين نوع الاستثمار؟ اكتب إجابتك في التعليقات أدناه.
+#لغز_الأسبوع_ENBD #العافية_المالية #استثمر_بذكاء #أساسيات_المال https://t.co/vTM1HJze72</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1774584592000</v>
+        <v>1774534572000</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2037381565576040908</t>
+          <t>2037171768117314043</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEY7qbpbsAAFHhi.jpg', 'type': 'photo', 'id': '2037381481593810944'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEV87XMWgAANwm8.jpg', 'type': 'photo', 'id': '2037171765734965248'}]</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>{'name': 'Raja Tahoor Ahmad', 'screenName': 'Tahoor500', 'followersCount': 8225, 'favouritesCount': 100003, 'friendsCount': 8127, 'description': 'There is none worthy of worship except God (Allah) and Muhammad (SAW) is the messenger of God.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174038, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" t="n">
         <v>4</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>668</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" s="2" t="n">
-        <v>46108.34018518519</v>
+        <v>46107.76125</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
+          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2037414318078120348</t>
+          <t>2037427668879286533</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2037414318078120348</t>
+          <t>2037427668879286533</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
+          <t>https://x.com/jazrawia15/status/2037427668879286533</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting https://t.co/w2yAiSn6ht or the App https://t.co/MNACzihONn</t>
+          <t>@EmiratesNBD_AE صناديق الاستثمار المشتركة (Mutual Funds)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1774592401000</v>
+        <v>1774595584000</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2037414318078120348</t>
+          <t>2037171768117314043</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZZhqNXcAA4hLq.jpg', 'type': 'photo', 'id': '2037414316232634368'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18779, 'favouritesCount': 2502, 'friendsCount': 1474, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
+          <t>{'name': 'مريم ❤ MBZ', 'screenName': 'jazrawia15', 'followersCount': 1799, 'favouritesCount': 2251, 'friendsCount': 628, 'description': 'ﻋﻨﺪﻣﺎ ﻻ\u200c ﺗﻌﺮﻑ ﻣﺎ اﻗﺼﺪه ﻻ\u200c ﺗﻔﺴﺮ ﻣﺎ ﺗﺮﻳﺪه ... جزراوية حتى النخاع ... player 🏐⚽️'}</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -6382,174 +6395,40 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2037171768117314043</t>
+        </is>
+      </c>
       <c r="P85" s="2" t="n">
-        <v>46108.43056712963</v>
+        <v>46108.46740740741</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
+          <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2037414318078120348</t>
+          <t>2037369717959324018</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2037515075234267398</t>
+          <t>2037369704864702582</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2037515075234267398</t>
+          <t>https://x.com/wownews24x7/status/2037369704864702582</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
-        <is>
-          <t>Yeh kahani seedha dil pe lagegi 🔥The Urdu drama #AagLagayBastiMein brings raw emotions, strong relationships and moments that feel real. No drama for the sake of it… bas sachai. Now Playing at Novo Cinemas. Book your tickets 🎟️ on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/yuyHcap5gY</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1774616423000</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2037515075234267398</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEa1Kb2XEAA7jhI.jpg', 'type': 'photo', 'id': '2037515072310808576'}]</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18779, 'favouritesCount': 2502, 'friendsCount': 1474, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>46108.70859953704</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>https://x.com/marcelraj/status/2037384139725488443</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2037384139725488443</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2037384139725488443</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://x.com/marcelraj/status/2037384139725488443</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Mutual fund 
-#ENBDRiddleOfTheWeek 
-#financialwellbeing</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1774585206000</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2037171731865931987</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>{'name': 'Marcel Raj', 'screenName': 'marcelraj', 'followersCount': 278, 'favouritesCount': 6289, 'friendsCount': 493, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>2037171731865931987</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>46108.34729166667</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://x.com/wownews24x7/status/2037369717959324018</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2037369717959324018</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2037369704864702582</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://x.com/wownews24x7/status/2037369704864702582</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
         <is>
           <t>🌅 Good Morning, Markets!
 📆 27th March | ⏰ 06:40 AM IST
@@ -6559,68 +6438,68 @@
 #WOWNEWS24x7 #FromFOMOtoFMA https://t.co/TmnAR3J8EH</t>
         </is>
       </c>
-      <c r="F88" t="n">
+      <c r="F86" t="n">
         <v>1774581764000</v>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>2037369704864702582</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEYw8bebUAAWcmN.jpg', 'type': 'photo', 'id': '2037369696157388800'}]</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
         </is>
       </c>
-      <c r="J88" t="n">
+      <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" s="2" t="n">
         <v>46108.3074537037</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>2037369709453320618</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369709453320618</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>🌍 Global Futures
 ‣ US: Nasdaq +0.22%, Dow +0.29%, S&amp;amp;P +0.28%
@@ -6630,72 +6509,72 @@
 #GlobalMarkets #WOWNEWS24x7</t>
         </is>
       </c>
-      <c r="F89" t="n">
+      <c r="F87" t="n">
         <v>1774581765000</v>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>2037369704864702582</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
         </is>
       </c>
-      <c r="J89" t="n">
+      <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr">
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>2037369704864702582</t>
         </is>
       </c>
-      <c r="P89" s="2" t="n">
+      <c r="P87" s="2" t="n">
         <v>46108.30746527778</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>2037369713668550879</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369713668550879</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>💸 Money Flow
 ‣ FIIs: Net Sell ₹ 1,805.37 Cr
@@ -6703,72 +6582,72 @@
 #FIIs #DIIs #MarketFlow #WOWNEWS24x7</t>
         </is>
       </c>
-      <c r="F90" t="n">
+      <c r="F88" t="n">
         <v>1774581766000</v>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>2037369704864702582</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
         </is>
       </c>
-      <c r="J90" t="n">
+      <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
         <is>
           <t>2037369709453320618</t>
         </is>
       </c>
-      <c r="P90" s="2" t="n">
+      <c r="P88" s="2" t="n">
         <v>46108.30747685185</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>✅ Positives
 ‣ Infosys to acquire Stratus &amp;amp; Optimum Healthcare IT
@@ -6777,72 +6656,72 @@
 #StocksToWatch #WOWNEWS24x7</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F89" t="n">
         <v>1774581767000</v>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>2037369704864702582</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
         </is>
       </c>
-      <c r="J91" t="n">
+      <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
         <v>1</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M89" t="n">
         <v>1</v>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
         <is>
           <t>2037369713668550879</t>
         </is>
       </c>
-      <c r="P91" s="2" t="n">
+      <c r="P89" s="2" t="n">
         <v>46108.30748842593</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>2037369722308813190</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369722308813190</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>❌ Negatives
 ‣ Mphasis gets ₹22.87 bn tax demand
@@ -6851,12 +6730,154 @@
 #MarketWatch #WOWNEWS24x7</t>
         </is>
       </c>
+      <c r="F90" t="n">
+        <v>1774581768000</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2037369704864702582</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2037369717959324018</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>46108.3075</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://x.com/marcelraj/status/2037384139725488443</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2037384139725488443</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2037384139725488443</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://x.com/marcelraj/status/2037384139725488443</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Mutual fund 
+#ENBDRiddleOfTheWeek 
+#financialwellbeing</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1774585206000</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2037171731865931987</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>{'name': 'Marcel Raj', 'screenName': 'marcelraj', 'followersCount': 278, 'favouritesCount': 6289, 'friendsCount': 493, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2037171731865931987</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>46108.34729166667</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://x.com/babanasseralgh/status/2037319416560402505</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2037319416560402505</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2037319416560402505</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://x.com/babanasseralgh/status/2037319416560402505</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ممكن تردون خاص</t>
+        </is>
+      </c>
       <c r="F92" t="n">
-        <v>1774581768000</v>
+        <v>1774569775000</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2037369704864702582</t>
+          <t>2037319416560402505</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6866,11 +6887,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>{'name': 'WOWNEWS24x7', 'screenName': 'wownews24x7', 'followersCount': 86, 'favouritesCount': 11, 'friendsCount': 1, 'description': 'Fastest Updates | Verified Stories 🚀 https://t.co/ztV0XwvKR0'}</t>
+          <t>{'name': 'لفقيدي والدي', 'screenName': 'babanasseralgh', 'followersCount': 9, 'favouritesCount': 26, 'friendsCount': 59, 'description': 'لقد بُتر أعظم جناح كنت أملكه . ابوي حبيبي في ذمة الله .. 8 رمضان ١٤٤٤ هـ الخميس 🇸🇦30/3/2023'}</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -6883,16 +6904,12 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>2037369717959324018</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
       <c r="P92" s="2" t="n">
-        <v>46108.3075</v>
+        <v>46108.16869212963</v>
       </c>
     </row>
     <row r="93">
@@ -6956,7 +6973,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="O93" t="inlineStr"/>
@@ -7096,7 +7113,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7240,7 +7257,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7384,7 +7401,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7456,7 +7473,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7528,7 +7545,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7672,7 +7689,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7816,7 +7833,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -7888,7 +7905,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -7960,7 +7977,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8320,7 +8337,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8335,35 +8352,36 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://x.com/babanasseralgh/status/2037319416560402505</t>
+          <t>https://x.com/BusinessTiding/status/2037351848236155236</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2037319416560402505</t>
+          <t>2037351848236155236</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2037319416560402505</t>
+          <t>2037351848236155236</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://x.com/babanasseralgh/status/2037319416560402505</t>
+          <t>https://x.com/BusinessTiding/status/2037351848236155236</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ممكن تردون خاص</t>
+          <t>#IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs. 30 lakh to Rs. 15 Crores
+#RBLBank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1774569775000</v>
+        <v>1774577507000</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2037319416560402505</t>
+          <t>2037351848236155236</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8373,7 +8391,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>{'name': 'لفقيدي والدي', 'screenName': 'babanasseralgh', 'followersCount': 9, 'favouritesCount': 26, 'friendsCount': 59, 'description': 'لقد بُتر أعظم جناح كنت أملكه . ابوي حبيبي في ذمة الله .. 8 رمضان ١٤٤٤ هـ الخميس 🇸🇦30/3/2023'}</t>
+          <t>{'name': 'BUSINESS TIDING', 'screenName': 'BusinessTiding', 'followersCount': 527, 'favouritesCount': 368, 'friendsCount': 579, 'description': 'STOCK MARKET NEWS, NOT SEBI REGISTERED..'}</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -8383,19 +8401,19 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>77</t>
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" s="2" t="n">
-        <v>46108.16869212963</v>
+        <v>46108.25818287037</v>
       </c>
     </row>
     <row r="114">
@@ -8411,26 +8429,26 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2037351848236155236</t>
+          <t>2037353184042324120</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://x.com/BusinessTiding/status/2037351848236155236</t>
+          <t>https://x.com/BusinessTiding/status/2037353184042324120</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>#IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs. 30 lakh to Rs. 15 Crores
-#RBLBank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank</t>
+          <t>#AzadEngineering: The company has signed an 8-year pact with Mitsubishi Heavy Industries, Japan, to be a single-source supplier for gas turbine parts
+#InterGlobe Aviation: The company has received a GST demand order seeking a penalty of Rs. 42.9 crore</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1774577507000</v>
+        <v>1774577825000</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2037351848236155236</t>
+          <t>2037353184042324120</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8440,7 +8458,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>{'name': 'BUSINESS TIDING', 'screenName': 'BusinessTiding', 'followersCount': 529, 'favouritesCount': 368, 'friendsCount': 579, 'description': 'STOCK MARKET NEWS, NOT SEBI REGISTERED..'}</t>
+          <t>{'name': 'BUSINESS TIDING', 'screenName': 'BusinessTiding', 'followersCount': 527, 'favouritesCount': 368, 'friendsCount': 579, 'description': 'STOCK MARKET NEWS, NOT SEBI REGISTERED..'}</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -8450,178 +8468,111 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
         <v>1</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>58</t>
         </is>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" s="2" t="n">
-        <v>46108.25818287037</v>
+        <v>46108.26186342593</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://x.com/BusinessTiding/status/2037351848236155236</t>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2037351848236155236</t>
+          <t>2037485522399236349</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2037353184042324120</t>
+          <t>2036821858868416788</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://x.com/BusinessTiding/status/2037353184042324120</t>
+          <t>https://x.com/abuzubayr1987/status/2036821858868416788</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
-        <is>
-          <t>#AzadEngineering: The company has signed an 8-year pact with Mitsubishi Heavy Industries, Japan, to be a single-source supplier for gas turbine parts
-#InterGlobe Aviation: The company has received a GST demand order seeking a penalty of Rs. 42.9 crore</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>1774577825000</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>2037353184042324120</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>{'name': 'BUSINESS TIDING', 'screenName': 'BusinessTiding', 'followersCount': 529, 'favouritesCount': 368, 'friendsCount': 579, 'description': 'STOCK MARKET NEWS, NOT SEBI REGISTERED..'}</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>0</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>1</v>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" s="2" t="n">
-        <v>46108.26186342593</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2036821858868416788</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
         <is>
           <t>@centralbankuae 
 I am left in a precarious situation having no living expenses for the coming weeks after @emiratesislamic bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
 @JamalIslamic</t>
         </is>
       </c>
-      <c r="F116" t="n">
+      <c r="F115" t="n">
         <v>1774451148000</v>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>2036821858868416788</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
         </is>
       </c>
-      <c r="J116" t="n">
+      <c r="J115" t="n">
         <v>2</v>
       </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="inlineStr">
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" s="2" t="n">
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" s="2" t="n">
         <v>46106.79569444444</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>2036879879950786787</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>https://x.com/centralbankuae/status/2036879879950786787</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>Dear Consumer
 Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
@@ -8630,80 +8581,151 @@
 Central Bank of the UAE</t>
         </is>
       </c>
-      <c r="F117" t="n">
+      <c r="F116" t="n">
         <v>1774464981000</v>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>2036821858868416788</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>{'name': 'Central Bank of the UAE', 'screenName': 'centralbankuae', 'followersCount': 6336, 'favouritesCount': 383, 'friendsCount': 210, 'description': 'الحساب الرسمي لمصرف الإمارات العربية المتحدة المركزي The official account of the Central Bank of the UAE'}</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>{'name': 'Central Bank of the UAE', 'screenName': 'centralbankuae', 'followersCount': 6337, 'favouritesCount': 383, 'friendsCount': 210, 'description': 'الحساب الرسمي لمصرف الإمارات العربية المتحدة المركزي The official account of the Central Bank of the UAE'}</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="inlineStr">
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>2036821858868416788</t>
         </is>
       </c>
-      <c r="P117" s="2" t="n">
+      <c r="P116" s="2" t="n">
         <v>46106.95579861111</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>2037094634342744234</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987/status/2037094634342744234</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>@centralbankuae @emiratesislamic @JamalIslamic @SanadakUAE I was expecting a call back from the account manager of @emiratesislamic , got no calls or messages.
 Amazing, how without a notice an unfair 100% deduction is done leaving my family in lurch. I have been a customer since 2016!!!
 @JamalIslamic</t>
         </is>
       </c>
+      <c r="F117" t="n">
+        <v>1774516182000</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2036821858868416788</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2036879879950786787</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>46107.54840277778</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2037144761212023024</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037144761212023024</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>@abuzubayr1987 Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
+        </is>
+      </c>
       <c r="F118" t="n">
-        <v>1774516182000</v>
+        <v>1774528134000</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -8717,11 +8739,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -8734,253 +8756,328 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>2036879879950786787</t>
+          <t>2037094634342744234</t>
         </is>
       </c>
       <c r="P118" s="2" t="n">
-        <v>46107.54840277778</v>
+        <v>46107.68673611111</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>@emiratesislamic All I got was a feedback form!
+No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
+@SanadakUAE @JamalIslamic</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1774609377000</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2036821858868416788</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2037144761212023024</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>46108.62704861111</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2037499728318116157</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>@abuzubayr1987 @emiratesislamic @JamalIslamic Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website https://t.co/adEqqBw2GF.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1774612764000</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2036821858868416788</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>{'name': 'Sanadak', 'screenName': 'SanadakUAE', 'followersCount': 355, 'favouritesCount': 39, 'friendsCount': 36, 'description': 'الحساب الرسمي لوحدة "سندك" لتسوية المنازعات المصرفية والتأمينية The official account of the “Sanadak” Ombudsman Unit'}</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>46108.66625</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>2037484085459750931</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2037480161797722518</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1774608099000</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2036821858868416788</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
         <is>
           <t>2037144761212023024</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037144761212023024</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
+      <c r="P121" s="2" t="n">
+        <v>46108.61225694444</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2037484085459750931</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2037484085459750931</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
         <is>
           <t>@abuzubayr1987 Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="F119" t="n">
-        <v>1774528134000</v>
-      </c>
-      <c r="G119" t="inlineStr">
+      <c r="F122" t="n">
+        <v>1774609035000</v>
+      </c>
+      <c r="G122" t="inlineStr">
         <is>
           <t>2036821858868416788</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18453, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>2</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>2037094634342744234</t>
-        </is>
-      </c>
-      <c r="P119" s="2" t="n">
-        <v>46107.68673611111</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
         <is>
           <t>2037480161797722518</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>@emiratesislamic Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>1774608099000</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>1</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>2037144761212023024</t>
-        </is>
-      </c>
-      <c r="P120" s="2" t="n">
-        <v>46108.61225694444</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2037484085459750931</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>@abuzubayr1987 Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
-better please check your private message.</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>1774609035000</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18453, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>2037480161797722518</t>
-        </is>
-      </c>
-      <c r="P121" s="2" t="n">
+      <c r="P122" s="2" t="n">
         <v>46108.62309027778</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -8988,68 +9085,68 @@
 Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security. https://t.co/2qlWHXI9sD</t>
         </is>
       </c>
-      <c r="F122" t="n">
+      <c r="F123" t="n">
         <v>1774603827000</v>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEaFHIMWYAA9vs0.jpg', 'type': 'photo', 'id': '2037462238936588288'}]</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18453, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
         <v>1</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M123" t="n">
         <v>2</v>
       </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" s="2" t="n">
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" s="2" t="n">
         <v>46108.5628125</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>2037079016033681601</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037079016033681601</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>Small choices can make a big difference.
 Staying aware of your spending helps you stay in control — today and tomorrow.
@@ -9058,190 +9155,44 @@
 https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
         </is>
       </c>
-      <c r="F123" t="n">
+      <c r="F124" t="n">
         <v>1774512459000</v>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>2037079016033681601</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEUokXgXwAAZ2ai.jpg', 'type': 'video', 'id': '2037078979572588544'}]</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18453, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
         <v>1</v>
       </c>
-      <c r="M123" t="n">
+      <c r="M124" t="n">
         <v>5</v>
       </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" s="2" t="n">
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" s="2" t="n">
         <v>46107.5053125</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2037485522399236349</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>2037485522399236349</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>@emiratesislamic All I got was a feedback form!
-No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
-@SanadakUAE @JamalIslamic</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>1774609377000</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>{'name': 'Safwan', 'screenName': 'abuzubayr1987', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 63, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J124" t="n">
-        <v>1</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>2037144761212023024</t>
-        </is>
-      </c>
-      <c r="P124" s="2" t="n">
-        <v>46108.62704861111</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2037485522399236349</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>2037499728318116157</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>@abuzubayr1987 @emiratesislamic @JamalIslamic Dear Safwan,
-Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
-For more information about our services, please call 800SANADAK or visit our website https://t.co/adEqqBw2GF.  
-Best regards,
-Sanadak Team</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>1774612764000</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>{'name': 'Sanadak', 'screenName': 'SanadakUAE', 'followersCount': 355, 'favouritesCount': 39, 'friendsCount': 36, 'description': 'الحساب الرسمي لوحدة "سندك" لتسوية المنازعات المصرفية والتأمينية The official account of the “Sanadak” Ombudsman Unit'}</t>
-        </is>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>2037485522399236349</t>
-        </is>
-      </c>
-      <c r="P125" s="2" t="n">
-        <v>46108.66625</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,301 +517,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1774707097000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
-        <v>46109.75806712963</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2037955706662604958</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2037955706662604958</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1774721478000</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2037895388909142325</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46109.92451388889</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F2" t="n">
         <v>1774684800000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" s="2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
         <v>46109.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>2037911596106715381</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F3" t="n">
         <v>1774710961000</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>46109.80278935185</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>2037921044221010067</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -832,8 +694,148 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>1774713214000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2037911596106715381</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46109.82886574074</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1774714924000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>46109.8486574074</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>1774713214000</v>
+        <v>1774716905000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -851,7 +853,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -864,120 +866,118 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2037911596106715381</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46109.82886574074</v>
+        <v>46109.87158564815</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1774714924000</v>
+        <v>1774707097000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46109.8486574074</v>
+        <v>46109.75806712963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1774716905000</v>
+        <v>1774721478000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2037801868244533349</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,33 +987,33 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037895388909142325</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46109.87158564815</v>
+        <v>46109.92451388889</v>
       </c>
     </row>
     <row r="9">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1297,187 +1297,183 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2037804608517509572</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2037804608517509572</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1774685453000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2037804608517509572</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="2" t="n">
+        <v>46109.50755787037</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2037804608517509572</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2037855319393464474</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/eazyislit/status/2037855319393464474</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1774697544000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2037855319393464474</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="n">
+        <v>46109.6475</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2037827252075839770</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2037818020597215557</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>1774688651000</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2037818020597215557</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" s="2" t="n">
-        <v>46109.54457175926</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2037827252075839770</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2037827252075839770</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1774690852000</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17237, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46109.5700462963</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2037804608517509572</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2037804608517509572</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1774685453000</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2037804608517509572</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -1489,46 +1485,46 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>46109.50755787037</v>
+        <v>46109.54457175926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037855319393464474</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
+          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1774697544000</v>
+        <v>1774690852000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1538,7 +1534,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1555,12 +1551,16 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2037818020597215557</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>46109.6475</v>
+        <v>46109.5700462963</v>
       </c>
     </row>
     <row r="17">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111379, 'favouritesCount': 302129, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>430</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1645,60 +1645,57 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2038052874803118423</t>
+          <t>2038054346693435744</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/argosaki/status/2038052874803118423</t>
+          <t>https://x.com/argosaki/status/2038054346693435744</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>This picture of Donald Trump and John F. Kennedy Jr was at a New York Knicks game at Madison Square Garden on March 31, 1999
-March 31, 1999 - July 16, 1999 
-was exactly 107 days.  
-Everything always lines up so perfectly‼️‼️‼️ https://t.co/VdFCGIRBKl</t>
+          <t>.👇♥️🙏 https://t.co/k2P5WezRfZ</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1774744645000</v>
+        <v>1774744996000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2038052874803118423</t>
+          <t>2038054346693435744</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEieSZEakAAXfdV.jpg', 'type': 'photo', 'id': '2038052870189387776'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEifoD5b0AEmFq5.jpg', 'type': 'photo', 'id': '2038054341974937601'}]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111379, 'favouritesCount': 302129, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>677</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>46110.19265046297</v>
+        <v>46110.19671296296</v>
       </c>
     </row>
     <row r="19">
@@ -1761,7 +1758,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>525</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1772,12 +1769,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1829,7 +1826,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1844,12 +1841,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1899,7 +1896,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1914,12 +1911,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1969,7 +1966,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2031,7 +2028,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193209, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193214, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2048,7 +2045,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2114,7 +2111,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2129,172 +2126,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2037789707321622955</t>
+          <t>2037790087141101872</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>اجعل مفاجآت العيد أكثر قيمة.
-من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
-شاهد هذه الحلقة وأخبرنا:
-كيف يمكنك شراء الذهب والفضه من البنك؟
-للمشاركة:
-تابع حساب بنك الإمارات دبي الوطني 
-قم بالإشارة إلى 3 من أصدقائك
-اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1773832234000</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>91</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>39</v>
-      </c>
-      <c r="M25" t="n">
-        <v>50</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>46099.63233796296</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2037789707321622955</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2037789707321622955</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
-Tagging 
-@FazilAnas 
-@Emy191990 
-@Bushrasabih2</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1774681901000</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>46109.46644675926</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2037790087141101872</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2031673422921564269</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2321,68 +2171,68 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F25" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J25" t="n">
         <v>128</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>40</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M25" t="n">
         <v>53</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2342</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
         <v>46092.58871527778</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -2390,12 +2240,159 @@
 @Amanekhattab1</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>1774681991000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2031673422921564269</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>46109.46748842593</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1773832234000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>91</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>39</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2638</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>46099.63233796296</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+@FazilAnas 
+@Emy191990 
+@Bushrasabih2</t>
+        </is>
+      </c>
       <c r="F28" t="n">
-        <v>1774681991000</v>
+        <v>1774681901000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2422,16 +2419,16 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46109.46748842593</v>
+        <v>46109.46644675926</v>
       </c>
     </row>
     <row r="29">
@@ -2499,7 +2496,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2569,7 +2566,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2643,7 +2640,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2658,375 +2655,95 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>حل اللغز واربح 10,000 درهم.💰
-أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
-تابع @EmiratesNBD_ae
-قم بالإشارة إلى 3 من أصدقائك
-حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1771662146000</v>
+        <v>1774680795000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>857</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9395</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n">
-        <v>46074.5155787037</v>
+        <v>46109.45364583333</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037784498885243377</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1774680744000</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46109.45305555555</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2037785071189671937</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2037785071189671937</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1774680795000</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>46109.45364583333</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1774680699000</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>46109.45253472222</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1774680722000</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2025123939970584932</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>46109.45280092592</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2037784498885243377</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2027634643315404863</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2027634643315404863</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -3037,68 +2754,68 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F33" t="n">
         <v>1772260745000</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2027634643315404863</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634528185901056/img/L9yGlrO1upMqeKpB.jpg', 'type': 'video', 'id': '2027634528185901056'}]</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J33" t="n">
         <v>366</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K33" t="n">
         <v>2</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L33" t="n">
         <v>154</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M33" t="n">
         <v>183</v>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="2" t="n">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>10504</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
         <v>46081.44380787037</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2037784498885243377</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>2027634776555872373</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2027634776555872373</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Solve this Ramadan riddle and win AED 10,000.
 From food distribution to supporting workers and spending time with senior citizens, one program brings it all together.
@@ -3109,79 +2826,359 @@
 3.Drop your answer below https://t.co/PDRSppGlrJ</t>
         </is>
       </c>
+      <c r="F34" t="n">
+        <v>1772260777000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>38</v>
+      </c>
+      <c r="M34" t="n">
+        <v>46</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46081.44417824074</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1774680659000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2027634643315404863</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2027634776555872373</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46109.45207175926</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>حل اللغز واربح 10,000 درهم.💰
+أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
+تابع @EmiratesNBD_ae
+قم بالإشارة إلى 3 من أصدقائك
+حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1771662146000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>857</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>183</v>
+      </c>
+      <c r="M36" t="n">
+        <v>191</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>9397</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>46074.5155787037</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1774680699000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46109.45253472222</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="F38" t="n">
-        <v>1772260777000</v>
+        <v>1774680722000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2027634660532973568/img/NcwS9qq5kEQQ1U9q.jpg', 'type': 'video', 'id': '2027634660532973568'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46081.44417824074</v>
+        <v>46109.45280092592</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2037784498885243377</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2037784498885243377</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1774680659000</v>
+        <v>1774680637000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3195,7 +3192,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3221,37 +3218,37 @@
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46109.45207175926</v>
+        <v>46109.45181712963</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1774680637000</v>
+        <v>1774680620000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3265,7 +3262,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3282,7 +3279,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3291,37 +3288,37 @@
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46109.45181712963</v>
+        <v>46109.45162037037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1774680620000</v>
+        <v>1774680594000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3335,7 +3332,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3352,7 +3349,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3361,37 +3358,38 @@
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46109.45162037037</v>
+        <v>46109.45131944444</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2037784141006344295</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2037784141006344295</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1774680574000</v>
+        <v>1774680549000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3405,7 +3403,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3431,41 +3429,41 @@
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46109.45108796296</v>
+        <v>46109.45079861111</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1774680594000</v>
+        <v>1774680507000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3475,7 +3473,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3492,51 +3490,51 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46109.45131944444</v>
+        <v>46109.4503125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1774680549000</v>
+        <v>1774680462000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3546,7 +3544,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3563,46 +3561,46 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46109.45079861111</v>
+        <v>46109.44979166667</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037783775896313876</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037783775896313876</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1774680507000</v>
+        <v>1774680487000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3616,7 +3614,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -3633,7 +3631,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3642,41 +3640,41 @@
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>46109.4503125</v>
+        <v>46109.45008101852</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2037783775896313876</t>
+          <t>2037783335389540775</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2037783775896313876</t>
+          <t>2037783335389540775</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1774680487000</v>
+        <v>1774680381000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3686,7 +3684,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3703,51 +3701,50 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46109.45008101852</v>
+        <v>46109.44885416667</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1774680462000</v>
+        <v>1774680398000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3757,7 +3754,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -3774,120 +3771,117 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46109.44979166667</v>
+        <v>46109.44905092593</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2037783477979091314</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2037783477979091314</t>
+          <t>2037432200166277382</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1774680415000</v>
+        <v>1774596664000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2037432200166277382</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" s="2" t="n">
-        <v>46109.44924768519</v>
+        <v>46108.47990740741</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2037783335389540775</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2037783335389540775</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1774680381000</v>
+        <v>1774667679000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2037432200166277382</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3897,7 +3891,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1810, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3914,50 +3908,51 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>34</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2037432200166277382</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>46109.44885416667</v>
+        <v>46109.30184027777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2037783402758508685</t>
+          <t>2037783049065390446</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2037783402758508685</t>
+          <t>2037783049065390446</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1774680398000</v>
+        <v>1774680313000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3967,7 +3962,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3984,294 +3979,86 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46109.44905092593</v>
+        <v>46109.44806712963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1774596664000</v>
+        <v>1774680332000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2037432200166277382</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>46108.47990740741</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1774667679000</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1810, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>46109.30184027777</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1774680332000</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="n">
         <v>46109.44828703703</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1774680313000</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 967, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>46109.44806712963</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -517,163 +517,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2037955706662604958</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1774707097000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>46109.75806712963</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1774721478000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2037895388909142325</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46109.92451388889</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" t="n">
         <v>1774684800000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="n">
         <v>46109.5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>2037911596106715381</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>1774710961000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>46109.80278935185</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>2037921044221010067</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -694,166 +832,26 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F6" t="n">
         <v>1774713214000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2037911596106715381</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46109.82886574074</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2037928218003382573</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1774714924000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14498, 'friendsCount': 1923, 'description': 'libre.'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2037921044221010067</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>46109.8486574074</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2037936526093430909</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1774716905000</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -866,118 +864,120 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2037911596106715381</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46109.87158564815</v>
+        <v>46109.82886574074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-https://t.co/Rj1kVb2Rck https://t.co/MQajcVjmt6</t>
+          <t>@EmiratesNBD_AE I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1774707097000</v>
+        <v>1774714924000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEgPDX9WsAEtE9T.jpg', 'type': 'photo', 'id': '2037895382030528513'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Los 🥚 De Donald Trump 🇺🇸', 'screenName': 'cruizomfs', 'followersCount': 456, 'favouritesCount': 14453, 'friendsCount': 1923, 'description': 'libre.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n">
-        <v>46109.75806712963</v>
+        <v>46109.8486574074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2037936526093430909</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>@cruizomfs We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1774721478000</v>
+        <v>1774716905000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037801868244533349</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -987,33 +987,33 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Rita', 'screenName': 'Rita09729643', 'followersCount': 2, 'favouritesCount': 51, 'friendsCount': 24, 'description': 'Hi'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2037895388909142325</t>
+          <t>2037928218003382573</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46109.92451388889</v>
+        <v>46109.87158564815</v>
       </c>
     </row>
     <row r="9">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1297,49 +1297,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1774685453000</v>
+        <v>1774688651000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/tweet_video_thumb/HEe8fFcXcAAIJKZ.jpg', 'type': 'animated_gif', 'id': '2037804598631559168'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1352,46 +1353,46 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>46109.50755787037</v>
+        <v>46109.54457175926</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2037804608517509572</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/eazyislit/status/2037855319393464474</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I claim it 🙏🏼🙏🏼🙏🏼</t>
+          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1774697544000</v>
+        <v>1774690852000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2037855319393464474</t>
+          <t>2037818020597215557</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1401,7 +1402,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Dat Dark Rich Dude 💎🇳🇬🇬🇧', 'screenName': 'eazyislit', 'followersCount': 66, 'favouritesCount': 752, 'friendsCount': 238, 'description': 'Best in Maintaining Maximum 🕴🏽Composure 🥇🇺🇸🇳🇬 I Love Peace 🤍🛐Graphics Designer 👩\u200d🎤  A product of Grace 🕊️❤️✝️'}</t>
+          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1418,173 +1419,40 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2037818020597215557</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="n">
-        <v>46109.6475</v>
+        <v>46109.5700462963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2037827252075839770</t>
+          <t>2037799000171216897</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2037818020597215557</t>
+          <t>2037799000171216897</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1774688651000</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{'name': 'T.A', 'screenName': 'Talal_Hus', 'followersCount': 57, 'favouritesCount': 741, 'friendsCount': 983, 'description': '👷🏻\u200d♂️⏳🏗 ——— ✈️'}</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" s="2" t="n">
-        <v>46109.54457175926</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2037827252075839770</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2037827252075839770</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>@Talal_Hus نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1774690852000</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{'name': 'EmiratesNBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17238, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2037818020597215557</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46109.5700462963</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://x.com/argosaki/status/2037799000171216897</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2037799000171216897</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2037799000171216897</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://x.com/argosaki/status/2037799000171216897</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -1592,210 +1460,350 @@
 https://t.co/qE71v9rmUv</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F15" t="n">
         <v>1774684116000</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2037799000171216897</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111376, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" s="2" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="2" t="n">
         <v>46109.49208333333</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2037799000171216897</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2038054346693435744</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/argosaki/status/2038054346693435744</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>.👇♥️🙏 https://t.co/k2P5WezRfZ</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F16" t="n">
         <v>1774744996000</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2038054346693435744</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEifoD5b0AEmFq5.jpg', 'type': 'photo', 'id': '2038054341974937601'}]</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111374, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'name': 'GP Q', 'screenName': 'argosaki', 'followersCount': 111376, 'favouritesCount': 302141, 'friendsCount': 1637, 'description': 'Special? Mmmmm not really, just me :). *Standard disclaimer that nothing in these posts should be used as a substitute for financial or medical advice*'}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M16" t="n">
         <v>29</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" s="2" t="n">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="n">
         <v>46110.19671296296</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2037801868244533349</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2037796434725269639</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F17" t="n">
         <v>1774680622000</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" s="2" t="n">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="2" t="n">
         <v>46109.45164351852</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2037796434725269639</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2037785874474430532</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037785874474430532</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE I applied for liv X account Still not received any response 
 Reference number 
 2026038379331830</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>1774680987000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46109.45586805556</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2037796434725269639</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1774682607000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>46109.47461805555</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2037796434725269639</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2037796434725269639</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>1774680987000</v>
+        <v>1774683505000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1813,7 +1821,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1826,180 +1834,40 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037792667782824069</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46109.45586805556</v>
+        <v>46109.48501157408</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2037796434725269639</t>
+          <t>2037796009921900610</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2037792667782824069</t>
+          <t>2035436745538281762</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>@ZaibKang We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1774682607000</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2037785874474430532</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46109.47461805555</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2037796434725269639</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1774683505000</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2037784344333275440</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2037792667782824069</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46109.48501157408</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2037796009921900610</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2035436745538281762</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/RotanaLive/status/2035436745538281762</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2013,138 +1881,138 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F21" t="n">
         <v>1774120911000</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2035436745538281762</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2035436341970788352/img/OfSY4fBJEacp25TH.jpg', 'type': 'video', 'id': '2035436341970788352'}]</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193214, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193210, 'favouritesCount': 7051, 'friendsCount': 147, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L21" t="n">
         <v>6</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M21" t="n">
         <v>28</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>7289</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
         <v>46102.97350694444</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2037796009921900610</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2037796009921900610</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA 🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F22" t="n">
         <v>1774683403000</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2035436745538281762</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>{'name': 'مازن البلوشي', 'screenName': 'MazBalushi35285', 'followersCount': 1, 'favouritesCount': 458, 'friendsCount': 1, 'description': 'عربي. رجل أعمال. أبني المستقبل خطوة بخطوة.'}</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>2035436745538281762</t>
         </is>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>46109.48383101852</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2031673422921564269</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2171,68 +2039,68 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F23" t="n">
         <v>1773223665000</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HDH0NZXWQAAnKTa.jpg', 'type': 'video', 'id': '2031673271423295488'}]</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
         <v>128</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>40</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M23" t="n">
         <v>53</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
         <v>46092.58871527778</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -2240,72 +2108,72 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F24" t="n">
         <v>1774681991000</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>2031673422921564269</t>
         </is>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>46109.46748842593</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225946308358408</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -2317,68 +2185,68 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F25" t="n">
         <v>1773832234000</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225772156563456/img/fizQ3vAEH0uqiLix.jpg', 'type': 'video', 'id': '2034225772156563456'}]</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>91</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L25" t="n">
         <v>39</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M25" t="n">
         <v>50</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2638</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
         <v>46099.63233796296</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2387,72 +2255,72 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F26" t="n">
         <v>1774681901000</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>2034225946308358408</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P26" s="2" t="n">
         <v>46109.46644675926</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -2464,68 +2332,68 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F27" t="n">
         <v>1773832238000</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>72</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>29</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M27" t="n">
         <v>46</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>1678</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" s="2" t="n">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
         <v>46099.63238425926</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2534,72 +2402,72 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F28" t="n">
         <v>1774681600000</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>46109.46296296296</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2608,92 +2476,232 @@
 @yasar8212</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>1774681854000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2034225946308358408</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46109.46590277777</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1774680795000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46109.45364583333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2037784853866029145</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025123939970584932</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>حل اللغز واربح 10,000 درهم.💰
+أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
+تابع @EmiratesNBD_ae
+قم بالإشارة إلى 3 من أصدقائك
+حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
+        </is>
+      </c>
       <c r="F31" t="n">
-        <v>1774681854000</v>
+        <v>1771662146000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2034225946308358408</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1152, 'favouritesCount': 19738, 'friendsCount': 1787, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2034225946308358408</t>
-        </is>
-      </c>
+          <t>9399</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>46109.46590277777</v>
+        <v>46074.5155787037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>@EmiratesNBD_AE B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1774680795000</v>
+        <v>1774680744000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEequS2a4AAftLC.jpg', 'type': 'photo', 'id': '2037785068719235072'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Jahan Zaib Akbar Kang', 'screenName': 'ZaibKang', 'followersCount': 599, 'favouritesCount': 4475, 'friendsCount': 18, 'description': 'سُبْحَانَ اللَّهِ ، وَالْحَمْدُ لِلَّهِ ، وَلَا إِلَهَ إِلَّا اللَّهُ ، وَاللَّهُ أَكْبَرُ\nEntrepreneur &amp; investor'}</t>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2710,16 +2718,16 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2025123939970584932</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46109.45364583333</v>
+        <v>46109.45305555555</v>
       </c>
     </row>
     <row r="33">
@@ -2769,7 +2777,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2786,7 +2794,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -2841,7 +2849,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2858,7 +2866,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2929,7 +2937,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2954,91 +2962,91 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1774680699000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>2025123939970584932</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2025123939970584932</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>حل اللغز واربح 10,000 درهم.💰
-أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
-تابع @EmiratesNBD_ae
-قم بالإشارة إلى 3 من أصدقائك
-حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1771662146000</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>2025123939970584932</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2025123808986718208/img/anriFRhFhmo7262r.jpg', 'type': 'video', 'id': '2025123808986718208'}]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>857</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>183</v>
-      </c>
-      <c r="M36" t="n">
-        <v>191</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>9397</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46074.5155787037</v>
+        <v>46109.45253472222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2037784668028985459</t>
+          <t>2037784763122217375</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2037784668028985459</t>
+          <t>2037784763122217375</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1774680699000</v>
+        <v>1774680722000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3069,7 +3077,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3078,41 +3086,41 @@
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46109.45253472222</v>
+        <v>46109.45280092592</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2037784763122217375</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2037784763122217375</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1774680722000</v>
+        <v>1774680637000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2027634643315404863</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3144,41 +3152,41 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2025123939970584932</t>
+          <t>2027634776555872373</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46109.45280092592</v>
+        <v>46109.45181712963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1774680637000</v>
+        <v>1774680620000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3209,7 +3217,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3218,37 +3226,37 @@
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46109.45181712963</v>
+        <v>46109.45162037037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1774680620000</v>
+        <v>1774680594000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3279,7 +3287,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3288,37 +3296,38 @@
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46109.45162037037</v>
+        <v>46109.45131944444</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1774680594000</v>
+        <v>1774680549000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3349,7 +3358,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3358,42 +3367,41 @@
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46109.45131944444</v>
+        <v>46109.45079861111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1774680549000</v>
+        <v>1774680507000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2027634643315404863</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3420,46 +3428,47 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2027634776555872373</t>
+          <t>2031673422921564269</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46109.45079861111</v>
+        <v>46109.4503125</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1774680507000</v>
+        <v>1774680462000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3490,7 +3499,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3499,42 +3508,41 @@
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46109.4503125</v>
+        <v>46109.44979166667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783477979091314</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783477979091314</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1774680462000</v>
+        <v>1774680415000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3561,16 +3569,16 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2031673422921564269</t>
+          <t>2034225946308358408</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46109.44979166667</v>
+        <v>46109.44924768519</v>
       </c>
     </row>
     <row r="45">
@@ -3631,7 +3639,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3701,7 +3709,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3771,7 +3779,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3786,279 +3794,279 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1774680332000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46109.44828703703</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2037730056920088898</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Stay safe and bank with ease with ENBD X and businessONLINE 
 Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>1774596664000</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HEZpyN2aMAAR1EU.jpg', 'type': 'photo', 'id': '2037432192863973376'}]</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174059, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174061, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>1</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M49" t="n">
         <v>9</v>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="2" t="n">
         <v>46108.47990740741</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2037730056920088898</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1774667679000</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1810, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2037432200166277382</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>46109.30184027777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1774667679000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'wiil', 'screenName': 'wil3020', 'followersCount': 49, 'favouritesCount': 1811, 'friendsCount': 24, 'description': 'تهوى العين من يعجبها، ويهوى العقل من يفهمه، أمّا الروح فلا تهوى إلاّ من يُشبهها.'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2037432200166277382</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46109.30184027777</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>2037783049065390446</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>2037783049065390446</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
 @Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>1774680313000</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>2034225964863893587</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P51" s="2" t="n">
         <v>46109.44806712963</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1774680332000</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>{'name': 'Soha.mostafa77', 'screenName': 'Sosomostafa729S', 'followersCount': 345, 'favouritesCount': 22185, 'friendsCount': 968, 'description': 'Moom of 2 🙍\u200d♂️🙍\u200d♀️\nShopping 🛍 food 😋 traveling \nLive in UAE 🇦🇪🕊💕'}</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2034225964863893587</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>46109.44828703703</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193532, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -780,7 +780,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1776223385969</v>
+        <v>1776225794636</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46127.30770797453</v>
+        <v>46127.33558606482</v>
       </c>
     </row>
     <row r="7">
@@ -892,7 +892,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3881, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3881, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>94</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2518,12 +2518,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2657,12 +2657,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>142</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2727,12 +2727,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2798,12 +2798,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2868,12 +2868,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>63</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3080,169 +3080,171 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044047297034760542</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1776168712000</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2044025847523487886</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="2" t="n">
-        <v>46126.67490740741</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2044025847523487886</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2044038292707143832</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2044038292707143832</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Presenting Project Nightingale: A Coachbuild Collection https://t.co/KEb4FjZgsI</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1776171680000</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2044038292707143832</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" s="2" t="n">
-        <v>46126.70925925926</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2044047297034760542</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2044047297034760542</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
 #EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
 https://t.co/ukweMYki3P</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>1776173826000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2044047297034760542</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
+        <v>46126.73409722222</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2044047297034760542</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2044060507603382318</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/biztoday_intl/status/2044060507603382318</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>#DaherAircraft strengthens its customer support and distributor Network by adding the Kodiak to Columbia Air’s portfolio.
+@DAHER_official #aircraft #aviation #NicolasChabbert #MelissaDuzguner
+https://t.co/tFtCpJWMU9</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1776176976000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2044060507603382318</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="n">
+        <v>46126.77055555556</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2044025847523487886</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2044025847523487886</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+        </is>
+      </c>
       <c r="F41" t="n">
-        <v>1776173826000</v>
+        <v>1776168712000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3252,7 +3254,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3262,55 +3264,53 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46126.73409722222</v>
+        <v>46126.67490740741</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/dcgguide/status/2044025847523487886</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044025847523487886</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2043584275161977015</t>
+          <t>2044038581161996359</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2043584275161977015</t>
+          <t>https://x.com/dcgguide/status/2044038581161996359</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone Partners with @WioBank to Provide Digital Banking Solutions for Businesses.
-#DWTC #WioBank #Dubai #UAE #DXB @DWTCOfficial
-https://t.co/GIjGf2VZ0q</t>
+          <t>EWEC Opens Q2 2026 Clean Energy Certificates Auction To Empower Organisations To Lead Global Energy Transition https://t.co/wXSWsOlKcV</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1776063433000</v>
+        <v>1776171748000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2043584275161977015</t>
+          <t>2044038581161996359</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3333,73 +3333,62 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46125.45640046296</v>
+        <v>46126.7100462963</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
+#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
+https://t.co/rQ8bwNlb8E via @onevillenews https://t.co/uuh2N7Ktl1</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1776172925000</v>
+        <v>1776167865000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3mvnXaMAAc5dn.jpg', 'type': 'photo', 'id': '2044043511591481344'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3Tb09bMAAglq0.jpg', 'type': 'photo', 'id': '2044022280922279936'}]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3416,58 +3405,58 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" s="2" t="n">
-        <v>46126.72366898148</v>
+        <v>46126.66510416667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044022292972482932</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2043769833955917928</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044029975376855339</t>
+          <t>https://x.com/OneVilleNews/status/2043769833955917928</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
+#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
+https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1776169697000</v>
+        <v>1776107674000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2043769833955917928</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3abgLagAAnLi2.jpg', 'type': 'photo', 'id': '2044029971925204992'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFztt94bcAAnViP.jpg', 'type': 'photo', 'id': '2043769704880500736'}]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3477,19 +3466,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46126.68630787037</v>
+        <v>46125.96844907408</v>
       </c>
     </row>
     <row r="45">
@@ -3550,7 +3539,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -3599,7 +3588,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16972, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
+          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16975, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3616,7 +3605,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3687,7 +3676,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
@@ -3755,7 +3744,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
@@ -3810,7 +3799,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193532, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3827,7 +3816,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
@@ -3876,7 +3865,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 188, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
+          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 189, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3893,7 +3882,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3963,7 +3952,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
@@ -4029,7 +4018,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4375,7 +4364,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4445,7 +4434,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4517,7 +4506,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -4585,7 +4574,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -4665,96 +4654,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2043917165502316982</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>46126.41667824074</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
         <is>
           <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
 تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
@@ -4763,17 +4681,84 @@
 https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
         </is>
       </c>
+      <c r="F62" t="n">
+        <v>1776146400000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2043932263386157239</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="n">
+        <v>46126.41666666666</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2043932266456367150</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2043932266456367150</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>To know more:
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
       <c r="F63" t="n">
-        <v>1776146400000</v>
+        <v>1776146401000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2043932263725854816</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4795,23 +4780,27 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2043932263725854816</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46126.41667824074</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2043932263386157239</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4863,7 +4852,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,36 +517,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044517451078197394</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1776194041000</v>
+        <v>1776285920000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -556,11 +555,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -569,53 +568,50 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>309</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46126.96806712963</v>
+        <v>46128.03148148148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044610910640361699</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044068136115417120</t>
+          <t>https://x.com/dorienotfish/status/2044610910640361699</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>@DustshotW can i try</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1776178795000</v>
+        <v>1776308202000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -625,11 +621,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -642,132 +638,134 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46126.79160879629</v>
+        <v>46128.289375</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2042680872118174012</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>@dorienotfish s enbd</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1775848045000</v>
+        <v>1776308585000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2042680331732684801/img/ZnKpK7bzPoCB7Knz.jpg', 'type': 'video', 'id': '2042680331732684801'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25613, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6605</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2044610910640361699</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>46122.96348379629</v>
+        <v>46128.29380787037</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044613234427383893</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/dorienotfish/status/2044613234427383893</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>@DustshotW sorry at first i though u said 'skibdi' mb✌🏻✌🏻✌🏻 ok here https://t.co/DsboMnkCKn</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1776184114000</v>
+        <v>1776308756000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_s4_pbAAANiPL.jpg', 'type': 'photo', 'id': '2044613219751493632'}]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'طموح العجلان', 'screenName': 'AlAjlansambrfi', 'followersCount': 9, 'favouritesCount': 222, 'friendsCount': 164, 'description': 'طموح في عالم الأعمال بالمدينة، أحب التقنية والمشاريع الكبرى.'}</t>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -780,40 +778,59 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46126.85317129629</v>
+        <v>46128.29578703704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>1776225794636</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>1776308293000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2044611289733878057</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -821,205 +838,217 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46127.33558606482</v>
+        <v>46128.29042824074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2044119073538113567</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044119073538113567</t>
+          <t>https://x.com/BehindNums/status/2044611048305574280</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776190939000</v>
+        <v>1776308235000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJX0AE0m43.jpg', 'type': 'photo', 'id': '2044119052759584769'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJWkAARX1r.jpg', 'type': 'photo', 'id': '2044119052759502848'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2021899533345841203</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46126.93216435185</v>
+        <v>46128.28975694445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2044120061124698315</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044120061124698315</t>
+          <t>https://x.com/CryptoNewsHntrs/status/2029869216254341430</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef https://t.co/wJsGrMVAFs</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1776191175000</v>
+        <v>1772793508000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWL8XkAAwsHK.jpg', 'type': 'photo', 'id': '2044120040547520512'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWMZW8AAJzDO.jpg', 'type': 'photo', 'id': '2044120040669114368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2CXkAATb_t.jpg', 'type': 'photo', 'id': '2029869212919894016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2eXwAA68mZ.jpg', 'type': 'photo', 'id': '2029869213037346816'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Crypto News Hunters 🎯', 'screenName': 'CryptoNewsHntrs', 'followersCount': 28363, 'favouritesCount': 314597, 'friendsCount': 138, 'description': 'Crypto News 🌐 Financial Markets 📈 Memes &amp; Hopium 🔥 Not Financial Advice 🚫'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2044119073538113567</t>
-        </is>
-      </c>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46126.93489583334</v>
+        <v>46087.61004629629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2044121269105275233</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044121269105275233</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @Poloniex @WazirXIndia @tadawul @Cryptopia_NZ @binance @dogecoin @bankofengland @bankofcanada @BankofIndia_IN @Banxico @Bancolombia @BancoCentralBR @BankofAmerica https://t.co/FmIt0fuKbt</t>
+          <t>@CryptoNewsHntrs ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1776191463000</v>
+        <v>1776301372000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcaOW8AI_KR0.jpg', 'type': 'photo', 'id': '2044121246971916290'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcbqasAQGqbQ.jpg', 'type': 'photo', 'id': '2044121247358038020'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'زيد أكلب', 'screenName': 'zaydaklabhoqx', 'followersCount': 30, 'favouritesCount': 301, 'friendsCount': 48, 'description': 'مدير آي تي في دبي، أحب التقنية والسيارات والكرة. أعزب ومستمتع بالحياة الفاخرة.'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1032,200 +1061,201 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2044120061124698315</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46126.93822916667</v>
+        <v>46128.21032407408</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2044122040836206849</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044122040836206849</t>
+          <t>https://x.com/Brockutd/status/2043970652697211186</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @MonarchieBe @RoyalFamily @koninklijkhuis @KingSalman @takaichi_sanae @kantei @Kantei_Saigai @DefensieMin @OPRArgentina @presidencia_BR @CancilleriaPeru @Cancilleria_Ar @cancilleriasv @wef @wto @IMFNews @EU_Commission @iaeaorg https://t.co/NfbvQKMl3H</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1776191647000</v>
+        <v>1776155553000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJcxX0AApkCR.jpg', 'type': 'photo', 'id': '2044122020749758464'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJczXkAACxrB.jpg', 'type': 'photo', 'id': '2044122020758130688'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdMfXYAA7k8w.jpg', 'type': 'photo', 'id': '2043970627372015616'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdM8asAEzRR_.jpg', 'type': 'photo', 'id': '2043970627493867521'}]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BROCK(fan)', 'screenName': 'Brockutd', 'followersCount': 6684, 'favouritesCount': 145265, 'friendsCount': 791, 'description': 'Face of Pogba Fc •|• @manutd •|• Fan account •|• @Roobet'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1037</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>9501</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2044121269105275233</t>
-        </is>
-      </c>
+          <t>428722</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" s="2" t="n">
-        <v>46126.9403587963</v>
+        <v>46126.52260416667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2044123427083083921</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044123427083083921</t>
+          <t>https://x.com/STFU1346/status/2043989823325716661</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei @Kantei_Saigai MY INTERNATIONAL RECIPE: POWER SOUP. MA RECETTE INTERNATIONALE : SOUPE ÉNERGISANTE. @LeaderOkkes @EmmanuelMacron @Elysee @francediplo @francediplo_EN @lemondefr @FranceoSenegal @FratellidItalia @GiorgiaMeloni @ItalyMFA @Gazzetta_it @Pontifex @VaticanNews @netanyahu @IsraelMFA https://t.co/AOXivIo2V8</t>
+          <t>@Brockutd Man U had it easy for years, now maybe karma is at play.
+I think it was soft, but the rules are the rules.
+Man U were shite last night, and should've been down by 3 or more before they woke up.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1776191977000</v>
+        <v>1776160124000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMGXEAEjj03.jpg', 'type': 'photo', 'id': '2044123407843790849'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMQasAEPCjo.jpg', 'type': 'photo', 'id': '2044123407885971457'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2044122040836206849</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46126.94417824074</v>
+        <v>46126.57550925926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2044124392943137264</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044124392943137264</t>
+          <t>https://x.com/JeetyJeeterson/status/2044040984212758846</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei MY INTERNATIONAL RECIPE: POWER SOUP. המתכון הבינלאומי שלי: מרק עוצמתי. @LeaderOkkes @netanyahu @YairNetanyahu @IDF @IsraeliPM @IAFsite @IsraelMFA @Isaac_Herzog @TimesofIsrael @Jerusalem_Post @usembassyjlm @IsraelinUSA @IsraelinSpanish @IsraelinUK @IsraelinGermany @TelAvivUni https://t.co/1J3VzW57FV</t>
+          <t>@STFU1346 @Brockutd This narrative that United got all the decisions in the past is a complete lie. United are on the wrong end of poor decisions more than anybody, this lie was started by rival fans with zero evidence. We used to get alot of pens, as were attacking twice as much as everybody else</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1776192207000</v>
+        <v>1776172321000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlWoAAL2qo.jpg', 'type': 'photo', 'id': '2044124371388637184'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlXEAAQXCy.jpg', 'type': 'photo', 'id': '2044124371388665856'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Jeety', 'screenName': 'JeetyJeeterson', 'followersCount': 416, 'favouritesCount': 667, 'friendsCount': 1554, 'description': "Whatever people say I am, that's what I'm not"}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1238,64 +1268,66 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>58</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2044123427083083921</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46126.94684027778</v>
+        <v>46126.71667824074</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044125532476821949</t>
+          <t>https://x.com/STFU1346/status/2044048198029742561</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE 我的國際食譜能量湯. MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden @MHI_Group @RollsRoyce @LandRover @RangeRover @astonmartin @F1 @MercedesBenz @MercedesAMGF1 @BMW @Peugeot @Ford @FordMustang @VolvoCarUSA @renaultgroup @Tesla https://t.co/0QaF62lMwZ</t>
+          <t>@JeetyJeeterson @Brockutd No, none, nada, zilch,  penalties against Man U under Ferguson at Old Trafford during their purple.. Give your head a shake man.
+Look at Sky Sports and the coverage you's get. Be as well call it Man U TV.
+The "Red Cartel" is no conspiracy theory, Man U are the head of the gang.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1776192479000</v>
+        <v>1776174041000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUs2aMAA5imS.jpg', 'type': 'photo', 'id': '2044125512579297280'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUsPWAAA7hU8.jpg', 'type': 'photo', 'id': '2044125512415444992'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1305,67 +1337,67 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>69</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2044124392943137264</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46126.94998842593</v>
+        <v>46126.73658564815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044126467026497799</t>
+          <t>https://x.com/Cle_Etc/status/2044431315555024909</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden 私の国際レシピ：パワースープ. MY INTERNATIONAL RECIPE: POWER SOUP. LOOK AT. @LeaderOkkes @SwissMFA @DanishMFA @BelgiumMFA @FCDOGovUK @MofaJapan_jp @KSAMOFA @CanadaFP @IsraelMFA @MFA_China  @ItalyMFA_int @francediplo_EN @DutchMFA @GreeceMFA @ArgentinaMFA @ItamaratyGovBr https://t.co/0q2rnxRjDF</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Hmmm, from an Oil Money Club.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1776192702000</v>
+        <v>1776265383000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLEWEAEAEqo.jpg', 'type': 'photo', 'id': '2044126448403746817'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLRXYAABkRi.jpg', 'type': 'photo', 'id': '2044126448458358784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1378,64 +1410,67 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46126.95256944445</v>
+        <v>46127.79378472222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127070410674226</t>
+          <t>https://x.com/STFU1346/status/2044432755811860595</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @infopresidencia @Presidencia_Ec @presidenciaperu @PresidenciaSV @presidencia_BR @SecPrensaSV @PresidenciaCuba @PresidenciaPy @presidenciacr @PresidenciaCPNL @MonarchieBe @koninklijkhuis @RoyalFamily @IsraeliPM @SwissGov @GOVUK https://t.co/vaMTYIPN32</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd Here are your sponsors:
+Commercial Bank of Qatar: A Financial Services Affinity Partner for Qatar.
+VIVA: An integrated telecommunications partner for Bahrain and Kuwait. 
+TM: An integrated telecommunications partner for Malaysia (often grouped with regional Asian/Middle Eastern</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1776192846000</v>
+        <v>1776265727000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKsXEAAC63S.jpg', 'type': 'photo', 'id': '2044127049598570496'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKzWEAArvi3.jpg', 'type': 'photo', 'id': '2044127049627865088'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1448,64 +1483,67 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46126.95423611111</v>
+        <v>46127.7977662037</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127797086446009</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY INTERNATIONAL RECIPE: POWER SOUP.A MINHA RECEITA INTERNACIONAL:SOPA ENERGÉTICA. @LeaderOkkes @Walmart @Apple @AppleMusic @Microsoft @Google @SpaceX @X @Oracle @OracleDatabase @Huawei_Europe @Tesla  @Xiaomi @XiaomiIndonesia @McDonalds @BurgerKingUK @CocaCola @pepsi @RollsRoyce https://t.co/Pkuk6ynj28</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1776193019000</v>
+        <v>1776265837000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgqboAAYu-e.jpg', 'type': 'photo', 'id': '2044127777050566656'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgcaUAAEnpW.jpg', 'type': 'photo', 'id': '2044127776991760384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1518,64 +1556,64 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46126.95623842593</v>
+        <v>46127.79903935185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2044128711998411106</t>
+          <t>2044459400069357578</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044128711998411106</t>
+          <t>https://x.com/Cle_Etc/status/2044459400069357578</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @Apple @AppleMusic @Microsoft MY INTERNATIONAL RECIPE: POWER SOUP. LA MIA RICETTA INTERNAZIONALE: ZUPPA ENERGETICA. @LeaderOkkes @GiorgiaMeloni @FratellidItalia @ItalyMFA @Jaemyung_Lee @SamsungKorea @VogueKorea @kantei @bankofengland @TheEconomist @lemondefr @folha @DefensieMin @DilanYesilgoz @koninklijkhuis https://t.co/yZXs4ltxR4</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Awe, you worked really hard for that. My point is that there are a handful of states sports washing, pumping billions into their purchased clubs… but we still have to listen to the fans complaining about imaginary cartels that control referees.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1776193237000</v>
+        <v>1776272079000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N6HasAQaFiL.jpg', 'type': 'photo', 'id': '2044128694416093188'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N50WwAA9QJR.jpg', 'type': 'photo', 'id': '2044128694336143360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1588,68 +1626,69 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46126.95876157407</v>
+        <v>46127.87128472222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2044129315659345996</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044129315659345996</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart MY INTERNATIONAL RECIPE: POWER SOUP. MEUM COQUENDI INTERNATIONALE: IUS ENERGETICUM. I’M KING - BARON OF THE WORLD. @LeaderOkkes @spagov @Reuters @NatGeo @Forbes @TIME @FT @TheEconomist @MarketWatch @MorganStanley @jpmorgan @NYSE @Nasdaq @BBCWorld @SkyNews @cnni @FoxNews @Nike https://t.co/645SVweoGN</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1776193381000</v>
+        <v>1776265201000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w1xbYAAHhrr.jpg', 'type': 'photo', 'id': '2044129294545543168'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w0_XwAA1srp.jpg', 'type': 'photo', 'id': '2044129294335590400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8-vnKWcAAQyPA.jpg', 'type': 'video', 'id': '2044421704122798080'}]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1658,64 +1697,60 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2044128711998411106</t>
-        </is>
-      </c>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>46126.96042824074</v>
+        <v>46127.79167824074</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2044130108303085904</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130108303085904</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2043932263717482626</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @spagov MY INTERNATIONAL RECIPE: POWER SOUP - IUS POTENTIA - SOUPE PUISSANTE - パワースープ. I’M BARON - KING OF THE WORLD. @LeaderOkkes @Walmart @Apple  @Microsoft @Google @SpaceX @X @Oracle @Huawei_Europe @Tesla @TeslaAUNZ @Xiaomi  @McDonaldsJapan @BurgerKingUK @CocaCola @pepsi @Meta https://t.co/rRQOciWTn0</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1776193570000</v>
+        <v>1776146400000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e7mXYAA1rfh.jpg', 'type': 'photo', 'id': '2044130086383738880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e8TasAId-9v.jpg', 'type': 'photo', 'id': '2044130086572699650'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043610882656059392/img/HaP0BSdqwFktNLDX.jpg', 'type': 'video', 'id': '2043610882656059392'}]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1725,71 +1760,70 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2044129315659345996</t>
-        </is>
-      </c>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>46126.96261574074</v>
+        <v>46126.41666666666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2044130932110626901</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130932110626901</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors ནུས་ཤུགས་ཐང་།. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @NASA @SpaceX @teslaeurope @Tesla_Asia @amazon @alibaba_cloud @msdev @ApplePodcasts @FCDOGovUK @ChinaMusicData @GovernmentRF @MichSoS @DefenceHQ @RoyalFamily @GiorgiaMeloni @EmmanuelMacron @francediplo @elonmusk https://t.co/hBU5y91OWL</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1776193766000</v>
+        <v>1776252503000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XcAEKunC.jpg', 'type': 'photo', 'id': '2044130916491030529'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XAAA-k6v.jpg', 'type': 'photo', 'id': '2044130916491001856'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8VrwnXkAApAXH.jpg', 'type': 'photo', 'id': '2044376597378076672'}]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1798,68 +1832,65 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2044130108303085904</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46126.96488425926</v>
+        <v>46127.64471064815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2044132642241568996</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044132642241568996</t>
+          <t>https://x.com/khir_llnas/status/2044440524782764312</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY POWER SOUP. पावर सूप. I’M KING OF THE WORLD. @LeaderOkkes @UniofOxford @OUPAcademic @Harvard @Stanford @Cambridge_Uni @Yale @WHU_1893 @universityofky @MIT @techreview @WashInstitute @ForeignPolicy @ForeignAffairs @CFR_org @ChathamHouse @BrookingsInst @McKinsey_MGI @TelAvivUni https://t.co/Gv1O15jASP</t>
+          <t>تبرع الآن
+https://t.co/sk7px2ePBH https://t.co/lsrrrAISd0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1776194174000</v>
+        <v>1776267579000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDhasAE0J8P.jpg', 'type': 'photo', 'id': '2044132613951238145'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDZWAAA220e.jpg', 'type': 'photo', 'id': '2044132613917376512'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9PwRYXUAAfgil.jpg', 'type': 'photo', 'id': '2044440446567403520'}]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1868,68 +1899,69 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2044130932110626901</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46126.96960648148</v>
+        <v>46127.81920138889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2044133212385874152</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133212385874152</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford MY POWER SOUP. MIJN KRACHTSOEP. I’M KING OF THE WORLD. @LeaderOkkes @DefenceU @DefesaGovBr @DefenceHQ @Defensoria_Peru @DefensaSV @Defensagob @Defensie @DefensieMin @DefensieStas @DHQNigeria @kdfinfo @RwandaMoD  @DefensoriaCol @ArmedForcesJO @CanadianForces @IDF @Armees_Gouv https://t.co/j9UW8NkvCJ</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+https://t.co/AuS5pOClPI
+https://t.co/uOBF8Ce7As
+https://t.co/0Q3Pd23x0U
+https://t.co/QMIfzjAAnq
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776194310000</v>
+        <v>1776260321000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxYXQAALIb0.jpg', 'type': 'photo', 'id': '2044133193196978176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxXWgAA_cP6.jpg', 'type': 'photo', 'id': '2044133193192734720'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1942,64 +1974,65 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2044132642241568996</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46126.97118055556</v>
+        <v>46127.73519675926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2044133751009997207</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133751009997207</t>
+          <t>https://x.com/ibmag_magazine/status/2043999660285862211</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford @DefenceU MIN KRAFTSOPPA. MY POWER SOUP. @LeaderOkkes @BankofAmerica @bankofengland @bankofcanada @BankofIndia_IN @bankofthailand @BankOfTanzania @bankofmaldives @BcodeVenezuela @Banxico @BancoMundialLAC @Bancolombia @el_BID @BancoMundial @BancoCentralBR @BancoCentral_AR @BancoCentralRD https://t.co/tHfR0Eljxf</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1776194439000</v>
+        <v>1776162469000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-vasAANkaM.jpg', 'type': 'photo', 'id': '2044133729359278080'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-RWQAA5RfD.jpg', 'type': 'photo', 'id': '2044133729233158144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2012,134 +2045,130 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2044133212385874152</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46126.97267361111</v>
+        <v>46126.60265046296</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X https://t.co/8qnHpREKqV</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on https://t.co/966sAK8POe
+#GCnews #emirates #MENA https://t.co/B6wVnQqtgg</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1776194550000</v>
+        <v>1776255595000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OSkbEAAvVjg.jpg', 'type': 'photo', 'id': '2044134198538342400'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OTeXYAA1oKr.jpg', 'type': 'photo', 'id': '2044134198781370368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8h57OawAA3WNa.jpg', 'type': 'photo', 'id': '2044390034883919872'}]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2044133751009997207</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" s="2" t="n">
-        <v>46126.97395833334</v>
+        <v>46127.68049768519</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2044134999616549139</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134999616549139</t>
+          <t>https://x.com/Gulf_const/status/2044017573616893963</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei MY INTERNATIONAL RECIPE. MEUM RECEPTUM INTERNATIONALE. EGO SUM: ÖKKEŞ. @LeaderOkkes @nvidia @amazon @Apple @aramco @Broadcom @Tesla @Walmart @Walmart @Disney @Meta @NetflixKR @EliLillyandCo @jpmorgan @exxonmobil @Oracle @Roche @AstraZeneca @Shell @MorganStanley @lorealparisfr https://t.co/WRKhLq07T0</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1776194736000</v>
+        <v>1776166740000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45710WwAAMkZ5.jpg', 'type': 'photo', 'id': '2044134981094522880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4572xasAA1gCB.jpg', 'type': 'photo', 'id': '2044134981350633472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFxca_0aMAAamjh.jpg', 'type': 'photo', 'id': '2043609949796970496'}]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2152,58 +2181,49 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" s="2" t="n">
-        <v>46126.97611111111</v>
+        <v>46126.65208333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044064867896963237</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1776178016000</v>
+        <v>1776250630000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2213,63 +2233,63 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Preetam Chakraborty', 'screenName': 'iRonyForChange', 'followersCount': 42, 'favouritesCount': 1281, 'friendsCount': 193, 'description': 'Work &amp; live in 🇦🇪 | Strong political opinions | Anti-establishment'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46126.78259259259</v>
+        <v>46127.62303240741</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2044071581186699505</t>
+          <t>2044371163166466284</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/alnuaimi_bader/status/2044071581186699505</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044371163166466284</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@ChirinAsadi ما شاء الله عليكم اخت شيرين. دائماً تثبتين بُعد النظر والفهم العميق للأسواق. أتوقع تألُّق قطاع البنوك عندنا في الإمارات وحتى قطاع العقارات بتكون نتائجه مميزة بإذن الله تعالى.</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #997789 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1776179616000</v>
+        <v>1776251042000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2279,11 +2299,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'bader_alain', 'screenName': 'alnuaimi_bader', 'followersCount': 47, 'favouritesCount': 5559, 'friendsCount': 217, 'description': 'Power of simplicity'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174062, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2292,57 +2312,44 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46126.80111111111</v>
+        <v>46127.62780092593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2044082310447018168</t>
-        </is>
-      </c>
+          <t>2044363346460172688</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>@alnuaimi_bader اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>1776182174000</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2044064867896963237</t>
-        </is>
-      </c>
+        <v>1776312254982</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2350,67 +2357,51 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3884, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2044071581186699505</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46126.83071759259</v>
+        <v>46128.33628451389</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1776182192000</v>
+        <v>1776249178000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044358706846941680</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2420,63 +2411,68 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'आदियोगी', 'screenName': 'SunnyLusty', 'followersCount': 78, 'favouritesCount': 224, 'friendsCount': 39, 'description': 'Not related to any Political Party, but can’t close eyes if someone tries to fool, It’s can be any1'}</t>
+          <t>{'name': 'Sem', 'screenName': 'Sems3499', 'followersCount': 4, 'favouritesCount': 275, 'friendsCount': 7, 'description': ''}</t>
         </is>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2044358706846941680</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46126.83092592593</v>
+        <v>46127.60622685185</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2044085223952900599</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044085223952900599</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@SunnyLusty Hello, we have replied to you privately.</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1776182869000</v>
+        <v>1776235930000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2486,11 +2482,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174047, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Akbar Syed', 'screenName': 'metakixakbar', 'followersCount': 0, 'favouritesCount': 88, 'friendsCount': 25, 'description': ''}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2503,53 +2499,46 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2044082383205609853</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" s="2" t="n">
-        <v>46126.83876157407</v>
+        <v>46127.45289351852</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044310308068425734</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/ENBDdeals/status/2044310308068425734</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>@metakixakbar Quoting case #997567 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1756642722000</v>
+        <v>1776236533000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2559,11 +2548,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2572,50 +2561,55 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2044307778140025041</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="n">
-        <v>45900.67965277778</v>
+        <v>46127.45987268518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044310246277967968</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/ENBDdeals/status/2044310246277967968</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>@metakixakbar We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at
+ social@emiratesnbd.com</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1756721423000</v>
+        <v>1776236518000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2625,11 +2619,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2638,54 +2632,57 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45901.59054398148</v>
+        <v>46127.45969907408</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1776180604000</v>
+        <v>1774963476000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2695,68 +2692,67 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46126.8125462963</v>
+        <v>46112.72541666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>@RBLBankCares @rblbank I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1776180751000</v>
+        <v>1776247575000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2766,7 +2762,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2783,50 +2779,50 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46126.81424768519</v>
+        <v>46127.58767361111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044364006027403737</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/RBLBankCares/status/2044364006027403737</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1776180930000</v>
+        <v>1776249336000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2836,11 +2832,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15139, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2853,130 +2849,129 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46126.81631944444</v>
+        <v>46127.60805555555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai https://t.co/yHBmK8RVEk</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1776180989000</v>
+        <v>1776246435000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7_CgOb0AAEGFF.jpg', 'type': 'photo', 'id': '2044351699348082688'}]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2044077090039873867</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46126.81700231481</v>
+        <v>46127.57447916667</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044042548185010299</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044042548185010299</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1776181236000</v>
+        <v>1776172694000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044042548185010299</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3loHrbsAAWgHC.jpg', 'type': 'photo', 'id': '2044042283314819072'}]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2986,59 +2981,53 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2044078181662019702</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46126.81986111111</v>
+        <v>46126.72099537037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2044084483222127002</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/BSF_help/status/2044084483222127002</t>
+          <t>https://x.com/AliAhmedk66633/status/2039084064070623329</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1776182692000</v>
+        <v>1774990499000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3048,11 +3037,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'BSF Help', 'screenName': 'BSF_help', 'followersCount': 56031, 'favouritesCount': 1, 'friendsCount': 1, 'description': 'مرحبًا بكم في الحساب الرسمي BSF Help، المصدر المعتمد للإجابة على استفساراتكم المصرفية. تابعوا حسابنا @BSF_sa لمعرفة آخر الأخبار'}</t>
+          <t>{'name': 'Ali Ahmed', 'screenName': 'AliAhmedk66633', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 6, 'description': ''}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3065,52 +3054,46 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2044075725334954107</t>
-        </is>
-      </c>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" s="2" t="n">
-        <v>46126.83671296296</v>
+        <v>46113.03818287037</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>@AliAhmedk66633 @EmiratesNBD_KSA هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1776173826000</v>
+        <v>1776234320000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3120,7 +3103,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'oras2030', 'screenName': 'oras_2030', 'followersCount': 0, 'favouritesCount': 133, 'friendsCount': 126, 'description': 'سبحان الله وبحمده سبحان الله العظيم'}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3130,55 +3113,57 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2039084064070623329</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n">
-        <v>46126.73409722222</v>
+        <v>46127.43425925926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044060507603382318</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>#DaherAircraft strengthens its customer support and distributor Network by adding the Kodiak to Columbia Air’s portfolio.
-@DAHER_official #aircraft #aviation #NicolasChabbert #MelissaDuzguner
-https://t.co/tFtCpJWMU9</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1776176976000</v>
+        <v>1776230024000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3188,7 +3173,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'عـيـســى الأمـيــري', 'screenName': 'Eisa_Shj', 'followersCount': 74, 'favouritesCount': 40740, 'friendsCount': 404, 'description': 'Don’t be sorry, BE BETTER ✨'}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3205,46 +3190,46 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>77</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" s="2" t="n">
-        <v>46126.77055555556</v>
+        <v>46127.38453703704</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1776168712000</v>
+        <v>1776243753000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3254,7 +3239,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3267,50 +3252,50 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46126.67490740741</v>
+        <v>46127.5434375</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044038581161996359</t>
+          <t>https://x.com/dcgguide/status/2044619960383848830</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EWEC Opens Q2 2026 Clean Energy Certificates Auction To Empower Organisations To Lead Global Energy Transition https://t.co/wXSWsOlKcV</t>
+          <t>Soulland Arrives In Dubai, Marking Its First Entry Into The Middle East https://t.co/lNcIEXHcGK</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1776171748000</v>
+        <v>1776310360000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3320,7 +3305,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3337,58 +3322,58 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46126.7100462963</v>
+        <v>46128.31435185186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-https://t.co/rQ8bwNlb8E via @onevillenews https://t.co/uuh2N7Ktl1</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1776167865000</v>
+        <v>1776243957000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3Tb09bMAAglq0.jpg', 'type': 'photo', 'id': '2044022280922279936'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3398,65 +3383,65 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" s="2" t="n">
-        <v>46126.66510416667</v>
+        <v>46127.54579861111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2043769833955917928</t>
+          <t>https://x.com/EntAlArabiya/status/2044366042470977758</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>شراكة بين RGB وBNC Publishing لتعزيز الوصول إلى المحتوى الصحي الموثوق في المنطقة @EntMagazineME  
+#الإمارات #صحة #توعية #طب #إعلام #شركات #محتوى #رفاهية #ابتكار #entalarabiya
+https://t.co/PFB5U9YnOG</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1776107674000</v>
+        <v>1776249821000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFztt94bcAAnViP.jpg', 'type': 'photo', 'id': '2043769704880500736'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3466,53 +3451,53 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>137</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46125.96844907408</v>
+        <v>46127.61366898148</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/Zawya/status/2044002065840521609</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1776163042000</v>
+        <v>1776269241000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3522,73 +3507,73 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'Zawya', 'screenName': 'Zawya', 'followersCount': 26278, 'favouritesCount': 259, 'friendsCount': 94, 'description': 'https://t.co/zY3tN9MLkQ, by @LSEGplc, is a leading source of regional news and intelligence. Retweets are not endorsements.'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46126.60928240741</v>
+        <v>46127.8384375</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044582960431554593</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044582960431554593</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>@Zawya Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>Modesty is a defining element of a Muslim’s “style” — a “less is more” philosophy that prioritizes spirituality and personal comfort over overt attention seeking. Identity is both internal and external. Modesty is a conscious choice —and a powerful one. https://t.co/hcxLG2j35s https://t.co/V2EWTgPYbW</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1776163478000</v>
+        <v>1776301538000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044582960431554593</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_RXPNWoAA_0TN.jpg', 'type': 'photo', 'id': '2044582952999231488'}]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16975, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23737, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3605,51 +3590,48 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2044002065840521609</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46126.6143287037</v>
+        <v>46128.21224537037</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1776196874000</v>
+        <v>1776232801000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3659,11 +3641,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Hero Gidwani', 'screenName': 'GidwaniHero', 'followersCount': 19, 'favouritesCount': 24, 'friendsCount': 154, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3676,62 +3658,61 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" s="2" t="n">
-        <v>46127.00085648148</v>
+        <v>46127.41667824074</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+https://t.co/lQDtk9615Y</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1776158836000</v>
+        <v>1776232801000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2w_zAWYAA52Xp.jpg', 'type': 'photo', 'id': '2043984415965995008'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39131, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3740,132 +3721,141 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2044294653097156714</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="n">
-        <v>46126.56060185185</v>
+        <v>46127.41667824074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2043039035585700343</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+https://t.co/XwkOLamNf0</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1775933438000</v>
+        <v>1776232802000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043038860767068160/img/roy7XPjYQBFoKXUJ.jpg', 'type': 'video', 'id': '2043038860767068160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193533, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>8833</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2044294656716836969</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n">
-        <v>46123.95182870371</v>
+        <v>46127.41668981482</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1776128208000</v>
+        <v>1776237111000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7bgFgb0AArMEW.jpg', 'type': 'photo', 'id': '2044312625153298432'}]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 189, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3875,128 +3865,129 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>2043039035585700343</t>
-        </is>
-      </c>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" s="2" t="n">
-        <v>46126.20611111111</v>
+        <v>46127.4665625</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/EntMagazineME/status/2044354972473766389</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>RGB (@RGBDubai), a #Dubai-based broadcasting and content production company known for its cutting-edge output and expertise in branding and identity since 2006, and the creator of The Health Community—a digital platform focused on verified medical knowledge—has entered a strategic media partnership with Dubai-headquartered regional media company BNC Publishing.
+The collaboration aims to expand access to credible, expert-led health content across the Middle East, leveraging Entrepreneur’s bilingual platforms and established regional audience.
+Designed as more than a content platform, The Health Community seeks to create a connected ecosystem where reliable #healthcare knowledge can be shared in ways that are practical and accessible for everyday life.
+Under the partnership, Entrepreneur Middle East (@EntMagazineME) and Entrepreneur Al Arabiya will collaborate with RGB to develop bilingual editorial features, #expert insights, and multimedia storytelling that elevate conversations around prevention, wellbeing, and human performance across the region.
+Read more HERE: https://t.co/KBGmbzdXAG</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1776165319000</v>
+        <v>1776247182000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8B64ZaYAECgQU.jpg', 'type': 'photo', 'id': '2044354866932506625'}]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Zahara Sadiq', 'screenName': 'ZaharaMMalik', 'followersCount': 741, 'favouritesCount': 827, 'friendsCount': 564, 'description': 'Impact Investing | Entrepreneur | Driven by Building Bridges Globally | Serial Tea Drinker | Part Time Wisdom Coach'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178521, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>189</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" s="2" t="n">
-        <v>46126.63563657407</v>
+        <v>46127.583125</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>@ZaharaMMalik Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1776168046000</v>
+        <v>1776274926000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4005,7 +3996,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4014,54 +4005,55 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2044011613422834071</t>
-        </is>
-      </c>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46126.66719907407</v>
+        <v>46127.90423611111</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1775720297000</v>
+        <v>1776274927000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4071,11 +4063,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4088,51 +4080,57 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2044471339784810653</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="n">
-        <v>46121.48491898148</v>
+        <v>46127.90424768518</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2042152553400385940</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1775722084000</v>
+        <v>1776239419000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4150,64 +4148,62 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" s="2" t="n">
-        <v>46121.50560185185</v>
+        <v>46127.49327546296</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2042853514049917277</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1775889206000</v>
+        <v>1776274923000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4224,50 +4220,50 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2042152553400385940</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" s="2" t="n">
-        <v>46123.43988425926</v>
+        <v>46127.90420138889</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2043560931511189651</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1776057868000</v>
+        <v>1776274924000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4281,7 +4277,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4294,50 +4290,53 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>73</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2042853514049917277</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="P56" s="2" t="n">
-        <v>46125.39199074074</v>
+        <v>46127.90421296296</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1776150922000</v>
+        <v>1776239419000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4347,11 +4346,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4364,55 +4363,58 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>142</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2043560931511189651</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46126.46900462963</v>
+        <v>46127.49327546296</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1776151835000</v>
+        <v>1776239416000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4421,7 +4423,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4430,56 +4432,53 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2043951228640747823</t>
-        </is>
-      </c>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" s="2" t="n">
-        <v>46126.47957175926</v>
+        <v>46127.49324074074</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+https://t.co/WN0tZk19JS</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1776146400000</v>
+        <v>1776239417000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4506,358 +4505,16 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2044322401052250291</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1776142801000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw707XWcAAVI5E.jpg', 'type': 'photo', 'id': '2043574111394230272'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw71ETXwAAPour.jpg', 'type': 'photo', 'id': '2043574113793458176'}]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
-        <v>46126.37501157408</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46126.41667824074</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49325231482</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,102 +517,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045203152040018428</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - https://t.co/l4qu0XUPAx</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1776707097000</v>
+        <v>1776449404000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_XbAAAbdED.jpg', 'type': 'photo', 'id': '2045203142024036352'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_QaQAAmKGx.jpg', 'type': 'photo', 'id': '2045203141994627072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_MbMAAD7Cp.jpg', 'type': 'photo', 'id': '2045203141977911296'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_kboAEToWB.jpg', 'type': 'photo', 'id': '2045203142078603265'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'EVO Cars Rental', 'screenName': 'evocarsrental', 'followersCount': 34, 'favouritesCount': 7, 'friendsCount': 55, 'description': 'Go on! Drive your dream LUXURY car now!\nServices available for Individuals/Corporate Clients/Events/'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>573195</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46132.90621527778</v>
+        <v>46129.92365740741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2046287756955930787</t>
+          <t>2046285967863279687</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046287756955930787</t>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@evocarsrental Thanks for writing to us, kindly visit the below link to review the terms and conditions then you can apply 
-https://t.co/ZUuqqadVdS</t>
+          <t>@EmiratesNBD_AE Please launch prepaid debit card for tourists.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1776707994000</v>
+        <v>1776707567000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,11 +621,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Jeanvaljeanrambo', 'screenName': 'saigol7', 'followersCount': 98, 'favouritesCount': 801, 'friendsCount': 495, 'description': 'Planes,  automobiles, things that go fast and make a lot of noise. Also Linux, Unix and Android, Electronics, economics, astronomy, photography.'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -639,16 +638,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>109</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2046283996015800804</t>
+          <t>2045203152040018428</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46132.91659722223</v>
+        <v>46132.91165509259</v>
       </c>
     </row>
     <row r="4">
@@ -664,57 +663,62 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2046289305190953193</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289305190953193</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>@saigol7 For suggestions please visit the below link, We will make every effort to address the matter promptly and provide the necessary support.
+https://t.co/nfKBl3vphJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1776708363000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2045203152040018428</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045203152040018428</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1776449404000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_XbAAAbdED.jpg', 'type': 'photo', 'id': '2045203142024036352'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_QaQAAmKGx.jpg', 'type': 'photo', 'id': '2045203141994627072'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_MbMAAD7Cp.jpg', 'type': 'photo', 'id': '2045203141977911296'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGIFa_kboAEToWB.jpg', 'type': 'photo', 'id': '2045203142078603265'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>567313</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>46129.92365740741</v>
+        <v>46132.92086805555</v>
       </c>
     </row>
     <row r="5">
@@ -730,96 +734,97 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2046289251550044333</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046289251550044333</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@saigol7 Thanks for writing to us, please visit the below link to review the prepaid cards 
+https://t.co/6Lk5Jbb44I</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1776708350000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2045203152040018428</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2046285967863279687</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Please launch prepaid debit card for tourists.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1776707567000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'Jeanvaljeanrambo', 'screenName': 'saigol7', 'followersCount': 98, 'favouritesCount': 801, 'friendsCount': 495, 'description': 'Planes,  automobiles, things that go fast and make a lot of noise. Also Linux, Unix and Android, Electronics, economics, astronomy, photography.'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2045203152040018428</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="n">
-        <v>46132.91165509259</v>
+        <v>46132.92071759259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2046285967863279687</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2046289305190953193</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046289305190953193</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@saigol7 For suggestions please visit the below link, We will make every effort to address the matter promptly and provide the necessary support.
-https://t.co/nfKBl3vphJ</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1776708363000</v>
+        <v>1776702221000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2045203152040018428</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -829,7 +834,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -839,129 +844,123 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2046285967863279687</t>
-        </is>
-      </c>
+          <t>7175</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46132.92086805555</v>
+        <v>46132.84978009259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/saigol7/status/2046285967863279687</t>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2046285967863279687</t>
+          <t>2046263546024165797</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2046289251550044333</t>
+          <t>2046375898933231804</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046289251550044333</t>
+          <t>https://x.com/wallet/status/2046375898933231804</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@saigol7 Thanks for writing to us, please visit the below link to review the prepaid cards 
-https://t.co/6Lk5Jbb44I</t>
+          <t>Need this? Drop a GM below👇 https://t.co/XjAc2KdaHx</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776708350000</v>
+        <v>1776729008000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2045203152040018428</t>
+          <t>2046375898933231804</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGYwBO5WgAEB478.jpg', 'type': 'photo', 'id': '2046375878423117825'}]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'OKX Wallet', 'screenName': 'wallet', 'followersCount': 1929766, 'favouritesCount': 14748, 'friendsCount': 422, 'description': 'The crypto wallet for everything onchain. Self-custody is the future.\n\nEngagement is not endorsement.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2046285967863279687</t>
-        </is>
-      </c>
+          <t>27261</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46132.92071759259</v>
+        <v>46133.15981481481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
-https://t.co/sNYXzG1RYE</t>
+          <t>#EmiratesNBD @EmiratesNBD_AE Sent Me An Account Statement,They Owe Me 200000AED Which They Won't Pay.@HHShkMohd @MohamedBinZayed
+#Lebanese #Banks Stole My Money @FransabankGroup @EmmanuelMacron.
+#Emirates @emirates &amp;amp; @BarackObama
+ Owe Me 2 Years Pay
+I Am Just Too Tired To Give Up</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1776702221000</v>
+        <v>1776739171000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,119 +970,187 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+          <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46132.84978009259</v>
+        <v>46133.27744212963</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2046263546024165797</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2046375898933231804</t>
+          <t>2046433498962026756</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/wallet/status/2046375898933231804</t>
+          <t>https://x.com/Mario_thomas_y/status/2046433498962026756</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Need this? Drop a GM below👇 https://t.co/XjAc2KdaHx</t>
+          <t>@yallaweb Were you able to file a legal complaint @yallaweb ?</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1776729008000</v>
+        <v>1776742741000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2046375898933231804</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGYwBO5WgAEB478.jpg', 'type': 'photo', 'id': '2046375878423117825'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'OKX Wallet', 'screenName': 'wallet', 'followersCount': 1929748, 'favouritesCount': 14748, 'friendsCount': 422, 'description': 'The crypto wallet for everything onchain. Self-custody is the future.\n\nEngagement is not endorsement.'}</t>
+          <t>{'name': 'Mario Thomas', 'screenName': 'Mario_thomas_y', 'followersCount': 1643, 'favouritesCount': 2658, 'friendsCount': 236, 'description': 'Victim of Elon scams.'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>547</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>24341</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="n">
-        <v>46133.15981481481</v>
+        <v>46133.31876157408</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2046311476127023142</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/yallaweb/status/2046311476127023142</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>#God I Hate Slow #Internet,it's Killer Of  #Productivity
+Had 1000Mbps In #MexicoCity,But #GenocidalJews &amp;amp; #GenocidalGays Did    #Sabotage That,As They Thought My #highspeed Can Hinder/Expose/Endanger Their Crimes &amp;amp; Conspiracies.
+#EconomicSiege #Mexico #CDMX #Islamophobia #USA</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1776713649000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2046311476127023142</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="n">
+        <v>46132.98204861111</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2046264235852718127</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://x.com/preeminentdxb/status/2046264189786714117</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>A quiet shift, but a powerful one.
 The gap between intent and ownership in Dubai just got smaller, and more predictable.
@@ -1091,230 +1158,161 @@
 #MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>1776702375000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKavSW8AAvugA.jpg', 'type': 'photo', 'id': '2046264166428635136'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbQLWYAAjRuc.png', 'type': 'photo', 'id': '2046264175257608192'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbh8WgAAvC6X.png', 'type': 'photo', 'id': '2046264180026540032'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbz0W4AAHPcf.png', 'type': 'photo', 'id': '2046264184824848384'}]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="2" t="n">
         <v>46132.8515625</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1776702386000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>46132.85168981482</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1776702386000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46132.85168981482</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
 #RBLBank</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>1776686602000</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>{'name': 'Naveen Reddy', 'screenName': 'naveenthumala', 'followersCount': 20, 'favouritesCount': 1498, 'friendsCount': 127, 'description': 'Remember you will die'}</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" s="2" t="n">
-        <v>46132.66900462963</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>@DFMalerts 
-I have old account with DFM and now dormant. 
-I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
-I have the full details. I need your help to update my investor’s account.</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1776684807000</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
-        </is>
-      </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
@@ -1329,104 +1327,36 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>46132.64822916667</v>
+        <v>46132.66900462963</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2046171931813011938</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2046171931813011938</t>
+          <t>2045093015459352679</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1776680379000</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2046171931813011938</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39177, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" s="2" t="n">
-        <v>46132.59697916666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045093015459352679</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -1440,8 +1370,74 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>1776423145000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>346</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>866700</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="n">
+        <v>46129.61973379629</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2046173095581647055</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2046173095581647055</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE حرام ولا حلال؟</t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>1776423145000</v>
+        <v>1776680656000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1450,64 +1446,69 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGhQnfXsAAHpYo.jpg', 'type': 'photo', 'id': '2045093012653453312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Gamin Niu', 'screenName': 'GaminNiukkua', 'followersCount': 2, 'favouritesCount': 941, 'friendsCount': 16, 'description': ''}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>862354</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>46129.61973379629</v>
+        <v>46132.60018518518</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046176687994376576</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2046176687994376576</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
+          <t>@GaminNiukkua مرحبا شكرا لتواصلك معنا يمكنك مراجعه التفاصيل من خلال زياره هذا الرابط 
+https://t.co/7964Z6bRKk</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1776680212000</v>
+        <v>1776681513000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1521,11 +1522,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1538,50 +1539,53 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>137</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046173095581647055</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46132.59504629629</v>
+        <v>46132.61010416667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2046175033328890208</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1776681118000</v>
+        <v>1776684807000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046190505554321598</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1591,7 +1595,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1608,107 +1612,311 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>46132.6055324074</v>
+        <v>46132.64822916667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1776680379000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2046171931813011938</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39177, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>46132.59697916666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1776680212000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>46132.59504629629</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2046175033328890208</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1776681118000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2045093015459352679</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2046171233243541979</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46132.6055324074</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2046167018303602898</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2046167018303602898</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
 With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F21" t="n">
         <v>1776679207000</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2046167018303602898</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" s="2" t="n">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
         <v>46132.58341435185</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2046167018303602898</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>2046118862736003268</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
 Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
@@ -1716,408 +1924,336 @@
 https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F22" t="n">
         <v>1776667726000</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>2046118862736003268</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" s="2" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
         <v>46132.45053240741</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2046061240511082734</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2046061240511082734</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1776653988000</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'name': 'Rashed Sem', 'screenName': 'she7ii88', 'followersCount': 9, 'favouritesCount': 303, 'friendsCount': 49, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46132.29152777778</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2046166030557614556</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>2046166030557614556</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
 https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F23" t="n">
         <v>1776678972000</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>2046166030557614556</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195567, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>51</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>8330</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
+      <c r="M23" t="n">
+        <v>52</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>8379</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
         <v>46132.58069444444</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2046166030557614556</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>2046265860453761085</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>🚨 End of Mike Hesson 🚨
 - PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>1776702773000</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2046265860453761085</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174811, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>29</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" t="n">
-        <v>38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>752</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>35692</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
+      <c r="J24" t="n">
+        <v>31</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>41</v>
+      </c>
+      <c r="M24" t="n">
+        <v>785</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>38069</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
         <v>46132.85616898148</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2046033950339166455</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2046033950339166455</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
 https://t.co/H82MnfRa04</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>1776647481000</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>2046033950339166455</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
         <v>46132.21621527777</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2046033950339166455</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2046424774474391989</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://x.com/Kyodonews_JBN/status/2046424774474391989</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Singapore imagines new ways of living at Milan Design Week with the opening of Prototype Island【DesignSingapore Council】
 https://t.co/SxdfkcpvgF</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>1776740661000</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2046424774474391989</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="n">
         <v>46133.2946875</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
 أجب واربح 
@@ -2135,584 +2271,444 @@
 مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F27" t="n">
         <v>1776239183000</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137563, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137558, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
         <v>393</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>69</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M27" t="n">
         <v>206</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>1435284</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1440032</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
         <v>46127.49054398148</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
 كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>1776442857000</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>46129.84788194444</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>1776669394000</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>46132.46983796296</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
 تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
 كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>1776692805000</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>46132.74079861111</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2046217543870738694</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
 Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
 Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F31" t="n">
         <v>1776337169000</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>4</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>6419</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" s="2" t="n">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="2" t="n">
         <v>46128.62464120371</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2046217543870738694</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2044758862017007662</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://x.com/RakeshMavath/status/2044758862017007662</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>@aaditsh @emiratesislamic especially now they are not going to let go of your business easily. you can raise the issue with UAECB who will in turn contact the bank</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F32" t="n">
         <v>1776343477000</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>46128.69765046296</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2046217543870738694</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>2044759599656689929</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>@RakeshMavath @emiratesislamic Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
 And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F33" t="n">
         <v>1776343653000</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>2044732404938702855</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2044758862017007662</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>46128.6996875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2046217543870738694</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2044832798670995759</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1776361105000</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2044732404938702855</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2044759599656689929</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>46128.90167824074</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2046217543870738694</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2046217543870738694</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/aaditsh/status/2046217543870738694</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>@RakeshMavath @emiratesislamic Alright. Will do! Thanks.</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>1776691253000</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2044732404938702855</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523004, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2725,61 +2721,60 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2044832798670995759</t>
+          <t>2044758862017007662</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46132.72283564815</v>
+        <v>46128.6996875</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
- #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
+          <t>@aaditsh @emiratesislamic Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1776674710000</v>
+        <v>1776361105000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2792,61 +2787,64 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2044759599656689929</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n">
-        <v>46132.53136574074</v>
+        <v>46128.90167824074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2046148194392740002</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
-#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
+          <t>@RakeshMavath @emiratesislamic Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1776674719000</v>
+        <v>1776691253000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523000, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2859,20 +2857,20 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2046148156560121974</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46132.53146990741</v>
+        <v>46132.72283564815</v>
       </c>
     </row>
     <row r="36">
@@ -2936,7 +2934,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -3002,7 +3000,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3017,25 +3015,163 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1776674710000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148122250809344/pu/img/WEGHCsaWoyjDb-ot.jpg', 'type': 'video', 'id': '2046148122250809344'}]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
+        <v>46132.53136574074</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2046148194392740002</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth https://t.co/udWgfz8rNb</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1776674719000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046148161090068480/pu/img/GpPJv5a4DR5wZAQc.jpg', 'type': 'video', 'id': '2046148161090068480'}]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46132.53146990741</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
 Do not fall for the traps. Stay alert to scams.
@@ -3044,136 +3180,136 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F40" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2046106592232214645</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" s="2" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
 مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
 ✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="F41" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="2" t="n">
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>✔️ متابعة استثماراتك لحظة بلحظة
 ✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
@@ -3183,143 +3319,143 @@
 https://t.co/PgcKVmrsKA</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F42" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="P40" s="2" t="n">
+      <c r="P42" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
 ✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="F43" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="P43" s="2" t="n">
         <v>46132.41668981482</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2046106600142725209</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>✔️ Track your investments in real time
 ✔️ Get smart insights to guide your decisions
@@ -3329,72 +3465,72 @@
 https://t.co/BZed26iXDD</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F44" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="P44" s="2" t="n">
         <v>46132.41668981482</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3404,72 +3540,72 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>1776690722000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
         </is>
       </c>
-      <c r="P43" s="2" t="n">
+      <c r="P45" s="2" t="n">
         <v>46132.71668981481</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
 ✅ بدون رسوم عضوية سنوية
@@ -3477,68 +3613,68 @@
 🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F46" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="2" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
         <v>46132.71599537037</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2046215063929749703</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>🚗 خدمة صف السيارات
 🛫 الدخول إلى صالات المطارات
@@ -3548,72 +3684,72 @@
 https://t.co/WJhVBxsiSW</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F47" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P47" s="2" t="n">
         <v>46132.71599537037</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2044702429464441285</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>@emiratesislamic 
 السلام عليكم
@@ -3624,138 +3760,138 @@
 او عدم هو اهتمام بالعملاء</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="F48" t="n">
         <v>1776330022000</v>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" s="2" t="n">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
         <v>46128.5419212963</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F49" t="n">
         <v>1776337725000</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="P47" s="2" t="n">
+      <c r="P49" s="2" t="n">
         <v>46128.63107638889</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045014720416186802</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>@emiratesislamic تم امس التواصل معي من عندكم
 سألني عن تاريخ الميلاد
@@ -3769,143 +3905,143 @@
 في انتظار الحل!!!</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F50" t="n">
         <v>1776404478000</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2044734739718824109</t>
         </is>
       </c>
-      <c r="P48" s="2" t="n">
+      <c r="P50" s="2" t="n">
         <v>46129.40368055556</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F51" t="n">
         <v>1776409547000</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>2045014720416186802</t>
         </is>
       </c>
-      <c r="P49" s="2" t="n">
+      <c r="P51" s="2" t="n">
         <v>46129.46234953704</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>2045418169452695808</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045418169452695808</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
 مع الأسف لايوجد متابعة لطلب من الفرع
@@ -3915,702 +4051,702 @@
 متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F52" t="n">
         <v>1776500668000</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J52" t="n">
         <v>1</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>46130.51699074074</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F53" t="n">
         <v>1776671148000</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>2045418169452695808</t>
         </is>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>46132.49013888889</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>2046181231432495104</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2046181231432495104</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>@emiratesislamic ردكم لم يحرك ساكن 
  إنجاز المعاملة إلى اليوم صفر</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F54" t="n">
         <v>1776682596000</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="P52" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>46132.62263888889</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>1776687234000</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>2046181231432495104</t>
         </is>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P55" s="2" t="n">
         <v>46132.67631944444</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1776584832000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4615, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>46131.49111111111</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1776678723000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46132.5778125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>2046200603928338537</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2046139112361717905</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>@emiratesislamic 
 منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
 هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F58" t="n">
         <v>1776672554000</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
         <v>46132.50641203704</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>2046200603928338537</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>2046200603928338537</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F59" t="n">
         <v>1776687215000</v>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>2046139112361717905</t>
         </is>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="P59" s="2" t="n">
         <v>46132.67609953704</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2046164985571598514</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1776584832000</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1776676254000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4614, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" s="2" t="n">
-        <v>46131.49111111111</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2046164985571598514</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2046164985571598514</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1776678723000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46132.5778125</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46132.54923611111</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>2046200645498130445</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2046154630548402178</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1776676254000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>46132.54923611111</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2046200645498130445</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2046200645498130445</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F61" t="n">
         <v>1776687225000</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t>2046154630548402178</t>
         </is>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P61" s="2" t="n">
         <v>46132.67621527778</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>2046125833811615920</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -4618,68 +4754,68 @@
 💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F62" t="n">
         <v>1776420809000</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J62" t="n">
         <v>2</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>1</v>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="n">
         <v>46129.59269675926</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>2046125833811615920</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>2045083221952532551</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
 Valid until 30 June 2026.
@@ -4687,218 +4823,78 @@
 https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F63" t="n">
         <v>1776420810000</v>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>2045083218303402442</t>
         </is>
       </c>
-      <c r="P61" s="2" t="n">
+      <c r="P63" s="2" t="n">
         <v>46129.59270833333</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2046125833811615920</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2045521200613560345</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/gassann20203/status/2045521200613560345</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>@emiratesislamic It's fake prize from 15 year u have account with u never ever I trusted u and today after removing otp u start steel the money from account</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1776525232000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>46130.8012962963</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2046125833811615920</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2046125833811615920</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1776669388000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2045521200613560345</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46132.46976851852</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2046125792552222931</t>
+          <t>2046125833811615920</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2045520833406464393</t>
+          <t>2045521200613560345</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/gassann20203/status/2045520833406464393</t>
+          <t>https://x.com/gassann20203/status/2045521200613560345</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
+          <t>@emiratesislamic It's fake prize from 15 year u have account with u never ever I trusted u and today after removing otp u start steel the money from account</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1776525145000</v>
+        <v>1776525232000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4929,37 +4925,37 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2045083218303402442</t>
+          <t>2045083221952532551</t>
         </is>
       </c>
       <c r="P64" s="2" t="n">
-        <v>46130.80028935185</v>
+        <v>46130.8012962963</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2046125792552222931</t>
+          <t>2046125833811615920</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2046125792552222931</t>
+          <t>2046125833811615920</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4968,7 +4964,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1776669378000</v>
+        <v>1776669388000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4999,40 +4995,180 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2045520833406464393</t>
+          <t>2045521200613560345</t>
         </is>
       </c>
       <c r="P65" s="2" t="n">
-        <v>46132.46965277778</v>
+        <v>46132.46976851852</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045520833406464393</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1776525145000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>46130.80028935185</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1776669378000</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>46132.46965277778</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>2046106592135831614</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>2046106592135831614</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
 لا تقع في الفخ. احذر الاحتيال.
@@ -5040,43 +5176,43 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F68" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>2046106592135831614</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,115 +517,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Emirates NBD secures $750m AT1 bond in first GCC debt deal since February
-Read the full story ➡ https://t.co/f2uzKriH3Q
-#EmiratesNBD #DubaiFinance #AT1Issuance #GCCMarkets #BankingNews #UAEEconomy https://t.co/zsvXNiOlyY</t>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777604630000</v>
+        <v>1773832238000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHM8Qh5bgAALRPt.jpg', 'type': 'photo', 'id': '2050048510058528768'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Middle East News 247', 'screenName': 'menews247', 'followersCount': 223, 'favouritesCount': 232, 'friendsCount': 11, 'description': 'News, trends, and insights for the Middle East region.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46143.29432870371</v>
+        <v>46099.63238425926</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2050050326774903170</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050050326774903170</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIFC launches public consultation on revised Prescribed Company Regulations
-Read the full story ➡ https://t.co/0lnO6j8o3D
-#DIFC #Dubai #Finance #Regulations #Business #UAE https://t.co/QcfjNZwmDX</t>
+          <t>@EmiratesNBD_AE @Bushrasabih1 👍</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777605060000</v>
+        <v>1777684200000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2050050326774903170</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHM95n3bQAEh-pM.jpg', 'type': 'photo', 'id': '2050050315547000833'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Middle East News 247', 'screenName': 'menews247', 'followersCount': 223, 'favouritesCount': 232, 'friendsCount': 11, 'description': 'News, trends, and insights for the Middle East region.'}</t>
+          <t>{'name': 'Bu_shaikh🌸❤️', 'screenName': 'Bushrasabih2', 'followersCount': 244, 'favouritesCount': 5862, 'friendsCount': 540, 'description': 'الحمدلله'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -640,115 +643,118 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2034225964863893587</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46143.29930555556</v>
+        <v>46144.21527777778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049427338119557617</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049379193910165928</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Follow these simple steps to access the Voyager Travel Portal and start exploring.
-Apply Now at https://t.co/UGR3KI4NhM https://t.co/klrBtm1x0Q</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777456528000</v>
+        <v>1777445050000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHEHTXNWIAAAvD9.jpg', 'type': 'video', 'id': '2049427279692943360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174560, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12</v>
-      </c>
       <c r="M4" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>572459</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46141.58018518519</v>
+        <v>46141.44733796296</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/STKgenghis/status/2049468314699825596</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE سونيويلكم</t>
+          <t>@EmiratesNBD_AE would not recommend bank that suspends 40 year old accounts wout notification. Only found out when i temp blocked credit card i thought id misplaced. It cant be unblocked because of suspension...
+deprived of services no notification  told KYC take 8-10 buss days 2 get back. So..</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777596744000</v>
+        <v>1777466298000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -758,11 +764,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'ummayed.666', 'screenName': 'Ummayed666', 'followersCount': 44, 'favouritesCount': 158, 'friendsCount': 176, 'description': ''}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -775,123 +781,120 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46143.20305555555</v>
+        <v>46141.69326388889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049368082779394430</t>
+          <t>https://x.com/STKgenghis/status/2049469132337561727</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Have you received an email about a Golden Visa? Before you get excited, pause for a moment. -You’re looking at three emails - two are legitimate, and one is designed to steal your data. -Can you identify the fraudulent one?
-Share your answer in the comments and stand the chance to win AED 2,000.
-#UnitedAgainstFraud</t>
+          <t>@EmiratesNBD_AE O and also after emails customer support has yet to issue a complaint number. No logging = no complaint. The perfect system.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777442401000</v>
+        <v>1777466493000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHAKjlHXsAA394W.jpg', 'type': 'video', 'id': '2049149365818728448'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174560, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2049468314699825596</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>46141.41667824074</v>
+        <v>46141.69552083333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049469842646818920</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD 
-@EmiratesNBD_AE</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1004599 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777577021000</v>
+        <v>1777466662000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -901,11 +904,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -918,53 +921,50 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46142.97478009259</v>
+        <v>46141.69747685185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932465704456686</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2049932465704456686</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2049932465704456686</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932465704456686</t>
+          <t>https://x.com/STKgenghis/status/2049470212714737829</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD
-@EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE I will give this a try but am not holding my breath.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777576960000</v>
+        <v>1777466750000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -974,11 +974,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -991,52 +991,50 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46142.97407407407</v>
+        <v>46141.69849537037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932218081095958</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2049932218081095958</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2049932218081095958</t>
+          <t>2049472842727665850</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932218081095958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049472842727665850</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>@STKgenghis Hi khana! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004599 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1777576901000</v>
+        <v>1777467377000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1046,11 +1044,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1063,119 +1061,120 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46142.9733912037</v>
+        <v>46141.70575231482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Universal_USDU/status/2016771897816645888</t>
+          <t>https://x.com/STKgenghis/status/2049474377788604862</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universal launches USDU - the UAE’s first Central Bank-registered USD stablecoin.
-Issued by an FSRA-regulated entity in @ADGlobalMarket, USDU is supported by banking partners @EmiratesNBD_AE , @MashreqTweets, and @almaryahbank with global distribution via @aquanow, and alignment with the UAE’s AED ecosystem through @AECoin_UAE.
-Built for regulated digital asset settlement.
-🔗Press release: https://t.co/R5ypIoHbxM</t>
+          <t>@EmiratesNBD_AE Done. As I said not holding breath.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1769670864000</v>
+        <v>1777467743000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2016768856669511680/img/KCUOpCUXTpHGeDMT.jpg', 'type': 'video', 'id': '2016768856669511680'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Universal', 'screenName': 'Universal_USDU', 'followersCount': 124, 'favouritesCount': 23, 'friendsCount': 18, 'description': 'FSRA-regulated ADGM issuer of USDU, a USD-backed stablecoin registered with the Central Bank of the UAE for regulated digital asset settlement.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1573</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2049472842727665850</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n">
-        <v>46051.46833333333</v>
+        <v>46141.70998842592</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2049475517070348292</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049475517070348292</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Very refined presentation, nice job. 🚀</t>
+          <t>@STKgenghis Hello, we will check the email and update you shortly.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777564062000</v>
+        <v>1777468015000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1185,11 +1184,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Crypto Lady', 'screenName': 'DaCryptoLady_', 'followersCount': 451183, 'favouritesCount': 115866, 'friendsCount': 38989, 'description': 'Crypto lover💕| $SOL investor | WEB3 Creator | Growth 👩🏽\u200d💻 | DM for Marketing Inquiries &amp; Business | #DYOR'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1202,119 +1201,122 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46142.82479166667</v>
+        <v>46141.71313657407</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
-Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
-Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
-@EmiratesNBD_AE @Visa</t>
+          <t>@EmiratesNBD_AE So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777558260000</v>
+        <v>1777535453000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKFRgnaEAAYS6w.jpg', 'type': 'photo', 'id': '2049847316266487808'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'سيف الدرعي| Saif alderei', 'screenName': 'saif_aldareei', 'followersCount': 91398, 'favouritesCount': 44750, 'friendsCount': 1461, 'description': 'إماراتي 🇦🇪.. صوت فخر وهوية، أكتب بلسان الوطن وأصون الحق العربي. شغوف بالسياسة والدبلوماسية، دار زايد نهجي ..'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2049475517070348292</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="n">
-        <v>46142.75763888889</v>
+        <v>46142.49366898148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2049854802947940358</t>
+          <t>2049759572416495861</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/D10oaa/status/2049854802947940358</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049759572416495861</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@saif_aldareei والله يفرح القلب</t>
+          <t>@STKgenghis We are extremely sorry and we have escalated the matter and will reply to your email as soon as possible with an update.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777558444000</v>
+        <v>1777535739000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1324,11 +1326,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Doaa', 'screenName': 'D10oaa', 'followersCount': 69, 'favouritesCount': 869, 'friendsCount': 129, 'description': 'ماعندي اعداء بحياتي غير  اللي ببجي .'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1341,50 +1343,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46142.75976851852</v>
+        <v>46142.49697916667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2049854823411933347</t>
+          <t>2049927131657081284</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/BRANDONFI23/status/2049854823411933347</t>
+          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@saif_aldareei برافو</t>
+          <t>@EmiratesNBD_AE Right. So its now almost 14 days with credit card not functioning.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777558449000</v>
+        <v>1777575688000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1394,11 +1396,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'نوره الرشيدي', 'screenName': 'BRANDONFI23', 'followersCount': 98, 'favouritesCount': 1100, 'friendsCount': 104, 'description': 'يكفيك في هذه الدنيا أن يتذكرك أحدهم في مكان ما من العالم ثم يبتسم ، ويكفي أن تكون ذكرى جميلة في ذاكرة أحدهم .'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1411,54 +1413,50 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049759572416495861</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46142.75982638889</v>
+        <v>46142.95935185185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2049948361885720783</t>
+          <t>2050063207486587148</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/wajdi_6/status/2049948361885720783</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050063207486587148</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>كيف تعرف أن الشخص #قوي أم يتظاهر؟ 💪
-1. مواقفه
-2. صمته
-3. تحمله
-4. إحساسك</t>
+          <t>@STKgenghis Please note that our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777580750000</v>
+        <v>1777608131000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2049948361885720783</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1468,53 +1466,69 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'wajdi سؤال وجواب', 'screenName': 'wajdi_6', 'followersCount': 24288, 'favouritesCount': 166949, 'friendsCount': 8438, 'description': 'قل الله ينجيكم منها ومن كل كرب\n\nمبرمج لغة php والبايثون + تصميم مواقع'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2049927131657081284</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>46143.01793981482</v>
+        <v>46143.33484953704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2050170081574056214</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>https://x.com/STKgenghis/status/2050170081574056214</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I dont think you appreciate where this places me through no fault of mine. I have had several subscriptions stopped because card is blocked. A monthly payment didnt go through - i am facing a fine.  OVER TWO WEEKS since i asked for my card to be blocked as a precaution !????</t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>1777607983348</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>1777633612000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1522,51 +1536,67 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2050063207486587148</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>46143.33314060186</v>
+        <v>46143.62976851852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
+          <t>2050275701312324065</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275701312324065</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@t_Duches @SalmaCocomoney What bank do you use. Hsbc abi DIB abi Emirates NBD abi Mashreq. Na Hsbc I dey use that year😎</t>
+          <t>@STKgenghis We apologize for the inconvenience, our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777558904000</v>
+        <v>1777658794000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2049851769593921909</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1576,11 +1606,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': '𝐃𝐚𝐝𝐝𝐲 𝐅𝐞𝐫𝐧𝐚𝐧𝐝𝐞𝐳 ⭐️', 'screenName': 'Froshbankss', 'followersCount': 1962, 'favouritesCount': 7258, 'friendsCount': 1872, 'description': '𝐏𝐥𝐮𝐯𝐢𝐨𝐩𝐡𝐢𝐥𝐞, 𝐀𝐬𝐭𝐫𝐨𝐩𝐡𝐢𝐥𝐞, 𝐄𝐜𝐜𝐞𝐝𝐞𝐧𝐭𝐞𝐬𝐢𝐚𝐬𝐭. Owner of Froshluxe wears, where quality clothings meet good vibes 😎. #CFC🤍💙'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1593,62 +1623,60 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2049851769593921909</t>
+          <t>2050170081574056214</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46142.76509259259</v>
+        <v>46143.92122685185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Visa appoints Emirates NBD as UAE NNSS agent, enabling faster domestic card settlements in dirhams and boosting payment efficiency.
-https://t.co/yy0VYtPQ4n
-#Visa #EmiratesNBD #DigitalPayments #NNSSAgent #AEDTransactions #GCCBusinessNews @EmiratesNBD_AE https://t.co/GE4ETgCNup</t>
+          <t>@EmiratesNBD_AE Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777556594000</v>
+        <v>1777682263000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKFAwEb0AA8ePZ.jpg', 'type': 'photo', 'id': '2049847028356993024'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 485, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1665,133 +1693,131 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="n">
-        <v>46142.73835648148</v>
+        <v>46144.1928587963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2049902278983975149</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049902278983975149</t>
+          <t>https://x.com/CaVivekkhatri/status/1880843050014089636</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DIFC opens public consultation on amended Prescribed Company regulations, expanding access and roles for corporate service providers.
-https://t.co/LBv5b09AVg
-#DIFC #PrescribedCompanyRegulations #CorporateServiceProviders #PCRegulations #Dubai #GCCBusinessNews
-@DIFC https://t.co/vvWfJBcX3G</t>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777569763000</v>
+        <v>1737262902000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2049902278983975149</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHK3PFCaoAEGPHM.jpg', 'type': 'photo', 'id': '2049902250085228545'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 485, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
+          <t>{'name': 'CA Vivek Khatri', 'screenName': 'CaVivekkhatri', 'followersCount': 219630, 'favouritesCount': 52078, 'friendsCount': 161, 'description': 'Daily Threads &amp; Learning Articles | Algo Trader &amp; Investor | Macro l Building Wealth Community l Founder &amp; Partner @Stocki_zen –SEBI RA Firm (INH000017675)'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>89863</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>46142.89077546296</v>
+        <v>45676.37618055556</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UAE News Highlights – May 2026
-Fuel: Diesel holds at 4.69. Petrol 98: 3.66 | 95: 3.55 | 91: 3.48.
-Security: Central Bank bans WhatsApp for banking; stick to official portals only.
-Finance: Emirates NBD x Visa partnership goes local for faster payments.
-* https://t.co/t0NMTDrBeh</t>
+          <t>@CaVivekkhatri RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777557465000</v>
+        <v>1777688375000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKISuZbEAAH7Bt.jpg', 'type': 'photo', 'id': '2049850635680681984'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKIUONbQAAxArj.jpg', 'type': 'photo', 'id': '2049850661400166400'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': "Jami's Nest", 'screenName': 'Jami076152121', 'followersCount': 58, 'favouritesCount': 21722, 'friendsCount': 1447, 'description': 'NMIMS, Entrepreneur,Consumer Guidance society.\nEquityTA, Country music, Health&amp;Fitness Wiz.'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1804,48 +1830,52 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1880843050014089636</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="n">
-        <v>46142.7484375</v>
+        <v>46144.26359953704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2049850859971100900</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850859971100900</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>**Travel: 40+ new daily flights via Air India Express. Entertainment: Rashed Al Majed live at Etihad Arena tonight (7:30 PM).
-Trust the experts for your UAE needs.
-Contact Desea: +971 56 296 8027 | +971 58 533 2900  https://t.co/EQd4bfIpRG</t>
+          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
+Emirates NBD – Dammam Branch | Financial Consultant
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1777557504000</v>
+        <v>1777680009000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1855,11 +1885,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': 'Yasmeen Aljadah', 'screenName': 'yasmeenalja', 'followersCount': 188, 'favouritesCount': 20, 'friendsCount': 33, 'description': 'ياسمين\nمستشارة التمويل الشخصي – بنك الإمارات دبي الوطني فرع الدمام \nأساعدك تختار الحل المناسب لك بكل وضوح وسهولة 💸\n📩 تواصل خاص'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1872,117 +1902,117 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2049850698876223572</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46142.74888888889</v>
+        <v>46144.16677083333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2049805562968465634</t>
+          <t>2050357066875748710</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049805562968465634</t>
+          <t>https://x.com/yasmeenalja/status/2050357066875748710</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Numbers don't lie. Abu Dhabi real estate is on the rise. 
-With a projected 12-16% price increase by year-end and unrivaled rental yields, the scarcity premium in Abu Dhabi is real. Secure your 10-year Golden Visa and capitalize on the 96% occupancy rate in high-volume areas. https://t.co/dVu1vBhEJc</t>
+          <t>ياسمين صالح
+📞 0552891984
+🏦 بنك الإمارات دبي – فرع الدمام
+#تمويل #قروض #بدون_تحويل_راتب #السعودية https://t.co/t5wubHztjE</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1777546704000</v>
+        <v>1777678193000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2049805562968465634</t>
+          <t>2050357066875748710</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfKTgakAAuT1P.jpg', 'type': 'photo', 'id': '2049805411046559744'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfPqia4AEusWM.jpg', 'type': 'photo', 'id': '2049805503128330241'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfRPibsAAF_Co.jpg', 'type': 'photo', 'id': '2049805530240364544'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfSbDbMAAATJN.jpg', 'type': 'photo', 'id': '2049805550511403008'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHRU4egWIAAB2vK.jpg', 'type': 'photo', 'id': '2050357059598557184'}]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': 'Yasmeen Aljadah', 'screenName': 'yasmeenalja', 'followersCount': 188, 'favouritesCount': 20, 'friendsCount': 33, 'description': 'ياسمين\nمستشارة التمويل الشخصي – بنك الإمارات دبي الوطني فرع الدمام \nأساعدك تختار الحل المناسب لك بكل وضوح وسهولة 💸\n📩 تواصل خاص'}</t>
         </is>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>73</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46142.62388888889</v>
+        <v>46144.14575231481</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/apex_led/status/2049804951631900789</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2049804951631900789</t>
+          <t>2050373118900977885</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2049804951631900789</t>
+          <t>2050373118900977885</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/apex_led/status/2049804951631900789</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777546558000</v>
+        <v>1777682020000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1992,7 +2022,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Mr Victor Crypto', 'screenName': 'apex_led', 'followersCount': 362524, 'favouritesCount': 66939, 'friendsCount': 23897, 'description': 'Long-term Crypto Vision 🌐 | DeFi, Blockchain &amp; Conservative Crypto 🔥 | Dm for business | #BTC #ETH #SOL #DOGE'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2009,50 +2039,50 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050275701312324065</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46142.62219907407</v>
+        <v>46144.19004629629</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/safakayani1/status/2049806132303258013</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2049806132303258013</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2049806132303258013</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/safakayani1/status/2049806132303258013</t>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777546840000</v>
+        <v>1777613768000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2049806132303258013</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2062,11 +2092,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': '+92', 'screenName': 'safakayani1', 'followersCount': 1177, 'favouritesCount': 60288, 'friendsCount': 681, 'description': 'adulting | founder @holdswl'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2079,46 +2109,46 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" s="2" t="n">
-        <v>46142.62546296296</v>
+        <v>46143.40009259259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/safakayani1/status/2049806132303258013</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2049806132303258013</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2049934012417007722</t>
+          <t>2050093026182131824</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/safakayani1/status/2049934012417007722</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Reels Ghoomte Ghoomte Pta nahi chalta roz Kerala pohanch jati hoon</t>
+          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777577329000</v>
+        <v>1777615240000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2049934012417007722</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2128,11 +2158,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': '+92', 'screenName': 'safakayani1', 'followersCount': 1177, 'favouritesCount': 60288, 'friendsCount': 681, 'description': 'adulting | founder @holdswl'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2141,65 +2171,68 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2050086851621593314</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="n">
-        <v>46142.97834490741</v>
+        <v>46143.41712962963</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777545300000</v>
+        <v>1777646110000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJZ77wWUAAPXXa.jpg', 'type': 'photo', 'id': '2049799666594631680'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJZ8OjWgAAcd41.jpg', 'type': 'photo', 'id': '2049799671640391680'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174560, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2212,143 +2245,135 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2050093026182131824</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="n">
-        <v>46142.60763888889</v>
+        <v>46143.77442129629</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050275958674932182</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in https://t.co/tewFiex0BH vouchers.
-Access benefits like:
-- AED 300 https://t.co/tewFiex0BH voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 https://t.co/tewFiex0BH voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: https://t.co/muX7gaxwoT
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من https://t.co/tewFiex0BH بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة https://t.co/tewFiex0BH بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة https://t.co/tewFiex0BH بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: https://t.co/au9YcHMBrP</t>
+          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777547024000</v>
+        <v>1777658855000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJggwbXwAAQLLo.jpg', 'type': 'photo', 'id': '2049806896278781952'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJgg-eXcAA73o8.jpg', 'type': 'photo', 'id': '2049806900049440768'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174560, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2050222500295123129</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="n">
-        <v>46142.62759259259</v>
+        <v>46143.92193287037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2049802474387566693</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2049802474387566693</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050224474650181731</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on spends of AED 50 and above with your Emirates NBD card.
-Learn More: https://t.co/zeINKlJVvn https://t.co/QhWQTFy8YP</t>
+          <t>قبل أي خطوة، استشر المختصين📱
+تواصل مع المستشار الائتماني في ⁧#بنك_الإمارات_دبي_الوطني⁩ وخذ القرار بثقة✨ https://t.co/lJ3j6amaZa</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777545968000</v>
+        <v>1777646580000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2049802474387566693</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJcfOsWAAEGrDR.jpg', 'type': 'photo', 'id': '2049802471996784641'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKuIqgXsAAi-Jy.jpg', 'type': 'photo', 'id': '2049892244279242752'}]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2361,62 +2386,61 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>374</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46142.61537037037</v>
+        <v>46143.77986111111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2049802474387566693</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2049690099617857683</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2049690099617857683</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
+          <t>@EmiratesNBD_KSA السلام عليكم، هل يوجد خصومات بالتعاون مع اي شركات مبيعات الاكترونيات قريبا
+فقدناكم بين البنوك الثانية</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777519175000</v>
+        <v>1777647297000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2049690099617857683</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHH2R0ZakAAKlsR.jpg', 'type': 'photo', 'id': '2049690091413737472'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Mohammad S.', 'screenName': 'MohSSD4', 'followersCount': 87, 'favouritesCount': 931, 'friendsCount': 161, 'description': "I trust everyone, it's the devil inside them I don't trust\nلايوجد شيء اسمه دين، جنس، لون، اصل او حتى مكان سيء, بل يوجد شخص جيد او شخص سيء"}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2425,61 +2449,65 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2050224474650181731</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46142.3052662037</v>
+        <v>46143.78815972222</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2049720588764377543</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2049720588764377543</t>
+          <t>2050233737401479508</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050233737401479508</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
+          <t>@MohSSD4 مرحباً بك, يمكنك الأن معرفة المزيد عن العروض والخصومات من خلال الضغط على الرابط ادناه.
+https://t.co/ANkkIZKNb4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1777526444000</v>
+        <v>1777648789000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2049720588764377543</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIR_xObIAAzv8v.jpg', 'type': 'photo', 'id': '2049720567650263040'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'ArabianBusiness.com', 'screenName': 'ArabianBusiness', 'followersCount': 83040, 'favouritesCount': 413, 'friendsCount': 14, 'description': 'https://t.co/gfzSi29ov5'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2489,67 +2517,71 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2050227480842154486</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>46142.38939814815</v>
+        <v>46143.80542824074</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2049721813379522964</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2049721813379522964</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
+          <t>@EmiratesNBD_KSA , I have a credit card that I can't use for international transactions. My complaint was raised and closed without a solution (22667042570). Domestic transactions are also being declined. Are you restricting my usage? https://t.co/3tBz51OQPM</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1777526736000</v>
+        <v>1777646860000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2049721813379522964</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHPdW1aWMAAuulT.jpg', 'type': 'photo', 'id': '2050225639748153344'}]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93536, 'favouritesCount': 19507, 'friendsCount': 106572, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'Sohan 🇮🇳 ಸೋಹನ್', 'screenName': 'sanju_soh1', 'followersCount': 170, 'favouritesCount': 1957, 'friendsCount': 382, 'description': 'Proud Bengaluru resident with a vision to make our city the ultimate global gem! Pushing for public transport to create a swift, sustainable urban paradise.'}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2558,50 +2590,50 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>46142.39277777778</v>
+        <v>46143.78310185186</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2049721813379522964</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2050051295571268076</t>
+          <t>2050229504618991913</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2050051295571268076</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050229504618991913</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ferrari World Yas Island, Abu Dhabi’s Formula Rossa Achieves Guinness World Records™ Title For Fastest Rollercoaster Launch https://t.co/mpAE7sutEu</t>
+          <t>@sanju_soh1 Hello, we're sorry to hear you're having an unpleasant experience. We're happy to help and resolve it. Please send details of your complaint via private message so we can assist you better.</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1777605291000</v>
+        <v>1777647779000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2050051295571268076</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2611,7 +2643,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93536, 'favouritesCount': 19507, 'friendsCount': 106572, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2624,50 +2656,56 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2050225649172832351</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n">
-        <v>46143.30197916667</v>
+        <v>46143.79373842593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214078409527791</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
+          <t>Extremely Disappointed with ENBD @EmiratesNBD_AE Services
+I raised case in Sep 2025. Partial recovery was done by Dec, then the case was closed and new one was reopened. That too got closed in March without full recovery and without my consent.
+Dispute ref. 230952198951</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1777528366000</v>
+        <v>1777644102000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2677,11 +2715,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'jibin', 'screenName': 'jibinsymphony', 'followersCount': 99, 'favouritesCount': 5, 'friendsCount': 231, 'description': ''}</t>
+          <t>{'name': 'Usman Chaudhry', 'screenName': 'iUsmanChaudhary', 'followersCount': 1540, 'favouritesCount': 129646, 'friendsCount': 4628, 'description': 'Oracle Certified Professional (Sr. Software Engineer )\n#Oracle | Oracle University\nاَلْحَمْدُ لِلّٰهِ من جانبازم.'}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2694,46 +2732,50 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46142.41164351852</v>
+        <v>46143.75118055556</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2049737455960809521</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/jibinsymphony/status/2049737455960809521</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>@OfficialADCB</t>
+          <t>An amount is still pending, and there’s been no proper follow-up or support.
+Expected much better transparency and accountability from a bank. please look into this urgently.
+@EmiratesNBD_AE
+@centralbankuae
+#ENBD #EmiratesNBD #CustomerService #CreditCardFraud #BankingExperience</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1777530466000</v>
+        <v>1777644102000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2743,11 +2785,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'jibin', 'screenName': 'jibinsymphony', 'followersCount': 99, 'favouritesCount': 5, 'friendsCount': 231, 'description': ''}</t>
+          <t>{'name': 'Usman Chaudhry', 'screenName': 'iUsmanChaudhary', 'followersCount': 1540, 'favouritesCount': 129646, 'friendsCount': 4628, 'description': 'Oracle Certified Professional (Sr. Software Engineer )\n#Oracle | Oracle University\nاَلْحَمْدُ لِلّٰهِ من جانبازم.'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2760,51 +2802,54 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46142.43594907408</v>
+        <v>46143.75118055556</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2049746300707520753</t>
+          <t>2050268003070271682</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/OfficialADCB/status/2049746300707520753</t>
+          <t>https://x.com/centralbankuae/status/2050268003070271682</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>@jibinsymphony Hi, thank you for reaching out. I’ve shared your matter with the concerned team, and you’ll be contacted shortly. To protect your privacy and maintain confidentiality, please refrain from sharing any personal or banking information on social media.
-R.B</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: https://t.co/Dptt9dWyCm 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1777532575000</v>
+        <v>1777656958000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2814,69 +2859,67 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'ADCB بنك أبوظبي التجاري', 'screenName': 'OfficialADCB', 'followersCount': 50751, 'favouritesCount': 1685, 'friendsCount': 0, 'description': 'نرحب بكم في الحساب الرسمي لبنك أبوظبي التجاري Welcome to Abu Dhabi Commercial Bank’s official Twitter account'}</t>
+          <t>{'name': 'Central Bank of the UAE', 'screenName': 'centralbankuae', 'followersCount': 6478, 'favouritesCount': 389, 'friendsCount': 213, 'description': 'الحساب الرسمي لمصرف الإمارات العربية المتحدة المركزي The official account of the Central Bank of the UAE'}</t>
         </is>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2049728649910497496</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46142.4603587963</v>
+        <v>46143.89997685186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/Emy191990/status/2049715289319723379</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2049715289319723379</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2049715289319723379</t>
+          <t>2050236953451188518</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/Emy191990/status/2049715289319723379</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050236953451188518</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>@iUsmanChaudhary We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1006207 in the subject line.</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1777525181000</v>
+        <v>1777649555000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2886,11 +2929,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Eman Mohamed', 'screenName': 'Emy191990', 'followersCount': 215, 'favouritesCount': 3984, 'friendsCount': 1364, 'description': '🌺 اللهم صلي وسلم وبارك على سيدنا محمد وآله وصحبه أجمعين 🌺'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2899,120 +2942,120 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>46142.37478009259</v>
+        <v>46143.81429398148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2049712002503999763</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2049379469551378526</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049379469551378526</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
+          <t>SEBI approves change in control for Emirates NBD Bank's preferential equity investment in RBL Bank; transaction pending other regulatory approvals.</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1777445115000</v>
+        <v>1777625449000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2049379469551378526</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHDbxAoXoAAvYB2.jpg', 'type': 'video', 'id': '2049379336847781888'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Hello Market', 'screenName': 'baro_jwngma', 'followersCount': 425, 'favouritesCount': 1706, 'friendsCount': 87, 'description': 'Stock Market | Business | Corporate Action | Value Investing | Basic Economics 📈 \n_ (Not SEBI RA)'}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46141.44809027778</v>
+        <v>46143.53528935185</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2049712002503999763</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2049712002503999763</t>
+          <t>2050142408357339369</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
+          <t>https://x.com/baro_jwngma/status/2050142408357339369</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Benefits of having borrowed money. Not earned</t>
+          <t>AWL Agri Business targets mid-teens volume growth, steady EBITDA per ton for edible oil, and EBITDA neutrality in food segment until FY27.</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1777524397000</v>
+        <v>1777627014000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2049379469551378526</t>
+          <t>2050142408357339369</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3022,7 +3065,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Smart green Landscape', 'screenName': 'Ahmed_44714', 'followersCount': 0, 'favouritesCount': 24, 'friendsCount': 57, 'description': 'Good and very good'}</t>
+          <t>{'name': 'Hello Market', 'screenName': 'baro_jwngma', 'followersCount': 425, 'favouritesCount': 1706, 'friendsCount': 87, 'description': 'Stock Market | Business | Corporate Action | Value Investing | Basic Economics 📈 \n_ (Not SEBI RA)'}</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3035,140 +3078,133 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2049379469551378526</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" s="2" t="n">
-        <v>46142.36570601852</v>
+        <v>46143.55340277778</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468522713462</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2049730468522713462</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2049730468522713462</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468522713462</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049458682694341011</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Scam messages often come from random or international numbers - not official IDs.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
+https://t.co/SzbRvQDh6V
+Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
+https://t.co/4VjReJkUUu</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1777528800000</v>
+        <v>1777464001000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2049730468522713462</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHEjz3MWYAANTmN.jpg', 'type': 'photo', 'id': '2049458679326334976'}]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>247827</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" s="2" t="n">
-        <v>46142.41666666666</v>
+        <v>46141.66667824074</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468522713462</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2049730468522713462</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2049775768025137608</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
+          <t>@EmiratesNBD_AE https://t.co/GZGbjrxpWb</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1777539600000</v>
+        <v>1777620084000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2049775768025137608</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2049762392007987200/pu/img/hUjmg8q1BluXAWbg.jpg', 'type': 'video', 'id': '2049762392007987200'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Dr:Mobark Ali', 'screenName': 'MabokM1849', 'followersCount': 254, 'favouritesCount': 868, 'friendsCount': 896, 'description': 'دكتور / مبارك أخصائي القلب والشريان 🌹'}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3177,133 +3213,134 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2049458682694341011</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n">
-        <v>46142.54166666666</v>
+        <v>46143.47319444444</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468916908361</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2049730468916908361</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2049730468916908361</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049730468916908361</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092857025757288</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Are you paying for something you don’t use?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>To limit online scam risks, just lower your card limits! With ENBD X App, you’re in control – reduce card limits anytime, anywhere! Stay one step ahead of fraud. Stay #UnitedAgainstFraud https://t.co/uTL4FBuhZu</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1777528800000</v>
+        <v>1777615200000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2049730468916908361</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049776489160126464/img/8bh7b27h1YuvE1BT.jpg', 'type': 'video', 'id': '2049776489160126464'}]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>645</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46142.41666666666</v>
+        <v>46143.41666666666</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049745585540894884</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2049745585540894884</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2049745576544084269</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049745576544084269</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
+          <t>@EmiratesNBD_AE Is the app down?</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1777532402000</v>
+        <v>1777619949000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2049745576544084269</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIovJFWkAAeGxZ.jpg', 'type': 'photo', 'id': '2049745570764328960'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIovUwWwAA1XNb.jpg', 'type': 'photo', 'id': '2049745573897486336'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Rasha Gh', 'screenName': 'rashagha', 'followersCount': 408, 'favouritesCount': 7742, 'friendsCount': 159, 'description': '🇱🇧\n🤍\n🇦🇪'}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3316,57 +3353,60 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2050092857025757288</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="n">
-        <v>46142.45835648148</v>
+        <v>46143.47163194444</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049745585540894884</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2049745585540894884</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2049745585540894884</t>
+          <t>2050118059285737835</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049745585540894884</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050118059285737835</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rank your debts, clear the smallest first, and roll that momentum over to the next. You don’t have to do it all at once, you just have to start with one. 
-#EmiratesIslamic https://t.co/GSuOwyUITc</t>
+          <t>@rashagha Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist. Please mention in the email subject social media case #1005963. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1777532404000</v>
+        <v>1777621209000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2049745576544084269</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIovp6XMAAyLnU.jpg', 'type': 'photo', 'id': '2049745579576602624'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIov2JWEAAxCVJ.jpg', 'type': 'photo', 'id': '2049745582860668928'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3383,65 +3423,64 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2049745576544084269</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46142.45837962963</v>
+        <v>46143.48621527778</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775771418308967</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2049775771418308967</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2049775767735722193</t>
+          <t>2050118024770822463</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775767735722193</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050118024770822463</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. https://t.co/M6BJYGU1xI</t>
+          <t>@rashagha Hi Rasha, thanks for reaching us, and we are extremely sorry for the inconvenience caused to you. Please note that our app is working fine. If you are facing any issue with the app,</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1777539600000</v>
+        <v>1777621201000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2049775767735722193</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2049627001242169344/pu/img/jTM3E4kxLuyz1LVV.jpg', 'type': 'video', 'id': '2049627001242169344'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3450,54 +3489,54 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2050112775310172515</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="n">
-        <v>46142.54166666666</v>
+        <v>46143.48612268519</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775771418308967</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2049775771418308967</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2049775771418308967</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775771418308967</t>
+          <t>https://x.com/chin2to/status/2043682357216149641</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1777539601000</v>
+        <v>1776086818000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2049775767735722193</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3507,11 +3546,11 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3524,90 +3563,1837 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2049775767735722193</t>
-        </is>
-      </c>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46142.54167824074</v>
+        <v>46125.72706018519</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775771397288351</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2049775771397288351</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2049775771397288351</t>
+          <t>2043691745330798829</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049775771397288351</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2043691745330798829</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>⭐️منتج متوافق مع أحكام الشريعة الإسلامية
-⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
-⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #996916 for us to assist you better. Thanks.</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1776089056000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>46125.75296296296</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was supposed to get a call for card cancellation in 2 days, been 4 and no one has bothered calling me yet. Trying to save the cancellation targets?</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1777618043000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2043691745330798829</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46143.44957175926</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2050106080517030039</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050106080517030039</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>@chin2to Hi Chintn, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1777618353000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46143.45315972222</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2050106139660935372</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050106139660935372</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>@chin2to Please mention in the email subject social media case #1005933. Thanks- Zubair</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1777618367000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46143.45332175926</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092857025757288</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2050092857025757288</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2050141465431462302</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050141465431462302</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Embrace higher earnings with your salary transfer
+ Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
+ 1. Open a Millionaire Account, Current Account or Savings Account
+ 2. Transfer your salary of AED 10,000 or more
+ 3. Maintain an average monthly balance of AED 25,000 or more
+ 4. Earn bonus interest with a credit card
+ Terms and conditions apply
+ https://t.co/u4ZGMVsftb</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1777626789000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2050141465431462302</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHOQzBXW8AAguXa.jpg', 'type': 'video', 'id': '2050141414244200448'}]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>27</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>149306</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>46143.55079861111</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092856904163635</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2050092856904163635</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2050092856904163635</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092856904163635</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>خفّض الحد الائتماني لبطاقتك للتقليل من مخاطر الاحتيال، كُن المتحكّم دائماً مع تطبيق ENBD X، وخفّض الحد الائتماني لبطاقتك في أي وقت ومن أي مكان. كُن حذراً وتغلّب على الاحتيال. #معاً_ضد_الاحتيال https://t.co/msVzqyWc5H</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1777615200000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2050092856904163635</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049819267961376768/img/nxQGabpsq_zByt3_.jpg', 'type': 'video', 'id': '2049819267961376768'}]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>7</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>46143.41666666666</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2050087425452757033</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2050086804280459271</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/FaheemKhan10045/status/2050086804280459271</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>I really don understand why the bank is charging minimum account balance fees every month, even though i have my bank account since 2023 plus credit card from the same bank. Here i am talking about my personal experience with the commercial bank of dubai @CBDUAE</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1777613757000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2050086804280459271</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'Faheem Khan', 'screenName': 'FaheemKhan10045', 'followersCount': 22, 'favouritesCount': 562, 'friendsCount': 154, 'description': 'Live Free Enjoy Hard Live Most Serve Best'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="2" t="n">
+        <v>46143.39996527778</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2050087425452757033</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2050087425452757033</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>I have always appreciated this bank @CBDUAE but every time i got the disappointment from your end, i have an account in enbd bank as well but they haven’t changed any single penny from my account, but in CBD every month they’ve charged 105 AED.</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1777613905000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2050086804280459271</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'Faheem Khan', 'screenName': 'FaheemKhan10045', 'followersCount': 22, 'favouritesCount': 562, 'friendsCount': 154, 'description': 'Live Free Enjoy Hard Live Most Serve Best'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2050086804280459271</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46143.40167824074</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2050086851621593314</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2049699745061626360</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45/status/2049699745061626360</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Hey @makemytripcare @makemytrip are you guys scammer???? Disgusting,unprofessional. Dm me now</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1777521475000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2049699745061626360</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>46142.33188657407</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2050068236809687186</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2049880868882387271</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/Saoud7758/status/2049880868882387271</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>بلغوا الجار الصغير أن إيرادات السعودية غير النفطية أكثر من 500 مليار ريال ( 45٪ من داخل المملكة 🇸🇦🌍</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1777564658000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2049880868882387271</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'سعـود الـغامـدي🇸🇦', 'screenName': 'Saoud7758', 'followersCount': 83068, 'favouritesCount': 8906, 'friendsCount': 674, 'description': 'اللهم ادِم على المملكة العربية السعودية نعمة الأمن والإيمان والعز والتمكين في ظل قيادتها الرشيدة'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>140</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8</v>
+      </c>
+      <c r="L55" t="n">
+        <v>23</v>
+      </c>
+      <c r="M55" t="n">
+        <v>169</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>32310</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>46142.83168981481</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2050068236809687186</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2050068236809687186</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>@Saoud7758 شاركت بنوك إماراتية، وفي مقدمتها بنك أبوظبي الأول، في تمويل جزء من خطة الاقتراض السعودية لعام 2026 البالغة 217 مليار ريال (58 مليار دولار) لسد العجز وتمويل المشاريع.
+ بنك  (FAB)
+• بنك  (Emirates NBD)
+• بنك  (ADCB)
+• بنك (ADIB)
+• بنك  (DIB)
+عمار يا دار الفلاحي 
+🇦🇪✌🏼🇦🇪</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1777609330000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2049880868882387271</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'Sraj', 'screenName': 'Srajrmah555', 'followersCount': 8, 'favouritesCount': 322, 'friendsCount': 92, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2049880868882387271</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46143.34872685185</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2050070949534294424</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2050070949534294424</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>@QIBGroup @EmiratesNBD_AE @RussiaBank
+Would you finance God's Airport locations within Allah Republic's! You did a wonderful job, with emirates.....
+(Immaculate A380's)
+this @Cosmosnaire Victory - Airport will be essential for eternal travel within the new Bog Republic Company.</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1777609977000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2050070949534294424</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'President Cosmosnaire Allah🦉U.S👮MP', 'screenName': 'CosmosnaireoOMG', 'followersCount': 38, 'favouritesCount': 1195, 'friendsCount': 20, 'description': '@Cosmosnaire &amp; God Corporation \nAll Automated Globally🌐Unlimited Human Robots📈Only Y5\n3Googolplexs In Gold Deals🤝On Table-You Sue U.S.A 4IT\n\n Бor Authorities'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>46143.35621527778</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2050070949534294424</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2050386491877044229</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/CosmosnaireoOMG/status/2050386491877044229</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Someone tell everyone on earth
+My @Cosmosnaire Robots can replace everyone
+on earth TONIGHT
+except the anomaly 
+-----------------------------------------------
+Judges? Automated
+Attorney? Automated
+Departments? Automated
+Industry? Automated
+Research? Automated
+Space? Automated</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1777685208000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2050386491877044229</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'President Cosmosnaire Allah🦉U.S👮MP', 'screenName': 'CosmosnaireoOMG', 'followersCount': 38, 'favouritesCount': 1195, 'friendsCount': 20, 'description': '@Cosmosnaire &amp; God Corporation \nAll Automated Globally🌐Unlimited Human Robots📈Only Y5\n3Googolplexs In Gold Deals🤝On Table-You Sue U.S.A 4IT\n\n Бor Authorities'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
+        <v>46144.22694444445</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187236000272545</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
+⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
+💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/eEQQCEye3M</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1777637702000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHO6bB9W8AALzbv.jpg', 'type': 'photo', 'id': '2050187228928733184'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHO6bPaXwAAZSbB.jpg', 'type': 'photo', 'id': '2050187232540082176'}]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
+        <v>46143.67710648148</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>📅 يسري العرض من 1 مايو ولغاية 31 يوليو 2026.
 تطبق الشروط والأحكام.
-https://t.co/WN0tZk19JS</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1777539601000</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2049775768025137608</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2049775768025137608</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>46142.54167824074</v>
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/hYz3g60H3P
+#الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1777637703000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46143.67711805556</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2050187243571077499</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187243571077499</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>You can now enjoy a higher expected profit of 5% p.a. on your savings with your Emirates Islamic e-Savings Account. Simply follow the below steps:
+⭐️ Open an Emirates Islamic e-Savings Account
+💸 Deposit AED 50,000 and above in the e-Saving Account</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1777637704000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>46143.67712962963</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050187236000272545</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2050123058375966977</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123058375966977</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/chEh9l7qmm</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1777622401000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2050123058375966977</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKsxBhXUAA9-HW.jpg', 'type': 'photo', 'id': '2049890738628939776'}]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="n">
+        <v>46143.50001157408</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2050128828232519798</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2049808521357914559</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1777547409000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2049808521357914559</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالرحمن النعيمي 🇦🇪', 'screenName': 'alnuaimi1979', 'followersCount': 197, 'favouritesCount': 477, 'friendsCount': 317, 'description': 'عبدالرحمن عبدالله بن أحمد بن راشد بن أحمد النعيمي                 . Board Member at Alnuaimi Group, country: United Arab Emirates'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>46142.63204861111</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2050128828232519798</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2050128828232519798</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>@alnuaimi1979 Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1777623776000</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2049808521357914559</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2049808521357914559</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>46143.51592592592</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123060796096729</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2050123060796096729</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2050123060796096729</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123060796096729</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+https://t.co/csC9BzTLNy</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1777622401000</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2050123058375966977</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2050123058375966977</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>46143.50001157408</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2050123060796072388</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2050123058363388031</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123058363388031</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/0GjgDF6a3y</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1777622401000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2050123058363388031</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJf297WcAArZep.jpg', 'type': 'photo', 'id': '2049806178348068864'}]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>46143.50001157408</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2050123060796072388</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2050123060796072388</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+https://t.co/6VJUgOMZYN</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1777622401000</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2050123058363388031</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2050123058363388031</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>46143.50001157408</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2050092860842692729</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2050092856912630226</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092856912630226</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/pkjj9lXWt6</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1777615200000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2050092856912630226</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKTIgCWMAADyTn.jpg', 'type': 'photo', 'id': '2049862554655010816'}]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
+        <v>46143.41666666666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2050092860842692729</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2050092860842692729</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1777615201000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2050092856912630226</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2050092856912630226</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>46143.41667824074</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2050092860603584751</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2050092856895791483</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092856895791483</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/X9KYZFWhAu</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1777615200000</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2050092856895791483</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJYiKlXkAA6NjN.jpg', 'type': 'photo', 'id': '2049798124386881536'}]</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
+        <v>46143.41666666666</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2050092860603584751</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2050092860603584751</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1777615201000</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2050092856895791483</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2050092856895791483</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>46143.41667824074</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -517,25 +517,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2050638510642569502</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2050638510642569502</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and https://t.co/UjSvMjQEYl</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1777745294000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2050638510642569502</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVUtfvawAAi5os.jpg', 'type': 'photo', 'id': '2050638345928359936'}]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>46144.92238425926</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2050638510642569502</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2050284019321893373</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/homehustlerduba/status/2050284019321893373</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1777660777000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2050284019321893373</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHQSQ2GbUAA32Hv.jpg', 'type': 'photo', 'id': '2050283810970095616'}]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="2" t="n">
+        <v>46143.94417824074</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>https://x.com/Waleedels_/status/2050640575183962333</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2050640575183962333</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2050617092429189457</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://x.com/Jaw_02/status/2050617092429189457</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
 اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
@@ -544,68 +676,68 @@
 ** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" t="n">
         <v>1777740188000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2050617092429189457</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5YWYAEGarI.jpg', 'type': 'photo', 'id': '2050617084132876289'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5aWIAAfuru.jpg', 'type': 'photo', 'id': '2050617084141248512'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5YWQAAeQD_.jpg', 'type': 'photo', 'id': '2050617084132868096'}]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'name': 'جـواد💰💵👨\u200d💻', 'screenName': 'Jaw_02', 'followersCount': 57366, 'favouritesCount': 531, 'friendsCount': 137, 'description': '💥 مُــهتم في مواقـع التسوق والتجارة الإلكتـرونيــة بشـكل عام وبطــاقات الائتمــان.💥\n 💳🛒 💵'}</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J4" t="n">
         <v>19</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>7</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M4" t="n">
         <v>81</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>34173</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>34379</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="n">
         <v>46144.86328703703</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>https://x.com/Waleedels_/status/2050640575183962333</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2050640575183962333</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>2050640575183962333</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://x.com/Waleedels_/status/2050640575183962333</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>@Jaw_02 🤔
 عندي بطاقات الراجحي (المرابحة والكاش باك)
@@ -616,228 +748,92 @@
 ⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F5" t="n">
         <v>1777745786000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>2050617092429189457</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>{'name': 'وليد', 'screenName': 'Waleedels_', 'followersCount': 80, 'favouritesCount': 140, 'friendsCount': 69, 'description': ''}</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>854</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>2050617092429189457</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>46144.92807870371</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2050640575183962333</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2050701922651312538</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/asu1033/status/2050701922651312538</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>@Waleedels_ @Jaw_02 هي ميزه وحيدة وهو اعلى معدل نقاط مقابل كل ريال، الانفينت تعطي ٦ نقاط مقابل كل ريال، و 29,412 نقطة تساوي 100 ريال يمكن استبدالها بكوبونات.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1777760413000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2050617092429189457</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'name': 'Mohammed Ali', 'screenName': 'asu1033', 'followersCount': 3, 'favouritesCount': 2994, 'friendsCount': 115, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2050640575183962333</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46145.09737268519</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2050638510642569502</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2050638510642569502</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and https://t.co/UjSvMjQEYl</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1777745294000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2050638510642569502</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVUtfvawAAi5os.jpg', 'type': 'photo', 'id': '2050638345928359936'}]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" s="2" t="n">
-        <v>46144.92238425926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2050640575183962333</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2050284019321893373</t>
+          <t>2050701922651312538</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050284019321893373</t>
+          <t>https://x.com/asu1033/status/2050701922651312538</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>@Waleedels_ @Jaw_02 هي ميزه وحيدة وهو اعلى معدل نقاط مقابل كل ريال، الانفينت تعطي ٦ نقاط مقابل كل ريال، و 29,412 نقطة تساوي 100 ريال يمكن استبدالها بكوبونات.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777660777000</v>
+        <v>1777760413000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2050284019321893373</t>
+          <t>2050617092429189457</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHQSQ2GbUAA32Hv.jpg', 'type': 'photo', 'id': '2050283810970095616'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
+          <t>{'name': 'Mohammed Ali', 'screenName': 'asu1033', 'followersCount': 3, 'favouritesCount': 2994, 'friendsCount': 115, 'description': ''}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -854,12 +850,16 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2050640575183962333</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>46143.94417824074</v>
+        <v>46145.09737268519</v>
       </c>
     </row>
     <row r="7">
@@ -926,7 +926,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1011,25 +1011,441 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2043682357216149641</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1776086818000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>46125.72706018519</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2043691745330798829</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2043691745330798829</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #996916 for us to assist you better. Thanks.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1776089056000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46125.75296296296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I was supposed to get a call for card cancellation in 2 days, been 4 and no one has bothered calling me yet. Trying to save the cancellation targets?</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1777618043000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2043691745330798829</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46143.44957175926</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2050106139660935372</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050106139660935372</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>@chin2to Please mention in the email subject social media case #1005933. Thanks- Zubair</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1777618367000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46143.45332175926</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1777735386000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2050106139660935372</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>46144.80770833333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://x.com/chin2to/status/2050596951385944148</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2050635418245201953</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050635418245201953</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>@chin2to We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005933 in the subject line.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1777744557000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2050596951385944148</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46144.91385416667</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2050606238627496289</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2050606238627496289</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Are you still paying for everything upfront?
 Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
@@ -1038,528 +1454,112 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F15" t="n">
         <v>1777737600000</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2050606238627496289</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHUZ87uXgAATQzV.jpg', 'type': 'photo', 'id': '2050573739952144384'}]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2970, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" s="2" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="2" t="n">
         <v>46144.83333333334</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2050606238627496289</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2050274049398341738</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2050274049398341738</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
 نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F16" t="n">
         <v>1777658400000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2050274049398341738</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHP22m8XYAAmQIT.jpg', 'type': 'video', 'id': '2050253630624653312'}]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2970, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="n">
         <v>46143.91666666666</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2043682357216149641</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1776086818000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" s="2" t="n">
-        <v>46125.72706018519</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2043691745330798829</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2043691745330798829</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #996916 for us to assist you better. Thanks.</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1776089056000</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>46125.75296296296</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2050104780245344423</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050104780245344423</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I was supposed to get a call for card cancellation in 2 days, been 4 and no one has bothered calling me yet. Trying to save the cancellation targets?</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1777618043000</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2043691745330798829</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>46143.44957175926</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2050106139660935372</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050106139660935372</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>@chin2to Please mention in the email subject social media case #1005933. Thanks- Zubair</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1777618367000</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2050104780245344423</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46143.45332175926</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1777735386000</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2050106139660935372</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>46144.80770833333</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2050635418245201953</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050635418245201953</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>@chin2to We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005933 in the subject line.</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1777744557000</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2050596951385944148</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46144.91385416667</v>
       </c>
     </row>
     <row r="17">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1697,25 +1697,162 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2050500266760478726</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2050500266760478726</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
+Read more: https://t.co/zL56RMfxRn
+Follow @uaefintechvibes for daily fintech updates. 
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1777712334000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2050500266760478726</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTW1QiaMAEg7rf.jpg', 'type': 'photo', 'id': '2050499940821118977'}]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="2" t="n">
+        <v>46144.54090277778</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2050500266760478726</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2050501839184080980</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050501839184080980</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1777712709000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2050501839184080980</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTYCiLasAEMOgS.jpg', 'type': 'photo', 'id': '2050501268406448129'}]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="n">
+        <v>46144.54524305555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>https://x.com/Kashif111144/status/2050526894626427022</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>2050526894626427022</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2050526894626427022</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://x.com/Kashif111144/status/2050526894626427022</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>UAE controls banking sector of PK after bribing leaders 
 BANKS owned by UAE in PK(not complete list)
@@ -1735,166 +1872,27 @@
 #UAE https://t.co/hEotNuuvdl</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>1777718683000</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2050526894626427022</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTvTfqXMAAb2zz.jpg', 'type': 'photo', 'id': '2050526848556150784'}]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 24, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" s="2" t="n">
-        <v>46144.61438657407</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2050537570484801767</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/financebufffh/status/2050537570484801767</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>@Kashif111144 UAE banks operating in Pakistan reflect deep bilateral trade partnerships and standard international investment. These regulated entities support economic development and Islamic finance growth.</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1777721228000</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'name': 'Sal Faisal', 'screenName': 'financebufffh', 'followersCount': 153, 'favouritesCount': 5615, 'friendsCount': 345, 'description': 'MENA finance buff 🌟 | Runner 🏃\u200d♂️'}</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46144.6438425926</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2050500266760478726</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2050500266760478726</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1777712334000</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2050500266760478726</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTW1QiaMAEg7rf.jpg', 'type': 'photo', 'id': '2050499940821118977'}]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
@@ -1902,62 +1900,60 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>111</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46144.54090277778</v>
+        <v>46144.61438657407</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050526894626427022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2050501839184080980</t>
+          <t>2050537570484801767</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050501839184080980</t>
+          <t>https://x.com/financebufffh/status/2050537570484801767</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
-Read more: https://t.co/VrIYgQm2sy
-#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
+          <t>@Kashif111144 UAE banks operating in Pakistan reflect deep bilateral trade partnerships and standard international investment. These regulated entities support economic development and Islamic finance growth.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1777712709000</v>
+        <v>1777721228000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2050501839184080980</t>
+          <t>2050526894626427022</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTYCiLasAEMOgS.jpg', 'type': 'photo', 'id': '2050501268406448129'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'Sal Faisal', 'screenName': 'financebufffh', 'followersCount': 153, 'favouritesCount': 5615, 'friendsCount': 345, 'description': 'MENA finance buff 🌟 | Runner 🏃\u200d♂️'}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1970,176 +1966,44 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2050526894626427022</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="n">
-        <v>46144.54524305555</v>
+        <v>46144.6438425926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2050470345820565788</t>
+          <t>2050456364728680817</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2050470345820565788</t>
+          <t>2050456364728680817</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1777705200000</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKEp28b0AABZRp.jpg', 'type': 'photo', 'id': '2049846635065495552'}]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
-        <v>46144.45833333334</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2050530749590483216</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050530749590483216</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AUMA, one of the world’s leading manufacturers of electric actuators, has undergone a reorganisation at the start of 2026. 
-Read more on https://t.co/TJY1yMiFn8
-#ABCnews #Leadership #Reorganization https://t.co/7jJtHnLvoS</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1777719602000</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2050530749590483216</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKReVVXwAAfJ-6.jpg', 'type': 'photo', 'id': '2049860730715881472'}]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>46144.62502314815</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
 🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
@@ -2149,26 +2013,161 @@
 Apply Now: https://t.co/9cutEjf788</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>1777701867000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2050456364728680817</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHSvMkYXUAA3tzb.jpg', 'type': 'video', 'id': '2050456335695675392'}]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>12</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>46144.41975694444</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2050456364728680817</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2050519766687732177</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050519766687732177</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Open a current or savings account with us, earn up to AED 100,000 cashback, and unlock premium banking and wealth services designed to help you grow your finances with confidence.
+https://t.co/0ZwFJ9a0fj https://t.co/cschHnULS4</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1777716983000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2050519766687732177</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTo3DwXAAAuaL2.jpg', 'type': 'video', 'id': '2050519732051132416'}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
+        <v>22</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>92210</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>46144.59471064815</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2050470345820565788</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2050470345820565788</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+        </is>
+      </c>
       <c r="F25" t="n">
-        <v>1777701867000</v>
+        <v>1777705200000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2050456364728680817</t>
+          <t>2050470345820565788</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHSvMkYXUAA3tzb.jpg', 'type': 'video', 'id': '2050456335695675392'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKEp28b0AABZRp.jpg', 'type': 'photo', 'id': '2049846635065495552'}]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2177,86 +2176,84 @@
         <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" s="2" t="n">
-        <v>46144.41975694444</v>
+        <v>46144.45833333334</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2050456364728680817</t>
+          <t>2050470345820565788</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2050488444636323843</t>
+          <t>2050530749590483216</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050488444636323843</t>
+          <t>https://x.com/ABCinGCC/status/2050530749590483216</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Exclusive for Emiratis.
- • Get up to 7X entries
- • 50,000,000 in cash prizes
- • Boost your balance today.
-https://t.co/EPLm4qFpi4 https://t.co/eu2UPVybEk</t>
+          <t>AUMA, one of the world’s leading manufacturers of electric actuators, has undergone a reorganisation at the start of 2026. 
+Read more on https://t.co/TJY1yMiFn8
+#ABCnews #Leadership #Reorganization https://t.co/7jJtHnLvoS</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777709516000</v>
+        <v>1777719602000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2050488444636323843</t>
+          <t>2050530749590483216</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTMXpoWoAEyz8l.jpg', 'type': 'photo', 'id': '2050488437044584449'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTMXznXAAAuSPH.jpg', 'type': 'photo', 'id': '2050488439724769280'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTMX9fXcAAoBCz.jpg', 'type': 'photo', 'id': '2050488442375598080'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKReVVXwAAfJ-6.jpg', 'type': 'photo', 'id': '2049860730715881472'}]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>76244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46144.50828703704</v>
+        <v>46144.62502314815</v>
       </c>
     </row>
     <row r="27">
@@ -2320,7 +2317,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2386,7 +2383,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2457,7 +2454,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2524,7 +2521,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,49 +517,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and https://t.co/UjSvMjQEYl</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777745294000</v>
+        <v>1777613768000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVUtfvawAAi5os.jpg', 'type': 'photo', 'id': '2050638345928359936'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -572,60 +572,60 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46144.92238425926</v>
+        <v>46143.40009259259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2050284019321893373</t>
+          <t>2050093026182131824</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050284019321893373</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777660777000</v>
+        <v>1777615240000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2050284019321893373</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHQSQ2GbUAA32Hv.jpg', 'type': 'photo', 'id': '2050283810970095616'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;H Real Estate', 'screenName': 'homehustlerduba', 'followersCount': 4, 'favouritesCount': 50, 'friendsCount': 3, 'description': '🏢 Unlocking value in prime properties\n🔍 Strategic acquisitions &amp; asset management\n💰 Minimum Net Guaranteed Returns\n🌱 Committed to sustainability'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -634,126 +634,124 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2050086851621593314</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46143.94417824074</v>
+        <v>46143.41712962963</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2050617092429189457</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Jaw_02/status/2050617092429189457</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777740188000</v>
+        <v>1777646110000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2050617092429189457</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5YWYAEGarI.jpg', 'type': 'photo', 'id': '2050617084132876289'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5aWIAAfuru.jpg', 'type': 'photo', 'id': '2050617084141248512'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVBX5YWQAAeQD_.jpg', 'type': 'photo', 'id': '2050617084132868096'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'جـواد💰💵👨\u200d💻', 'screenName': 'Jaw_02', 'followersCount': 57366, 'favouritesCount': 531, 'friendsCount': 137, 'description': '💥 مُــهتم في مواقـع التسوق والتجارة الإلكتـرونيــة بشـكل عام وبطــاقات الائتمــان.💥\n 💳🛒 💵'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>34379</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2050093026182131824</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>46144.86328703703</v>
+        <v>46143.77442129629</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2050275958674932182</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@Jaw_02 🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777745786000</v>
+        <v>1777658855000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2050617092429189457</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -763,11 +761,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'وليد', 'screenName': 'Waleedels_', 'followersCount': 80, 'favouritesCount': 140, 'friendsCount': 69, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -776,54 +774,54 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2050617092429189457</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46144.92807870371</v>
+        <v>46143.92193287037</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2050701922651312538</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/asu1033/status/2050701922651312538</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@Waleedels_ @Jaw_02 هي ميزه وحيدة وهو اعلى معدل نقاط مقابل كل ريال، الانفينت تعطي ٦ نقاط مقابل كل ريال، و 29,412 نقطة تساوي 100 ريال يمكن استبدالها بكوبونات.</t>
+          <t>@EmiratesNBD_AE I have sent an email.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777760413000</v>
+        <v>1777867069000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2050617092429189457</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -833,7 +831,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Mohammed Ali', 'screenName': 'asu1033', 'followersCount': 3, 'favouritesCount': 2994, 'friendsCount': 115, 'description': ''}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -850,56 +848,53 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2050275958674932182</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46145.09737268519</v>
+        <v>46146.33181712963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2051003496439427421</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2051003496439427421</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777744420000</v>
+        <v>1777832314000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2051003496439427421</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -909,7 +904,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Vedant Kabra', 'screenName': 'VedantKabra19', 'followersCount': 149, 'favouritesCount': 276, 'friendsCount': 63, 'description': 'Founder, AVN Capital | Sub-Broker — Motilal Oswal | AMFI Registered Mutual Fund Distributor - ARN 329296 | DM to schedule a 1:1 call'}</t>
+          <t>{'name': 'Umesh R Kahar', 'screenName': 'KaharUmesh', 'followersCount': 75, 'favouritesCount': 2167, 'friendsCount': 452, 'description': "Proud Indian..Engineer.. Social Activists..Tweets for Noble Cause..\nCool n Calm...\nFly,Run..even fall..but don't stop.."}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -919,71 +914,64 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46144.91226851852</v>
+        <v>46145.92956018518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2050184571547959797</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050184571547959797</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan https://t.co/vkgqOIi7JH</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777637067000</v>
+        <v>1777863600000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2050184571547959797</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHathWkaoAAz1AL.jpg', 'type': 'photo', 'id': '2051017468819447808'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Vedant Kabra', 'screenName': 'VedantKabra19', 'followersCount': 149, 'favouritesCount': 276, 'friendsCount': 63, 'description': 'Founder, AVN Capital | Sub-Broker — Motilal Oswal | AMFI Registered Mutual Fund Distributor - ARN 329296 | DM to schedule a 1:1 call'}</t>
+          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -993,67 +981,69 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46143.66975694444</v>
+        <v>46146.29166666666</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2051011126469767476</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2043682357216149641</t>
+          <t>https://x.com/ClapPakistan/status/2051011126469767476</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1776086818000</v>
+        <v>1777834133000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2051011126469767476</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHanvW-bAAAswjd.jpg', 'type': 'photo', 'id': '2051011112376926208'}]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1066,46 +1056,46 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>50</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>46125.72706018519</v>
+        <v>46145.95061342593</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2043691745330798829</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2043691745330798829</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #996916 for us to assist you better. Thanks.</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1776089056000</v>
+        <v>1777827034000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1115,7 +1105,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1125,57 +1115,53 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2043682357216149641</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" s="2" t="n">
-        <v>46125.75296296296</v>
+        <v>46145.86844907407</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2050104780245344423</t>
+          <t>2050981528298000875</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050104780245344423</t>
+          <t>https://x.com/TrioMsPaname/status/2050981528298000875</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I was supposed to get a call for card cancellation in 2 days, been 4 and no one has bothered calling me yet. Trying to save the cancellation targets?</t>
+          <t>La France est laxiste, personne ne suit les règles ici.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777618043000</v>
+        <v>1777827076000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1185,11 +1171,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1202,50 +1188,50 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2043691745330798829</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46143.44957175926</v>
+        <v>46145.86893518519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2050106139660935372</t>
+          <t>2051032364747280512</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050106139660935372</t>
+          <t>https://x.com/TrioMsPaname/status/2051032364747280512</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@chin2to Please mention in the email subject social media case #1005933. Thanks- Zubair</t>
+          <t>1 coup ko encore lui son slogan de mrde @BallyBagayoko</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777618367000</v>
+        <v>1777839196000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2051032364747280512</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1255,11 +1241,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1272,60 +1258,56 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2050104780245344423</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>46143.45332175926</v>
+        <v>46146.00921296296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777735386000</v>
+        <v>1777228053000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG2ftYnacAADNVo.png', 'type': 'photo', 'id': '2048469007574134784'}]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1342,50 +1324,46 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2050106139660935372</t>
-        </is>
-      </c>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>46144.80770833333</v>
+        <v>46138.93579861111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2050635418245201953</t>
+          <t>2048469731607281786</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050635418245201953</t>
+          <t>https://x.com/Nidhinkn/status/2048469731607281786</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@chin2to We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005933 in the subject line.</t>
+          <t>There was no email or sms from @EmiratesNBD_KSA regarding the monthly spend of 3000 SR. The new customers could be aware of this, since you would have informed them. However VAC had mentioned in their app about spending of 100$ and I did spend that. I want the 460SAR refund</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777744557000</v>
+        <v>1777228217000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2043682357216149641</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1395,11 +1373,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1412,68 +1390,65 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46144.91385416667</v>
+        <v>46138.93769675926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2048470825146171877</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>@EmiratesNBD_KSA Hello @EmiratesNBD_KSA , I want the amount to refunded to my account. Else I will have to escalate this issue to @SAMA_GOV 
+@EmiratesNBD_AE @VisaCEMEA</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777737600000</v>
+        <v>1777228478000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHUZ87uXgAATQzV.jpg', 'type': 'photo', 'id': '2050573739952144384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2970, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1482,66 +1457,68 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2048469731607281786</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>46144.83333333334</v>
+        <v>46138.9407175926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2050274049398341738</t>
+          <t>2048615227546087604</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050274049398341738</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2048615227546087604</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1777658400000</v>
+        <v>1777262906000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2050274049398341738</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHP22m8XYAAmQIT.jpg', 'type': 'video', 'id': '2050253630624653312'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2970, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1550,64 +1527,68 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>46143.91666666666</v>
+        <v>46139.33918981482</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2049584024058810569</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/Nidhinkn/status/2049584024058810569</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_KSA I did send DM with all details of the issue. Also shared my mobile number and ID. I'll wait till tomorrow evening. If there is no response by then, I'll directly escalate this to @SAMA_GOV</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777714674000</v>
+        <v>1777493885000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2050510000146305024/img/V7elcd87nIrHFIkh.jpg', 'type': 'video', 'id': '2050510000146305024'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Mohamed Farag', 'screenName': 'SavannahP57037', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': 'Founder @viral.advertising \nTraveler,Entrepreneur.'}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1620,60 +1601,64 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2048615227546087604</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="n">
-        <v>46144.56798611111</v>
+        <v>46142.01255787037</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2050691342179979687</t>
+          <t>2049698552998244828</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050691342179979687</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2049698552998244828</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Love isn't seasonal, bring her flowers consistently🌹❤️ https://t.co/p2kOXhMsqs</t>
+          <t>@Nidhinkn We have already shared your details with our team and asked  to contact you with an update as soon as possible.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777757890000</v>
+        <v>1777521191000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2050691342179979687</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2050691259904483329/img/_JZ4r4RjsPaSwdis.jpg', 'type': 'video', 'id': '2050691259904483329'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Mohamed Farag', 'screenName': 'SavannahP57037', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': 'Founder @viral.advertising \nTraveler,Entrepreneur.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1686,59 +1671,61 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2049584024058810569</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="n">
-        <v>46145.0681712963</v>
+        <v>46142.32859953704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>@EmiratesNBD_KSA No update from your team. No update from anyone from @EmiratesNBD_KSA 
+Now I will escalate it to @SAMA_GOV</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777712334000</v>
+        <v>1777825766000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTW1QiaMAEg7rf.jpg', 'type': 'photo', 'id': '2050499940821118977'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1751,556 +1738,542 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2049698552998244828</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n">
-        <v>46144.54090277778</v>
+        <v>46145.85377314815</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050855805600092255</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2050855805600092255</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions https://t.co/hZmnE0KKFU https://t.co/dqextuYMnK</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1777797101000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2050855805600092255</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYaeCHXUAAlHfN.jpg', 'type': 'photo', 'id': '2050855783579996160'}]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'Gulf News', 'screenName': 'gulf_news', 'followersCount': 1541257, 'favouritesCount': 1075, 'friendsCount': 411, 'description': "We don't just cover the news - we uncover the truth. The official Twitter feed from Gulf News."}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>32</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="n">
+        <v>46145.52200231481</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2050855805600092255</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2050785564182392905</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1777780354000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2050785564182392905</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamTYXgAAT-o_.jpg', 'type': 'photo', 'id': '2050785556909490176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamj9XMAAx1Ze.jpg', 'type': 'photo', 'id': '2050785561359626240'}]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
+        <v>46145.3281712963</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2050845248088055847</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2050845248088055847</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1777794584000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2050845248088055847</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'Femal', 'screenName': 'z6894890', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 51, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>46145.49287037037</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2050841752987136094</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2050841752987136094</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1777793751000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2050841752987136094</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYNrg9boAAfrzr.jpg', 'type': 'photo', 'id': '2050841721546973184'}]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 518, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>46145.48322916667</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2050841752987136094</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2051042176843301084</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2051042176843301084</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>«هيوماين» تطلق أول نظام تشغيل مؤسسي للذكاء الاصطناعي التوليدي عالميًا بالتعاون مع أمازون ويب سيرفيسز
+https://t.co/9TmH5pLkPN | التفاصيل 
+#fintech_gate
+#هيوماين #للذكاء_الاصطناعي 
+#أمازون_ويب_سيرفيسز https://t.co/oF0ORrLiy2</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1777841536000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2051042176843301084</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHbD_MgWoAAKhW9.jpg', 'type': 'photo', 'id': '2051042170769940480'}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 518, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>46146.0362962963</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2050807726507516194</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2050807726507516194</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>UAE Fintech News this week
+@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
+#digitalpayments #uaefintech #proptech https://t.co/0prr3Cb7B5</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1777785638000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2050807726507516194</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2050806769707098112/img/S26hJZ2jdFx84hGu.jpg', 'type': 'video', 'id': '2050806769707098112'}]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>46145.38932870371</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2050807726507516194</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>2050501839184080980</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://x.com/uaefintechvibes/status/2050501839184080980</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
 Read more: https://t.co/VrIYgQm2sy
 #digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F26" t="n">
         <v>1777712709000</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>2050501839184080980</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTYCiLasAEMOgS.jpg', 'type': 'photo', 'id': '2050501268406448129'}]</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 23, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" s="2" t="n">
-        <v>46144.54524305555</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1777718683000</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTvTfqXMAAb2zz.jpg', 'type': 'photo', 'id': '2050526848556150784'}]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 24, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
-        <v>46144.61438657407</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2050537570484801767</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/financebufffh/status/2050537570484801767</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>@Kashif111144 UAE banks operating in Pakistan reflect deep bilateral trade partnerships and standard international investment. These regulated entities support economic development and Islamic finance growth.</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1777721228000</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'name': 'Sal Faisal', 'screenName': 'financebufffh', 'followersCount': 153, 'favouritesCount': 5615, 'friendsCount': 345, 'description': 'MENA finance buff 🌟 | Runner 🏃\u200d♂️'}</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2050526894626427022</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46144.6438425926</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1777701867000</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHSvMkYXUAA3tzb.jpg', 'type': 'video', 'id': '2050456335695675392'}]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
-        <v>46144.41975694444</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2050456364728680817</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2050519766687732177</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050519766687732177</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Open a current or savings account with us, earn up to AED 100,000 cashback, and unlock premium banking and wealth services designed to help you grow your finances with confidence.
-https://t.co/0ZwFJ9a0fj https://t.co/cschHnULS4</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1777716983000</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2050519766687732177</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTo3DwXAAAuaL2.jpg', 'type': 'video', 'id': '2050519732051132416'}]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174605, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>22</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>92210</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>46144.59471064815</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1777705200000</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKEp28b0AABZRp.jpg', 'type': 'photo', 'id': '2049846635065495552'}]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>46144.45833333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2050470345820565788</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2050530749590483216</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2050530749590483216</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AUMA, one of the world’s leading manufacturers of electric actuators, has undergone a reorganisation at the start of 2026. 
-Read more on https://t.co/TJY1yMiFn8
-#ABCnews #Leadership #Reorganization https://t.co/7jJtHnLvoS</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1777719602000</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2050530749590483216</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKReVVXwAAfJ-6.jpg', 'type': 'photo', 'id': '2049860730715881472'}]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 359, 'favouritesCount': 8, 'friendsCount': 191, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46144.62502314815</v>
+        <v>46144.54524305555</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2050448328266063924</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2050802535502365160</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/AnkitMittal1403/status/2050198001034092995</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050802535502365160</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
-Regards,
-Ankit K Mittal
-+54 702 3869 https://t.co/av2G1Lek3Q</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777640268000</v>
+        <v>1777784401000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2050802535502365160</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHPDrhHbwAABqGK.jpg', 'type': 'photo', 'id': '2050197407775047680'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVpoO7WQAAHCq4.jpg', 'type': 'video', 'id': '2050661313332854785'}]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Ankit Mittal', 'screenName': 'AnkitMittal1403', 'followersCount': 2, 'favouritesCount': 3, 'friendsCount': 11, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2310,53 +2283,53 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>593</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46143.70680555556</v>
+        <v>46145.37501157408</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2050448328266063924</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2050448328266063924</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@AnkitMittal1403 Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>@EmiratesNBD_AE اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777699951000</v>
+        <v>1777786022000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2050802535502365160</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2366,11 +2339,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18467, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Fahad', 'screenName': 'abotameem430', 'followersCount': 14, 'favouritesCount': 10, 'friendsCount': 38, 'description': 'Fahad'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2383,61 +2356,61 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2050802535502365160</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46144.39758101852</v>
+        <v>46145.39377314815</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2050455250096541870</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2050455246686527975</t>
+          <t>2050809681140916631</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050809681140916631</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
+          <t>@abotameem430 نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
+https://t.co/B8qzTltFYl</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777701601000</v>
+        <v>1777786104000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2050455246686527975</t>
+          <t>2050802535502365160</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHOrxzTWsAE_5jJ.jpg', 'type': 'video', 'id': '2050171091780333568'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18467, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2450,87 +2423,20 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2050809333848342901</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46144.41667824074</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2050455250096541870</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2050455250096541870</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: https://t.co/Vh2DVfNQFD</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1777701601000</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2050455246686527975</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18467, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2050455246686527975</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>46144.41667824074</v>
+        <v>46145.39472222222</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,35 +517,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049066491463553321</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777613768000</v>
+        <v>1777370496000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -555,7 +556,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -568,50 +569,50 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>55236</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46143.40009259259</v>
+        <v>46140.58444444444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2050093026182131824</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
+          <t>@EmiratesNBD_AE On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777615240000</v>
+        <v>1777925993000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -621,11 +622,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Muhammad Usman', 'screenName': 'Muhamma38929354', 'followersCount': 751, 'favouritesCount': 43872, 'friendsCount': 2152, 'description': 'The greatest good is positive thinking,     The greatest shame is negative thinking'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -634,54 +635,55 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46143.41712962963</v>
+        <v>46147.01380787037</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2050222500295123129</t>
+          <t>2051497841378414637</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2051497841378414637</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
+          <t>@Muhamma38929354 Thanks for interest in our products, please visit the below link to check the details 
+https://t.co/ywrne3Fcg2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777646110000</v>
+        <v>1777950175000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,11 +693,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -708,46 +710,46 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2050093026182131824</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46143.77442129629</v>
+        <v>46147.29369212963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2050275958674932182</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777658855000</v>
+        <v>1777613768000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -761,7 +763,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -778,46 +780,42 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2050222500295123129</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46143.92193287037</v>
+        <v>46143.40009259259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2050093026182131824</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I have sent an email.</t>
+          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777867069000</v>
+        <v>1777615240000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -831,11 +829,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -844,57 +842,54 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2050275958674932182</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46146.33181712963</v>
+        <v>46143.41712962963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-https://t.co/BcgwdgmQQQ</t>
+          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777832314000</v>
+        <v>1777646110000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -904,11 +899,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Umesh R Kahar', 'screenName': 'KaharUmesh', 'followersCount': 75, 'favouritesCount': 2167, 'friendsCount': 452, 'description': "Proud Indian..Engineer.. Social Activists..Tweets for Noble Cause..\nCool n Calm...\nFly,Run..even fall..but don't stop.."}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -921,61 +916,64 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2050093026182131824</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n">
-        <v>46145.92956018518</v>
+        <v>46143.77442129629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2050275958674932182</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan https://t.co/vkgqOIi7JH</t>
+          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777863600000</v>
+        <v>1777658855000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHathWkaoAAz1AL.jpg', 'type': 'photo', 'id': '2051017468819447808'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -988,62 +986,64 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2050222500295123129</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="n">
-        <v>46146.29166666666</v>
+        <v>46143.92193287037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2051011126469767476</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051011126469767476</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>@EmiratesNBD_AE I have sent an email.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1777834133000</v>
+        <v>1777867069000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2051011126469767476</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHanvW-bAAAswjd.jpg', 'type': 'photo', 'id': '2051011112376926208'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1056,46 +1056,50 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2050275958674932182</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="n">
-        <v>46145.95061342593</v>
+        <v>46146.33181712963</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051153017571840501</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2051153017571840501</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>@patilabhijeet45 Thanks for sharing, our team will check it and update you accordingly</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1777827034000</v>
+        <v>1777867962000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1118,50 +1122,54 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2051149273409143066</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n">
-        <v>46145.86844907407</v>
+        <v>46146.34215277778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2050981528298000875</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981528298000875</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La France est laxiste, personne ne suit les règles ici.</t>
+          <t>@EmiratesNBD_AE Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777827076000</v>
+        <v>1777919909000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1171,7 +1179,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1188,50 +1196,53 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051153017571840501</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46145.86893518519</v>
+        <v>46146.94339120371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2051032364747280512</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2051032364747280512</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049379193910165928</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1 coup ko encore lui son slogan de mrde @BallyBagayoko</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777839196000</v>
+        <v>1777445050000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2051032364747280512</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1241,77 +1252,78 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>46146.00921296296</v>
+        <v>46141.44733796296</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
+          <t>https://x.com/STKgenghis/status/2049468314699825596</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
+          <t>@EmiratesNBD_AE would not recommend bank that suspends 40 year old accounts wout notification. Only found out when i temp blocked credit card i thought id misplaced. It cant be unblocked because of suspension...
+deprived of services no notification  told KYC take 8-10 buss days 2 get back. So..</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777228053000</v>
+        <v>1777466298000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG2ftYnacAADNVo.png', 'type': 'photo', 'id': '2048469007574134784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1324,46 +1336,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="n">
-        <v>46138.93579861111</v>
+        <v>46141.69326388889</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2048469731607281786</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048469731607281786</t>
+          <t>https://x.com/STKgenghis/status/2049469132337561727</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>There was no email or sms from @EmiratesNBD_KSA regarding the monthly spend of 3000 SR. The new customers could be aware of this, since you would have informed them. However VAC had mentioned in their app about spending of 100$ and I did spend that. I want the 460SAR refund</t>
+          <t>@EmiratesNBD_AE O and also after emails customer support has yet to issue a complaint number. No logging = no complaint. The perfect system.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777228217000</v>
+        <v>1777466493000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1373,7 +1389,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1390,51 +1406,50 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46138.93769675926</v>
+        <v>46141.69552083333</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2048470825146171877</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049469842646818920</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Hello @EmiratesNBD_KSA , I want the amount to refunded to my account. Else I will have to escalate this issue to @SAMA_GOV 
-@EmiratesNBD_AE @VisaCEMEA</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1004599 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777228478000</v>
+        <v>1777466662000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1444,11 +1459,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1457,54 +1472,54 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2048469731607281786</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46138.9407175926</v>
+        <v>46141.69747685185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2048615227546087604</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2048615227546087604</t>
+          <t>https://x.com/STKgenghis/status/2049470212714737829</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
+          <t>@EmiratesNBD_AE I will give this a try but am not holding my breath.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1777262906000</v>
+        <v>1777466750000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1514,11 +1529,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1531,50 +1546,50 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2048470825146171877</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46139.33918981482</v>
+        <v>46141.69849537037</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2049584024058810569</t>
+          <t>2049472842727665850</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2049584024058810569</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049472842727665850</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I did send DM with all details of the issue. Also shared my mobile number and ID. I'll wait till tomorrow evening. If there is no response by then, I'll directly escalate this to @SAMA_GOV</t>
+          <t>@STKgenghis Hi khana! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004599 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777493885000</v>
+        <v>1777467377000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1584,7 +1599,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1601,50 +1616,50 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2048615227546087604</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46142.01255787037</v>
+        <v>46141.70575231482</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2049698552998244828</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2049698552998244828</t>
+          <t>https://x.com/STKgenghis/status/2049474377788604862</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@Nidhinkn We have already shared your details with our team and asked  to contact you with an update as soon as possible.</t>
+          <t>@EmiratesNBD_AE Done. As I said not holding breath.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777521191000</v>
+        <v>1777467743000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1654,7 +1669,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1671,51 +1686,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2049584024058810569</t>
+          <t>2049472842727665850</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46142.32859953704</v>
+        <v>46141.70998842592</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2049475517070348292</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049475517070348292</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA No update from your team. No update from anyone from @EmiratesNBD_KSA 
-Now I will escalate it to @SAMA_GOV</t>
+          <t>@STKgenghis Hello, we will check the email and update you shortly.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777825766000</v>
+        <v>1777468015000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1725,11 +1739,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1742,701 +1756,3495 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2049698552998244828</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46145.85377314815</v>
+        <v>46141.71313657407</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions https://t.co/hZmnE0KKFU https://t.co/dqextuYMnK</t>
+          <t>@EmiratesNBD_AE So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777797101000</v>
+        <v>1777535453000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYaeCHXUAAlHfN.jpg', 'type': 'photo', 'id': '2050855783579996160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf News', 'screenName': 'gulf_news', 'followersCount': 1541257, 'favouritesCount': 1075, 'friendsCount': 411, 'description': "We don't just cover the news - we uncover the truth. The official Twitter feed from Gulf News."}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3733</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2049475517070348292</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="n">
-        <v>46145.52200231481</v>
+        <v>46142.49366898148</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>2049759572416495861</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2049759572416495861</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>@STKgenghis We are extremely sorry and we have escalated the matter and will reply to your email as soon as possible with an update.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1777535739000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2049758371734229151</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46142.49697916667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2049927131657081284</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Right. So its now almost 14 days with credit card not functioning.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1777575688000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2049759572416495861</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>46142.95935185185</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2050063207486587148</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050063207486587148</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>@STKgenghis Please note that our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1777608131000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2049927131657081284</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>46143.33484953704</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2050170081574056214</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2050170081574056214</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I dont think you appreciate where this places me through no fault of mine. I have had several subscriptions stopped because card is blocked. A monthly payment didnt go through - i am facing a fine.  OVER TWO WEEKS since i asked for my card to be blocked as a precaution !????</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1777633612000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2050063207486587148</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>46143.62976851852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275701312324065</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>@STKgenghis We apologize for the inconvenience, our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1777658794000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2050170081574056214</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>46143.92122685185</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1777682263000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>46144.1928587963</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2050427142379282939</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050427142379282939</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>@STKgenghis We are extremely sorry and understand your concern. Please note that we are working very closely to resolve your concern and will update you on urgent basis.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1777694900000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46144.33912037037</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2051475218783158326</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Update. 
+Received email from your social medium team saying "Dear,
+Kindly note that the account is not active."
+No name. My account is active. Not sure what this cryptic email meant.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1777944781000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2050427142379282939</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46147.23126157407</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2051355715994878347</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051302125989236884</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1777903512000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051302098415812608/pu/img/kiycv3whSbLg1NL6.jpg', 'type': 'video', 'id': '2051302098415812608'}]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>46146.75361111111</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2051355715994878347</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2051355715994878347</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA متى بتدعمون سامسونج باي؟؟</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1777916289000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46146.90149305556</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2051355715994878347</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2051363915762708887</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051363915762708887</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>@hisho25 مرحبا, تم الرد على الخاص.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1777918244000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2051355715994878347</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46146.92412037037</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ماجاني شي على الخاص</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1777918278000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2051363915762708887</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>46146.92451388889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2051365950771871780</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051365950771871780</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>@hisho25 مرحبا, تم ارسال الرسالة مرة اخرى.</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1777918729000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>46146.9297337963</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051025258497396907</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1777837502000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHa0maLWAAAM-y5.jpg', 'type': 'photo', 'id': '2051025252268769280'}]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>824</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>58186</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="n">
+        <v>46145.98960648148</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2051282211920588860</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051282211920588860</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>@bokonndarro عین سگ، دروغ میگه.
+با پاسپورت کانادا و اقامت امارات، ازت یک کامیون مدارک می خواهند، بعد می فرستند دفتر مرکزی، آیا قبول بشه آیا قبول نشه!!
+امارات حساب باز کردن بعنوان توریسیت واقعا سخته</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1777898764000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'حوا🍎', 'screenName': 'BabyIamInJail', 'followersCount': 620, 'favouritesCount': 20504, 'friendsCount': 775, 'description': '🇨🇦 in Dubai'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46146.69865740741</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@BabyIamInJail توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1777899117000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2051282211920588860</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46146.70274305555</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@bokonndarro عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1777899921000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'name': 'حوا🍎', 'screenName': 'BabyIamInJail', 'followersCount': 620, 'favouritesCount': 20504, 'friendsCount': 775, 'description': '🇨🇦 in Dubai'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46146.71204861111</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2051290669126242679</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051290669126242679</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1777900781000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>46146.72200231482</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050914407471849643</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1777811073000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZPyC_WYAAg5zq.jpg', 'type': 'photo', 'id': '2050914401528471552'}]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
+        <v>46145.68371527778</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1777896671000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'الفنان سعود عبدالله', 'screenName': 'saudabdullah08', 'followersCount': 0, 'favouritesCount': 11, 'friendsCount': 17, 'description': 'فنان اطمح للعالميه ومحب للفن'}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46146.67443287037</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2051274681102049577</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051274681102049577</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>@saudabdullah08 نحن آسفون جدًا لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1007678 في موضوع الرسالة.</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1777896969000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46146.67788194444</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1777888498000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 38, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="n">
+        <v>46146.57983796296</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2051247081315057693</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051247081315057693</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>@abhiseksonusonu Hi Mishra, thanks for reaching out. We're sorry to hear you're facing an issue. We have replied to your post privately.</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1777890389000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46146.60172453704</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2048745045147123736</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1777293857000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 1, 'favouritesCount': 969, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="n">
+        <v>46139.69741898148</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1777893777000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 1, 'favouritesCount': 969, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>46146.6409375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2051263125849010218</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051263125849010218</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>@anwarquadri7 Hello, We have replied to your message in private</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1777894214000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>46146.64599537037</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/DeloitteME/status/2051210220634820985</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2051210220634820985</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2051210220634820985</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/DeloitteME/status/2051210220634820985</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>The future of finance is shaped by complex regulations.
+In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp;amp; the vital role of culture in driving innovation amid change.
+#Banking #FinancialServices https://t.co/THJgtlvhv5</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1777881600000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2051210220634820985</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZZtkSX0AAZhuo.jpg', 'type': 'photo', 'id': '2050925319683559424'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZZt3kW0AIfmx2.jpg', 'type': 'photo', 'id': '2050925324859265026'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZZuLuWEAAz8pH.jpg', 'type': 'photo', 'id': '2050925330269868032'}]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'Deloitte Middle East', 'screenName': 'DeloitteME', 'followersCount': 8624, 'favouritesCount': 392, 'friendsCount': 646, 'description': 'Sharing the latest news, articles and research from Deloitte in the Middle East, the business advisory firm, present in the region since 1926.'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="2" t="n">
+        <v>46146.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/hill_lilli40424/status/2051194736661381477</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2051194736661381477</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2051194736661381477</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/hill_lilli40424/status/2051194736661381477</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/3ecHAxJ2hs</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1777877909000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2051194736661381477</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2051194636891500544/img/r9yXLJXkoSSxgi89.jpg', 'type': 'video', 'id': '2051194636891500544'}]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohamed Farag', 'screenName': 'hill_lilli40424', 'followersCount': 7, 'favouritesCount': 0, 'friendsCount': 8, 'description': 'Founder @viral.advertising \nTraveler,Entrepreneur.'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
+        <v>46146.4572800926</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/hill_lilli40424/status/2051194736661381477</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2051194736661381477</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2051393108986990839</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/hill_lilli40424/status/2051393108986990839</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Love isn't seasonal, bring her flowers consistently🌹❤️ https://t.co/J7XNAb5pTB</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1777925204000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2051393108986990839</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2051393028276051968/img/dcGa2eQqwfH4YTf7.jpg', 'type': 'video', 'id': '2051393028276051968'}]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohamed Farag', 'screenName': 'hill_lilli40424', 'followersCount': 7, 'favouritesCount': 0, 'friendsCount': 8, 'description': 'Founder @viral.advertising \nTraveler,Entrepreneur.'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="2" t="n">
+        <v>46147.00467592593</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1777882561000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>46146.51112268519</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2051214251092783501</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/FF1991Whooo/status/2051214251092783501</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recently, I was marked overdue for a 1-day delay (paid immediately), and the remaining amount was auto-debited. Since then, I’ve spoken to 4–5 agents — each promising resolution, but nothing has been actioned.
+This has been dragging for months now with zero accountability.</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1777882561000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46146.51112268519</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2051219105496150060</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051219105496150060</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>@FF1991Whooo We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007505 in the subject line.</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1777883719000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46146.52452546296</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>2050785564182392905</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
 #transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
 https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F53" t="n">
         <v>1777780354000</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>2050785564182392905</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamTYXgAAT-o_.jpg', 'type': 'photo', 'id': '2050785556909490176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamj9XMAAx1Ze.jpg', 'type': 'photo', 'id': '2050785561359626240'}]</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
         <v>15</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" s="2" t="n">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
         <v>46145.3281712963</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2050845248088055847</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2050845248088055847</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1777794584000</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2050845248088055847</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'name': 'Femal', 'screenName': 'z6894890', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 51, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
-        <v>46145.49287037037</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2050841752987136094</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2050841752987136094</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1777793751000</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2050841752987136094</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYNrg9boAAfrzr.jpg', 'type': 'photo', 'id': '2050841721546973184'}]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 518, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" s="2" t="n">
-        <v>46145.48322916667</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2050841752987136094</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2051042176843301084</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2051042176843301084</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>«هيوماين» تطلق أول نظام تشغيل مؤسسي للذكاء الاصطناعي التوليدي عالميًا بالتعاون مع أمازون ويب سيرفيسز
-https://t.co/9TmH5pLkPN | التفاصيل 
-#fintech_gate
-#هيوماين #للذكاء_الاصطناعي 
-#أمازون_ويب_سيرفيسز https://t.co/oF0ORrLiy2</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1777841536000</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2051042176843301084</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHbD_MgWoAAKhW9.jpg', 'type': 'photo', 'id': '2051042170769940480'}]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 518, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>46146.0362962963</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2050807726507516194</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2050807726507516194</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>UAE Fintech News this week
-@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
-#digitalpayments #uaefintech #proptech https://t.co/0prr3Cb7B5</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1777785638000</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2050807726507516194</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2050806769707098112/img/S26hJZ2jdFx84hGu.jpg', 'type': 'video', 'id': '2050806769707098112'}]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>46145.38932870371</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2050807726507516194</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2050501839184080980</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/uaefintechvibes/status/2050501839184080980</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
-Read more: https://t.co/VrIYgQm2sy
-#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1777712709000</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2050501839184080980</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTYCiLasAEMOgS.jpg', 'type': 'photo', 'id': '2050501268406448129'}]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1777876484000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2050785564182392905</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'Mahmoud Moawad', 'screenName': 'mahmoudmoawad00', 'followersCount': 5, 'favouritesCount': 1512, 'friendsCount': 275, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2050785564182392905</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46146.44078703703</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2051204201930190866</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051204201930190866</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>@mahmoudmoawad00 We are sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007406 in the subject line.</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1777880165000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2050785564182392905</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174658, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" s="2" t="n">
-        <v>46144.54524305555</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2050802535502365160</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050802535502365160</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1777784401000</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2050802535502365160</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVpoO7WQAAHCq4.jpg', 'type': 'video', 'id': '2050661313332854785'}]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46146.48339120371</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2051192927792300267</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2051192927792300267</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2051192927792300267</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2051192927792300267</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Dear Consumer,
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: https://t.co/L4M7VN0dyV 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1777877477000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'Central Bank of the UAE', 'screenName': 'centralbankuae', 'followersCount': 6488, 'favouritesCount': 389, 'friendsCount': 213, 'description': 'الحساب الرسمي لمصرف الإمارات العربية المتحدة المركزي The official account of the Central Bank of the UAE'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46146.45228009259</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049022486218715385</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1777360004000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG-XFpUagAEQNCt.jpg', 'type': 'photo', 'id': '2049022478723481601'}]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>46140.46300925926</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2049060823264350309</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049060823264350309</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1777369144000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46140.5687962963</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2049065369416159269</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1777370228000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2049060823264350309</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46140.5813425926</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2049068445883314237</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1777370962000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2049065369416159269</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46140.58983796297</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2050249666336559176</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2050249666336559176</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>@emiratesislamic كم يوم طاف الحين ؟</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1777652586000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2049068445883314237</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>46143.849375</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1777877552000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2050249666336559176</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>46146.45314814815</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1777874760000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2050953741415694336/pu/img/_OWQjFIhaq2Dk8W-.jpg', 'type': 'video', 'id': '2050953741415694336'}]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>46146.42083333333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1777881600000</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdI4bpW0AAzk8W.jpg', 'type': 'photo', 'id': '2051188289621643264'}]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
-        <v>8</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
-        <v>46145.37501157408</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE اريد تمويل وارغب بالاتصال</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1777786022000</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2050802535502365160</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>{'name': 'Fahad', 'screenName': 'abotameem430', 'followersCount': 14, 'favouritesCount': 10, 'friendsCount': 38, 'description': 'Fahad'}</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2050802535502365160</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>46145.39377314815</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2050809681140916631</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050809681140916631</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>@abotameem430 نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
-https://t.co/B8qzTltFYl</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1777786104000</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2050802535502365160</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46145.39472222222</v>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" s="2" t="n">
+        <v>46146.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2051210223440871854</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210223440871854</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+https://t.co/pVA5yvt1qT</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1777881601000</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>46146.50001157408</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285716965986342</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1777899600000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdGISHWAAEPXm-.jpg', 'type': 'photo', 'id': '2051185263406088193'}]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>46146.70833333334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1777874400000</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadNzTWQAAUjIJ.jpg', 'type': 'photo', 'id': '2050999540749058048'}]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" s="2" t="n">
+        <v>46146.41666666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1777874401000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>46146.41667824074</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2051180027576750215</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180027576750215</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.) https://t.co/qqwuS90F3U</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1777874402000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadODvXQAAw5bH.jpg', 'type': 'photo', 'id': '2050999545161531392'}]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>46146.41668981482</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,102 +517,103 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
+          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2053208001905860832</t>
+          <t>2053544670014107870</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2053207767746326594</t>
+          <t>2053539327305560098</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/khaja_moin/status/2053207767746326594</t>
+          <t>https://x.com/FinTech_KSA/status/2053539327305560098</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
-نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
+          <t>كل ما تحتاج معرفته من البنوك لمحفظة جوجل
+Google Wallet في السعودية 🇸🇦 💳
+وين باقي الشباب 💀 https://t.co/9aXtCcnI0m</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1778357853000</v>
+        <v>1778436903000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2053207767746326594</t>
+          <t>2053539327305560098</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH-jIQ6WIAAdMEm.jpg', 'type': 'photo', 'id': '2053539317478203392'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39854, 'friendsCount': 695, 'description': '🤫'}</t>
+          <t>{'name': 'iipupii🤳💳', 'screenName': 'FinTech_KSA', 'followersCount': 15671, 'favouritesCount': 3842, 'friendsCount': 258, 'description': 'مهتم بالتقنية المالية والمدفوعات الرقمية 💳📱\n#Fintech #Payments #Banking #Cards #DigitalWallets #DigitalCommerce'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46152.0121875</v>
+        <v>46152.92711805556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
+          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2053208001905860832</t>
+          <t>2053544670014107870</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2053208001905860832</t>
+          <t>2053544670014107870</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
+          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA نرجو من Emirates NBD التعامل مع شكاوى العملاء بشكل أفضل وحل المشكلة بأسرع وقت.</t>
+          <t>@FinTech_KSA @EmiratesNBD_KSA فينكم</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1778357909000</v>
+        <v>1778438177000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2053207767746326594</t>
+          <t>2053539327305560098</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -622,7 +623,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39854, 'friendsCount': 695, 'description': '🤫'}</t>
+          <t>{'name': 'Mamdouh Safa', 'screenName': 'mamdouh_safa', 'followersCount': 19, 'favouritesCount': 101, 'friendsCount': 346, 'description': '\u200f🤔🤔🤔🤔🤔'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -639,50 +640,50 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>320</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2053207767746326594</t>
+          <t>2053539327305560098</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46152.01283564815</v>
+        <v>46152.94186342593</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053544670014107870</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053678312044511470</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053101582175326235</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053678312044511470</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
+          <t>@mamdouh_safa مرحبا محمود شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1778332536000</v>
+        <v>1778470039000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053539327305560098</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -692,11 +693,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -709,60 +710,64 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2053544670014107870</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>46151.71916666667</v>
+        <v>46153.31063657408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053561102663885109</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2053108968772231287</t>
+          <t>2053404320901505163</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053108968772231287</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053404320901505163</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@WahibaEsri Hi Wahiba, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>انجز كل عملياتك المصرفية وسدد كل فواتيرك بسهولة من تطبيق ENBD X📲 https://t.co/zf5cSFztjt</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1778334297000</v>
+        <v>1778404715000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053404320901505163</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8oWNzWkAIyRow.jpg', 'type': 'photo', 'id': '2053404317231517698'}]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174682, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -775,50 +780,46 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2053101582175326235</t>
-        </is>
-      </c>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46151.73954861111</v>
+        <v>46152.55457175926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053561102663885109</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053561102663885109</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Sure will send now. Thank you 😊</t>
+          <t>@EmiratesNBD_KSA لا استطيع تحويل النقاط</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1778385234000</v>
+        <v>1778442094000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053404320901505163</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -828,7 +829,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
+          <t>{'name': 'Qusai Alsaffar', 'screenName': 'QusaiAlsaffar', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -845,132 +846,136 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2053108968772231287</t>
+          <t>2053404320901505163</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46152.32909722222</v>
+        <v>46152.98719907407</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053561102663885109</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2053676082763571444</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052057840244646114</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053676082763571444</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
-By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
-#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
+          <t>@QusaiAlsaffar مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص ورقم هاتفك المسجل حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1778083689000</v>
+        <v>1778469508000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2053404320901505163</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2052057793599856657/img/uFYYXnfG8i7PvyMn.jpg', 'type': 'video', 'id': '2052057793599856657'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174682, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2053561102663885109</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n">
-        <v>46148.83899305556</v>
+        <v>46153.30449074074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2052132248523288581</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052132248523288581</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/1995473147164864765</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE وين الخصوصية اصبحت بلا خصوصية و تكلمت بمشاكل في التطبيق مع امكانية الوصول قبل بضع ايام و اعتقد الحل الوحيد اغلق الحساب و اترك القسم الجاهل في جهله</t>
+          <t>لمصاريفك الطبية، ومنتجات الصيدلية 
+احصل على 5% كاش باك مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/W4PgwsalPI https://t.co/6W6nmKBZFi</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1778101429000</v>
+        <v>1764592847000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/G7FYQAHWsAAam4s.jpg', 'type': 'photo', 'id': '1995473141833838592'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -979,55 +984,50 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2052057840244646114</t>
-        </is>
-      </c>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46149.04431712963</v>
+        <v>45992.69498842592</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2052239541616906712</t>
+          <t>2052787631394619720</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052239541616906712</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2052787631394619720</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@hamad5uae مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل إلى 
-social@EmiratesNBD.com</t>
+          <t>@EmiratesNBD_KSA وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1778127010000</v>
+        <v>1778257684000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174682, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1054,50 +1054,50 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2052132248523288581</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46149.34039351852</v>
+        <v>46150.85282407407</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2052264638478475341</t>
+          <t>2052788405314912358</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052264638478475341</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052788405314912358</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>@JJPnlXDGrYuyPOA مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1778132993000</v>
+        <v>1778257869000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1124,50 +1124,50 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2052239541616906712</t>
+          <t>2052787631394619720</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46149.4096412037</v>
+        <v>46150.85496527778</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2052281866342789437</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052281866342789437</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@hamad5uae سنبذل قصارى جهدنا لمعالجة الأمر في أسرع وقت ممكن وتقديم الدعم اللازم.</t>
+          <t>@EmiratesNBD_KSA 0545876007</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1778137101000</v>
+        <v>1778433856000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174682, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1194,50 +1194,50 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2052264638478475341</t>
+          <t>2052788405314912358</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46149.4571875</v>
+        <v>46152.89185185185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2053526867391439240</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053526867391439240</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+          <t>@JJPnlXDGrYuyPOA لقد شاركنا بياناتك مع فريقنا، وسيتواصلون معك في أقرب وقت ممكن. شكرًا لك.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1778139899000</v>
+        <v>1778433932000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1264,50 +1264,50 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2052281866342789437</t>
+          <t>2053526548691505417</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46149.48957175926</v>
+        <v>46152.89273148148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2052295354821886462</t>
+          <t>2053522784718876695</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052295354821886462</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053522784718876695</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@hamad5uae يرجى العلم بأن فريقنا سيرد على بريدك الإلكتروني في أقرب وقت ممكن. شكرًا لك.</t>
+          <t>@EmiratesNBD_KSA وش المشكلة في بطاقة مزيد تسديد الفواتير معلق والمبلغ مسحوب واسترداد النقاط الى نقود متعطل اول مره تسوي كذا معي كم رقم التواصل ؟؟</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1778140317000</v>
+        <v>1778432959000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174682, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1334,64 +1334,64 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052788405314912358</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46149.49440972223</v>
+        <v>46152.88146990741</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2053214685823221984</t>
+          <t>2053523237905047897</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053523237905047897</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الفريق رد برد غبي يقول هاذا عند التحقق و هاذا غير صحيح و صدّر تحديث اليوم اعتقدت انه بيحل الاشكال ولاكن التجاهل واضح يا من يّدعي الخصوصية الخصوصية اصبحت كلام يقال عند الحاجة https://t.co/wNobGBoYBp</t>
+          <t>@JJPnlXDGrYuyPOA مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1778359502000</v>
+        <v>1778433067000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH573vQbYAA8x1B.jpg', 'type': 'photo', 'id': '2053214677635915776'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1404,118 +1404,120 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2052295354821886462</t>
+          <t>2053522784718876695</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46152.03127314815</v>
+        <v>46152.88271990741</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/Researchpub9/status/2053137035909648470</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2053137035909648470</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2053105582903525791</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/thefaksa/status/2053105582903525791</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
-#معاً_نصنع_الأثر
-#الأكاديمية_المالية https://t.co/4OzuLTEgnR</t>
+          <t>@EmiratesNBD_KSA للاسف مافيه احد يرد على الرقم المجاني ولا زالت المشكلة قائمة ؟؟؟</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1778333490000</v>
+        <v>1778433622000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2053105582903525791</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053089968336027650/img/QwhCexoroVTnRewR.jpg', 'type': 'video', 'id': '2053089968336027650'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'الأكاديمية المالية', 'screenName': 'thefaksa', 'followersCount': 71026, 'favouritesCount': 1502, 'friendsCount': 9, 'description': 'نطور كفاءاتنا الوطنية في القطاع المالي لنحقق #رؤية_السعودية_2030 ونبني وطنًا طموحاً باقتصادٍ مزدهر | خدمة العملاء @TheFA_Care'}</t>
+          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2053523237905047897</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>46151.73020833333</v>
+        <v>46152.88914351852</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/Researchpub9/status/2053137035909648470</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2053137035909648470</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2053137035909648470</t>
+          <t>2053526205094076571</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/Researchpub9/status/2053137035909648470</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053526205094076571</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@thefaksa @EmiratesNBD_KSA برنامج مميز يعزز مهارات القيادة وصناعة القرار</t>
+          <t>@JJPnlXDGrYuyPOA يرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة، حتى نتمكن من ترتيب اتصال من فريقنا لمساعدتك. شكرًا.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1778340989000</v>
+        <v>1778433774000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2053105582903525791</t>
+          <t>1995473147164864765</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1525,7 +1527,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'المنارة | النشر العلمي', 'screenName': 'Researchpub9', 'followersCount': 1837, 'favouritesCount': 4058, 'friendsCount': 1749, 'description': 'تحويل البحث إلى ورقة قابلة للنشر\nتجهيز، تنسيق، واستيفاء متطلبات المجلات المحكمة\nللباحثين في السعودية والخليج.\n\nرابط الواتساب: https://t.co/sRCeRvP2FU'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1538,66 +1540,64 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2053105582903525791</t>
+          <t>2053525568876863654</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46151.81700231481</v>
+        <v>46152.89090277778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022164979216734</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2053022164979216734</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022161426579741</t>
+          <t>https://x.com/WahibaEsri/status/2053101582175326235</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
-💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات https://t.co/gS3flllhnr</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1778313601000</v>
+        <v>1778332536000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzynV6XoAAPJ3W.jpg', 'type': 'photo', 'id': '2052782287884886016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzynirWIAIVHd5.jpg', 'type': 'photo', 'id': '2052782291311534082'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzynrSXEAMWKoU.jpg', 'type': 'photo', 'id': '2052782293622657027'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzyn0vWUAE3zo8.jpg', 'type': 'photo', 'id': '2052782296160161793'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18500, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1610,62 +1610,60 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>46151.50001157408</v>
+        <v>46151.71916666667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022164979216734</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2053022164979216734</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2053022164979216734</t>
+          <t>2053108968772231287</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022164979216734</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053108968772231287</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-https://t.co/NnqfsCP9UY https://t.co/8JZzPt4B2r</t>
+          <t>@WahibaEsri Hi Wahiba, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1778313602000</v>
+        <v>1778334297000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzypr5XwAMzx7T.jpg', 'type': 'photo', 'id': '2052782328146018307'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzyp3hWAAIf7aN.jpg', 'type': 'photo', 'id': '2052782331266465794'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzyrupWgAAOcsO.jpg', 'type': 'photo', 'id': '2052782363243872256'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzyr4AXMAAHvUz.jpg', 'type': 'photo', 'id': '2052782365756305408'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18500, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174679, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1682,52 +1680,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46151.50002314815</v>
+        <v>46151.73954861111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022164979216734</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2053022164979216734</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2053022168665993266</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022168665993266</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships</t>
+          <t>@EmiratesNBD_AE Sure will send now. Thank you 😊</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1778313602000</v>
+        <v>1778385234000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1737,7 +1733,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18500, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1750,159 +1746,1407 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2053022164979216734</t>
+          <t>2053108968772231287</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46151.50002314815</v>
+        <v>46152.32909722222</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053022161426579741</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2053022161426579741</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2053348695387566423</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053348695387566423</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>@WahibaEsri Thank you for your email, our team will be checking your concern and respond to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1778391453000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2053101582175326235</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174679, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2053322615134273715</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46152.40107638889</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2053371316946780420</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2053371316946780420</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UAE controls Pakistan Banking sector 
+BANKS owned by UAE in PK(not complete list)  
+1. Alfalah  
+2. Dubai Islamic  
+3. Mashreq  
+4. Emirates NBD  
+5. Emirates Global  
+6. FWB  
+7. Al Baraka  
+8. BML
+9. Ubank  
+10. EasyPaisa  
+11. Jazzcash   
+#Islamabad #Pakistan #UAE https://t.co/cQoloUd86h</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1778396846000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2053371316946780420</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8KEK6XQAIASsM.jpg', 'type': 'photo', 'id': '2053371021869137922'}]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 23, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
+        <v>46152.46349537037</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2053371316946780420</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2053405007911788583</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2053405007911788583</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>always ready for action 
+#pakistan
+#india
+#ISPR https://t.co/7gl8CZT9i7</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1778404878000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2053405007911788583</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053400479992791040/img/hGw964ak9gc_rybe.jpg', 'type': 'video', 'id': '2053400479992791040'}]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 23, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>46152.55645833333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2048745045147123736</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1777293857000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>46139.69741898148</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1777893777000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>46146.6409375</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2051263125849010218</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051263125849010218</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>@anwarquadri7 Hello, We have replied to your message in private</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1777894214000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>46146.64599537037</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2051521697107382583</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051521697107382583</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Thank you; I await your team's response.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1777955862000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2051263125849010218</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>46147.35951388889</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2052110494291362208</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2052110494291362208</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear NBD, Despite submitting a credit card cancellation request over a month ago, and sending multiple reminders, you have now issued a new statement invoice. This is unacceptable. Confirm the cancellation immediately and reverse all unjustified charges.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1778096242000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2051521697107382583</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46148.98428240741</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear NBD, I received a call again from your representative confirming the cancellation and due amount reversal. But no confirmation is received via email or SMS. Please confirm officially as your team's verbal confirmations are not documented.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1778390578000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2052110494291362208</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46152.39094907408</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2053360805735702593</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053360805735702593</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>@anwarquadri7 Kindly note the same has been advised to our team for further assistance.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1778394340000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2053345026277576901</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46152.43449074074</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2053511203826139552</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2053511203826139552</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ICYMI: Emirates Islamic launches UAE’s first Shariah-Compliant Certificate of Deposit Programme https://t.co/Duoa8LYbvQ</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1778430198000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2053511203826139552</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1135, 'favouritesCount': 24603, 'friendsCount': 310, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>46152.84951388889</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2053511203826139552</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2053672771092136179</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2053672771092136179</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Now that Judaism has been contained in America, it becomes public policy to ensure the U.S. has no official state religion, as established by the Constitution to ensure religious freedom. The First Amendment prohibits Congress from establishing a religion. https://t.co/KBJFSkYS8U</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1778468718000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2053672771092136179</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1135, 'favouritesCount': 24603, 'friendsCount': 310, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="2" t="n">
+        <v>46153.29534722222</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414744829100530</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ندعمك مع نمو أعمالك وتوسعها. تتيح لك باقة الأعمال الذهبية من الإمارات الإسلامي الاستفادة من مدير علاقة خاص بك، وتسعير تفضيلي على منتجات التمويل والتجارة، وحتى 75 معاملة مجانية في الفروع شهرياً لتلبية احتياجاتك المتزايدة في الفروع بكل سهولة. https://t.co/bsQCtKQ9M1</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1778407200000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH5Rt7NWcAENOmg.jpg', 'type': 'photo', 'id': '2053168329557176321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HH5RuJzXsAITDNC.jpg', 'type': 'photo', 'id': '2053168333474738178'}]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="n">
+        <v>46152.58333333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2053414748482396213</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414748482396213</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، تفضل بزيارة:
+https://t.co/9lFTBHae18</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1778407201000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>46152.58334490741</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Supporting you as your business grows. Emirates Islamic Business Gold package offers you a dedicated Relationship Manager, exclusive pricing on financing and trade products, and up to 75 free counter transactions every month to handle higher branch activity with ease.</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1778407201000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2053414748482396213</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46152.58334490741</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2053414752643096586</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053414752643096586</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Learn more: https://t.co/jPBUeB7EVE</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1778407202000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2053414744829100530</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2053414750998941703</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46152.58335648148</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2053373220359639274</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2053373220359639274</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>The Middle East Specialised Cables Company (MESC), has announced that it has obtained sharia-compliant funding worth SAR110 million ($29.3 million) from the UAE's Emirates Islamic Bank.
+Read more on https://t.co/Iohw3gs4cT
+#GINews #Manufacturer #Cables #SaudiArabia https://t.co/NKwJQGHxFX</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1778397300000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2053373220359639274</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH7z7BpaQAAtDg9.jpg', 'type': 'photo', 'id': '2053346675507478528'}]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 107, 'favouritesCount': 18, 'friendsCount': 187, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>46152.46875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2053373220359639274</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2053471367086112970</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/GulfIndustryOn/status/2053471367086112970</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>The UAE Ministry of Industry and Advanced Technology, Emirates Development Bank &amp;amp; ADNOC have signed a memorandum of understanding.
+Read more on https://t.co/XL01aIrdJ2
+#GINews #MoU #IndustrialFund #Abudhabi https://t.co/aPwODIhqKU</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1778420700000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2053471367086112970</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8-Fd6a8AEY5E8.jpg', 'type': 'photo', 'id': '2053428218754166785'}]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 107, 'favouritesCount': 18, 'friendsCount': 187, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
+        <v>46152.73958333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2053384545815163241</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2053384545815163241</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Big goals don’t happen all at once.
+They take shape through small, consistent steps.
+When there’s a clear direction, every step starts to feel more meaningful.
+And over time, those steps quietly turn into real progress.
+#Finwell #FinancialWellbeing #EmiratesIslamic https://t.co/F28Rc1z9vt</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1778400000000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2053384545815163241</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2053176394633338886/pu/img/i7ZqY7HdP86qLlpS.jpg', 'type': 'video', 'id': '2053176394633338886'}]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
+        <v>46152.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2053384545815163241</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>2053052358729376236</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2053052358729376236</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>ادفع أعمالك إلى مستوى أعلى مع خدمات مصرفية مصممة لك. توفّر لك الباقة المميزة للأعمال من الإمارات الإسلامي مزايا مجمعة للمعاملات، وأسعار ربح تنافسية على حلول التمويل، وقنوات رقمية مريحة لتتفرغ لنمو عملك بدلاً من الأعمال الإدارية.
 https://t.co/r83TOi6WkA https://t.co/tVFefsmql9</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="F39" t="n">
         <v>1778320800000</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2053052358729376236</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzI9nSWUAI55Gj.jpg', 'type': 'photo', 'id': '2052736491017621506'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzI9zAXIAQacLI.jpg', 'type': 'photo', 'id': '2052736494163402756'}]</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18500, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>4</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" s="2" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
         <v>46151.58333333334</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053022170373083445</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2053022170373083445</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2053022170373083445</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053022170373083445</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>📅Offer valid till 31 May 2026.
-Terms &amp;amp; Conditions apply.
-https://t.co/WaJZP5JRva</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1778313603000</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2053022161426579741</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18500, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2053022168665993266</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46151.50003472222</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,113 +517,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
+          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2053544670014107870</t>
+          <t>2053946052726936040</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2053539327305560098</t>
+          <t>2053820075002438016</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/FinTech_KSA/status/2053539327305560098</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053820075002438016</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>كل ما تحتاج معرفته من البنوك لمحفظة جوجل
-Google Wallet في السعودية 🇸🇦 💳
-وين باقي الشباب 💀 https://t.co/9aXtCcnI0m</t>
+          <t>الحياة مليئة باللحظات. ونحن ندعمها كلّها.
+مع القروض الشخصية من بنك الإمارات دبي الوطني، احصل على الدعم المالي الذي تحتاجه لكل خططك.
+  https://t.co/HiEGCc4hi9 :قدّم الآن https://t.co/NCigHqexuW</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1778436903000</v>
+        <v>1778503838000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2053539327305560098</t>
+          <t>2053820075002438016</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH-jIQ6WIAAdMEm.jpg', 'type': 'photo', 'id': '2053539317478203392'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HICiePKXoAAhklU.jpg', 'type': 'video', 'id': '2053820035664097280'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'iipupii🤳💳', 'screenName': 'FinTech_KSA', 'followersCount': 15671, 'favouritesCount': 3842, 'friendsCount': 258, 'description': 'مهتم بالتقنية المالية والمدفوعات الرقمية 💳📱\n#Fintech #Payments #Banking #Cards #DigitalWallets #DigitalCommerce'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>257</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46152.92711805556</v>
+        <v>46153.70182870371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
+          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2053544670014107870</t>
+          <t>2053946052726936040</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2053544670014107870</t>
+          <t>2053946052726936040</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
+          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@FinTech_KSA @EmiratesNBD_KSA فينكم</t>
+          <t>@EmiratesNBD_AE رد فريقكم و ارسلت لهم و ما ردو الاشكال ناوين تحلونه ولا مستمرين بلتجاهل؟؟؟؟ https://t.co/OCh03ntFpy</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1778438177000</v>
+        <v>1778533874000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2053539327305560098</t>
+          <t>2053820075002438016</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIEVCEybQAAk5j6.jpg', 'type': 'photo', 'id': '2053946030446821376'}]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Mamdouh Safa', 'screenName': 'mamdouh_safa', 'followersCount': 19, 'favouritesCount': 101, 'friendsCount': 346, 'description': '\u200f🤔🤔🤔🤔🤔'}</t>
+          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -640,50 +640,51 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2053539327305560098</t>
+          <t>2053820075002438016</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46152.94186342593</v>
+        <v>46154.04946759259</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/mamdouh_safa/status/2053544670014107870</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2053544670014107870</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2053678312044511470</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053678312044511470</t>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@mamdouh_safa مرحبا محمود شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
+          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1778470039000</v>
+        <v>1777882561000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2053539327305560098</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -693,11 +694,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -710,64 +711,60 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2053544670014107870</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46153.31063657408</v>
+        <v>46146.51112268519</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2053561102663885109</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2053404320901505163</t>
+          <t>2051219105496150060</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053404320901505163</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2051219105496150060</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>انجز كل عملياتك المصرفية وسدد كل فواتيرك بسهولة من تطبيق ENBD X📲 https://t.co/zf5cSFztjt</t>
+          <t>@FF1991Whooo We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007505 in the subject line.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1778404715000</v>
+        <v>1777883719000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2053404320901505163</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8oWNzWkAIyRow.jpg', 'type': 'photo', 'id': '2053404317231517698'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -780,46 +777,51 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2051214248865656992</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="n">
-        <v>46152.55457175926</v>
+        <v>46146.52452546296</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2053561102663885109</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2053561102663885109</t>
+          <t>2052657495840285062</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
+          <t>https://x.com/FF1991Whooo/status/2052657495840285062</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA لا استطيع تحويل النقاط</t>
+          <t>@EmiratesNBD_AE No difference! Had sent an email right after this, usual 'escalated to the team' was the reply.
+Next payment due is 10 May, bcz you'll will drag this &amp;amp; I'll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y'all!!</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1778442094000</v>
+        <v>1778226658000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2053404320901505163</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -829,11 +831,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Qusai Alsaffar', 'screenName': 'QusaiAlsaffar', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -846,50 +848,50 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2053404320901505163</t>
+          <t>2051219105496150060</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46152.98719907407</v>
+        <v>46150.49372685186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/QusaiAlsaffar/status/2053561102663885109</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2053561102663885109</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2053676082763571444</t>
+          <t>2052659227227754933</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053676082763571444</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052659227227754933</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@QusaiAlsaffar مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص ورقم هاتفك المسجل حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>@FF1991Whooo We are extremely sorry for the delay and our team will review your email and help you out accordingly and update you on urgent basis.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1778469508000</v>
+        <v>1778227070000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2053404320901505163</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -899,11 +901,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -916,66 +918,64 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2053561102663885109</t>
+          <t>2052657495840285062</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46153.30449074074</v>
+        <v>46150.49849537037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2053439591856889966</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/1995473147164864765</t>
+          <t>https://x.com/FF1991Whooo/status/2053439591856889966</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>لمصاريفك الطبية، ومنتجات الصيدلية 
-احصل على 5% كاش باك مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/W4PgwsalPI https://t.co/6W6nmKBZFi</t>
+          <t>@EmiratesNBD_AE Today is the due date, I logged in to the app and I cant even find the card instead showing a negative 100 balance! I cant keep running behind this. Please clear them all so I can just get out of this trouble!!</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1764592847000</v>
+        <v>1778413124000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/G7FYQAHWsAAam4s.jpg', 'type': 'photo', 'id': '1995473141833838592'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -984,50 +984,54 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2052659227227754933</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="n">
-        <v>45992.69498842592</v>
+        <v>46152.65189814815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2052787631394619720</t>
+          <t>2053439958275301610</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2052787631394619720</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053439958275301610</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
+          <t>@FF1991Whooo We have already replied to you email, and also we are following up with our team to resolve your issue and will update you email as soon as possible.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1778257684000</v>
+        <v>1778413211000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1054,64 +1058,64 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2053439591856889966</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46150.85282407407</v>
+        <v>46152.65290509259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2052788405314912358</t>
+          <t>2053744584279416892</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052788405314912358</t>
+          <t>https://x.com/FF1991Whooo/status/2053744584279416892</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@JJPnlXDGrYuyPOA مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
+          <t>@EmiratesNBD_AE NO! they sent email saying all the amount will be reversed and updated which I trusted and waited. And today just a few mins ago I recived this email! For a less than 20AED all this started, and now youre adding overdue again and again. Ive been chasing y'all for the longest! https://t.co/64ln3qwfCh</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1778257869000</v>
+        <v>1778485840000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBd0M3a8AAltBX.jpg', 'type': 'photo', 'id': '2053744581469204480'}]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1124,50 +1128,50 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2052787631394619720</t>
+          <t>2053439958275301610</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46150.85496527778</v>
+        <v>46153.49351851852</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053771047145460107</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053771047145460107</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 0545876007</t>
+          <t>@FF1991Whooo Apologies for any inconvenience caused. Please share with us the same via email conversation. We certainly review it and assist you accordingly.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1778433856000</v>
+        <v>1778492149000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1194,50 +1198,51 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2052788405314912358</t>
+          <t>2053744584279416892</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46152.89185185185</v>
+        <v>46153.56653935185</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053526548691505417</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2053526867391439240</t>
+          <t>2053786818806734879</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053526867391439240</t>
+          <t>https://x.com/FF1991Whooo/status/2053786818806734879</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@JJPnlXDGrYuyPOA لقد شاركنا بياناتك مع فريقنا، وسيتواصلون معك في أقرب وقت ممكن. شكرًا لك.</t>
+          <t>@EmiratesNBD_AE HAVE ALREADY SENT AN EMAIL the moment I received this, &amp;amp; till now there's no response.  WHY ARE YOU ASKING TO CONTACT IF THERE'S NO ACTION BEEN TAKING RATHER MAKING IT WORSE FOR US?
+You promised about waiving the amount &amp;amp; to check the app later, &amp;amp; the next day I get this email?</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1778433932000</v>
+        <v>1778495909000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1247,11 +1252,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1264,50 +1269,50 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2053526548691505417</t>
+          <t>2053771047145460107</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46152.89273148148</v>
+        <v>46153.61005787037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2053522784718876695</t>
+          <t>2053790086836183455</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053522784718876695</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053790086836183455</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA وش المشكلة في بطاقة مزيد تسديد الفواتير معلق والمبلغ مسحوب واسترداد النقاط الى نقود متعطل اول مره تسوي كذا معي كم رقم التواصل ؟؟</t>
+          <t>@FF1991Whooo Hello, kindly note that our team is working on replying to the email as soon as possible.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1778432959000</v>
+        <v>1778496688000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1317,7 +1322,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1334,50 +1339,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2052788405314912358</t>
+          <t>2053786818806734879</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46152.88146990741</v>
+        <v>46153.61907407407</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2053523237905047897</t>
+          <t>2053830887448748503</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053523237905047897</t>
+          <t>https://x.com/FF1991Whooo/status/2053830887448748503</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@JJPnlXDGrYuyPOA مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+          <t>@EmiratesNBD_AE Ive been trusting this 'as soon as possible' and then you've kept on addinh overdue charges on it. Seriously for a AED20 something, bcz of your team's irresponsible behaviour its gone with AED400+ Why would you want to make customers run behind y'all??</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1778433067000</v>
+        <v>1778506416000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1387,7 +1392,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1404,50 +1409,50 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2053522784718876695</t>
+          <t>2053790086836183455</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46152.88271990741</v>
+        <v>46153.73166666667</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053842145887260736</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053842145887260736</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA للاسف مافيه احد يرد على الرقم المجاني ولا زالت المشكلة قائمة ؟؟؟</t>
+          <t>@FF1991Whooo Apologies for any inconvenience caused. We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1778433622000</v>
+        <v>1778509100000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'سلطان الصاعدي', 'screenName': 'JJPnlXDGrYuyPOA', 'followersCount': 223, 'favouritesCount': 43, 'friendsCount': 645, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1474,64 +1479,66 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2053523237905047897</t>
+          <t>2053830887448748503</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46152.88914351852</v>
+        <v>46153.76273148148</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2053525568876863654</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2053526205094076571</t>
+          <t>2053881673440428301</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053526205094076571</t>
+          <t>https://x.com/FF1991Whooo/status/2053881673440428301</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@JJPnlXDGrYuyPOA يرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة، حتى نتمكن من ترتيب اتصال من فريقنا لمساعدتك. شكرًا.</t>
+          <t>@EmiratesNBD_AE And this is what I received now!
+What are you guys upto?
+Delaying the process and increasing the customer's overdue wherein they dont even have an overdue. And then closing the issue by saying its resolved, while I can still see my app showing same negative aswl the overdue! https://t.co/Fhjouj0rk6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1778433774000</v>
+        <v>1778518524000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1995473147164864765</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDaf0WakAAxOe_.jpg', 'type': 'photo', 'id': '2053881670244405248'}]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1540,54 +1547,54 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2053525568876863654</t>
+          <t>2053842145887260736</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46152.89090277778</v>
+        <v>46153.87180555556</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053890991636062391</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053101582175326235</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053890991636062391</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
+          <t>@FF1991Whooo Hello, we will check your request and reply to the email as soon as possible.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1778332536000</v>
+        <v>1778520746000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1597,7 +1604,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1614,56 +1621,61 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2053881673440428301</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="n">
-        <v>46151.71916666667</v>
+        <v>46153.89752314815</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2053108968772231287</t>
+          <t>2053893546001018992</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053108968772231287</t>
+          <t>https://x.com/FF1991Whooo/status/2053893546001018992</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@WahibaEsri Hi Wahiba, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>@EmiratesNBD_AE What are you trying to do?
+It's as simple as to waive off the amount that occurred bcz of your team's negligence, &amp;amp; also the amount that got addea a day a before bcz you delayed the process &amp;amp; you mentioned that not to worry &amp;amp; it will be waived off. I've email proof of all this! https://t.co/XsVNWNGv1I</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1778334297000</v>
+        <v>1778521355000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDlS4RaAAAxPfu.jpg', 'type': 'photo', 'id': '2053893542586744832'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDlS64a8AAvQVF.jpg', 'type': 'photo', 'id': '2053893543287255040'}]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174679, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1680,50 +1692,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2053890991636062391</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46151.73954861111</v>
+        <v>46153.90457175926</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053895589192950144</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053895589192950144</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Sure will send now. Thank you 😊</t>
+          <t>@FF1991Whooo Hello, kindly note that we can only reply via email as we are not able to disclose any of your financial details through a social media public platform.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1778385234000</v>
+        <v>1778521842000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1733,7 +1745,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Wahiba Esri', 'screenName': 'WahibaEsri', 'followersCount': 1, 'favouritesCount': 135, 'friendsCount': 9, 'description': 'Mum life in Dubai📍                               Finding joy in the little things✨'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1750,50 +1762,53 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2053108968772231287</t>
+          <t>2053893546001018992</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46152.32909722222</v>
+        <v>46153.91020833333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2053348695387566423</t>
+          <t>2053945581698207970</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053348695387566423</t>
+          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@WahibaEsri Thank you for your email, our team will be checking your concern and respond to you as soon as possible.</t>
+          <t>@EmiratesNBD_AE Exactly!
+The emails you're sending each day is not connected!
+1 day you said you will check, next day you said it'll be waived off, then you send an email saying it's solved, &amp;amp; then again you sent email saying I need to lodge a new compalint! 
+Customers are getting drained out!</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1778391453000</v>
+        <v>1778533761000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2053101582175326235</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1803,7 +1818,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174679, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1820,142 +1835,131 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2053322615134273715</t>
+          <t>2053895589192950144</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46152.40107638889</v>
+        <v>46154.04815972222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2053371316946780420</t>
+          <t>2054012648761835613</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2053371316946780420</t>
+          <t>2053823138442432845</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053823138442432845</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UAE controls Pakistan Banking sector 
-BANKS owned by UAE in PK(not complete list)  
-1. Alfalah  
-2. Dubai Islamic  
-3. Mashreq  
-4. Emirates NBD  
-5. Emirates Global  
-6. FWB  
-7. Al Baraka  
-8. BML
-9. Ubank  
-10. EasyPaisa  
-11. Jazzcash   
-#Islamabad #Pakistan #UAE https://t.co/cQoloUd86h</t>
+          <t>Tech-savvy Um Allawi turns dinner talk into a smart sustainability lesson with the ENBD X carbon calculator, because every transaction tells two stories: one about you and one about the planet.
+Track your carbon footprint, make smarter spending choices, and discover how every dirham can support a more sustainable future.
+What is the name of the ENBD X carbon calculator? Comment below for a chance to win AED 500.
+تحوّل أم علاوي المُلِمّة بالتقنيات الحديثة أحاديث المائدة إلى درس ذكي في الاستدامة من خلال حاسبة البصمة الكربونية في ENBD X لأن كل معاملة تروي قصتين: واحدة عنك، وأخرى عن الكوكب.
+تابع بصمتك الكربونية، واتخذ قرارات إنفاق أكثر ذكاءً، واكتشف كيف يمكن لكل درهم أن يدعم مستقبلًا أكثر استدامة.
+ما اسم حاسبة البصمة الكربونية في ENBD X؟ شارك إجابتك في التعليقات لتحصل على فرصة للفوز بـ 500 درهم.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1778396846000</v>
+        <v>1778504569000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2053371316946780420</t>
+          <t>2053823138442432845</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8KEK6XQAIASsM.jpg', 'type': 'photo', 'id': '2053371021869137922'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053823018510512129/img/s9nsGhTTq-0KywPV.jpg', 'type': 'video', 'id': '2053823018510512129'}]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 23, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>321</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46152.46349537037</v>
+        <v>46153.71028935185</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2053371316946780420</t>
+          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2053371316946780420</t>
+          <t>2054012648761835613</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2053405007911788583</t>
+          <t>2054012648761835613</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2053405007911788583</t>
+          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>always ready for action 
-#pakistan
-#india
-#ISPR https://t.co/7gl8CZT9i7</t>
+          <t>@EmiratesNBD_AE Green Pulse</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1778404878000</v>
+        <v>1778549751000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2053405007911788583</t>
+          <t>2053823138442432845</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053400479992791040/img/hGw964ak9gc_rybe.jpg', 'type': 'video', 'id': '2053400479992791040'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 23, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'naveed sadiq', 'screenName': 'mnsadiq84', 'followersCount': 223, 'favouritesCount': 140333, 'friendsCount': 189, 'description': '😊'}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1970,115 +1974,116 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="n">
-        <v>46152.55645833333</v>
+        <v>46154.23322916667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2048745045147123736</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dear Emirates NBD,
-I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777293857000</v>
+        <v>1777780354000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamTYXgAAT-o_.jpg', 'type': 'photo', 'id': '2050785556909490176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamj9XMAAx1Ze.jpg', 'type': 'photo', 'id': '2050785561359626240'}]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46139.69741898148</v>
+        <v>46145.3281712963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2051261292133130490</t>
+          <t>2051188760185049183</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+          <t>@EmiratesNBD_AE After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777893777000</v>
+        <v>1777876484000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2088,7 +2093,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Mahmoud Moawad', 'screenName': 'mahmoudmoawad00', 'followersCount': 5, 'favouritesCount': 1513, 'friendsCount': 274, 'description': ''}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2105,50 +2110,50 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46146.6409375</v>
+        <v>46146.44078703703</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2051263125849010218</t>
+          <t>2051204201930190866</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2051263125849010218</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2051204201930190866</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@anwarquadri7 Hello, We have replied to your message in private</t>
+          <t>@mahmoudmoawad00 We are sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007406 in the subject line.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777894214000</v>
+        <v>1777880165000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2158,7 +2163,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2175,50 +2180,50 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2051261292133130490</t>
+          <t>2051188760185049183</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46146.64599537037</v>
+        <v>46146.48339120371</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2051521697107382583</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2051521697107382583</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Thank you; I await your team's response.</t>
+          <t>@EmiratesNBD_AE It has been 6 days since I last received an email from your support team, and there is still no update. The problem remains unresolved</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777955862000</v>
+        <v>1778522330000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2228,11 +2233,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Mahmoud Moawad', 'screenName': 'mahmoudmoawad00', 'followersCount': 5, 'favouritesCount': 1513, 'friendsCount': 274, 'description': ''}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2245,50 +2250,50 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2051263125849010218</t>
+          <t>2051204201930190866</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46147.35951388889</v>
+        <v>46153.91585648148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2052110494291362208</t>
+          <t>2053898727593476195</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2052110494291362208</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053898727593476195</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dear NBD, Despite submitting a credit card cancellation request over a month ago, and sending multiple reminders, you have now issued a new statement invoice. This is unacceptable. Confirm the cancellation immediately and reverse all unjustified charges.</t>
+          <t>@mahmoudmoawad00 Hello, we will check and update you via email as soon as possible.</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1778096242000</v>
+        <v>1778522590000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2298,11 +2303,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2315,50 +2320,53 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2051521697107382583</t>
+          <t>2053897635736731778</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46148.98428240741</v>
+        <v>46153.91886574074</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/naser8581/status/2053051787704164789</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dear NBD, I received a call again from your representative confirming the cancellation and due amount reversal. But no confirmation is received via email or SMS. Please confirm officially as your team's verbal confirmations are not documented.</t>
+          <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1778390578000</v>
+        <v>1778320664000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2368,7 +2376,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 0, 'favouritesCount': 974, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2385,50 +2393,46 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2052110494291362208</t>
-        </is>
-      </c>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46152.39094907408</v>
+        <v>46151.58175925926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2053345026277576901</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2053360805735702593</t>
+          <t>2053060206704177587</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2053360805735702593</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053060206704177587</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@anwarquadri7 Kindly note the same has been advised to our team for further assistance.</t>
+          <t>@naser8581 نحن آسفون جدًا لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1010403 في موضوع الرسالة.</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1778394340000</v>
+        <v>1778322671000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2048745045147123736</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17474, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2455,50 +2459,51 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2053345026277576901</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46152.43449074074</v>
+        <v>46151.60498842593</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2053511203826139552</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2053511203826139552</t>
+          <t>2053161447048249627</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+          <t>https://x.com/naser8581/status/2053161447048249627</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ICYMI: Emirates Islamic launches UAE’s first Shariah-Compliant Certificate of Deposit Programme https://t.co/Duoa8LYbvQ</t>
+          <t>@EmiratesNBD_EGY تم ارسال ايميل بذلك 
+نامل المعالجة وافادتي برقم ايصال سداد المديونية</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1778430198000</v>
+        <v>1778346809000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2053511203826139552</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2508,11 +2513,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1135, 'favouritesCount': 24603, 'friendsCount': 310, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2525,46 +2530,50 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2053060206704177587</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>46152.84951388889</v>
+        <v>46151.88436342592</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2053511203826139552</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2053511203826139552</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2053672771092136179</t>
+          <t>2053162375499403688</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2053672771092136179</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053162375499403688</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Now that Judaism has been contained in America, it becomes public policy to ensure the U.S. has no official state religion, as established by the Constitution to ensure religious freedom. The First Amendment prohibits Congress from establishing a religion. https://t.co/KBJFSkYS8U</t>
+          <t>@naser8581 سيقوم فريقنا بمراجعة بريدك الإلكتروني والرد عليك في أقرب وقت ممكن. شكرًا لك.</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1778468718000</v>
+        <v>1778347030000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2053672771092136179</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2574,7 +2583,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1135, 'favouritesCount': 24603, 'friendsCount': 310, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2591,56 +2600,61 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2053161447048249627</t>
+        </is>
+      </c>
       <c r="P31" s="2" t="n">
-        <v>46153.29534722222</v>
+        <v>46151.8869212963</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2053414750998941703</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2053414744829100530</t>
+          <t>2053341306580066658</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053414744829100530</t>
+          <t>https://x.com/naser8581/status/2053341306580066658</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ندعمك مع نمو أعمالك وتوسعها. تتيح لك باقة الأعمال الذهبية من الإمارات الإسلامي الاستفادة من مدير علاقة خاص بك، وتسعير تفضيلي على منتجات التمويل والتجارة، وحتى 75 معاملة مجانية في الفروع شهرياً لتلبية احتياجاتك المتزايدة في الفروع بكل سهولة. https://t.co/bsQCtKQ9M1</t>
+          <t>@EmiratesNBD_EGY تم الرد على الايميل 
+كرماً الاطلاع بشكل عاجل</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1778407200000</v>
+        <v>1778389691000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2053414744829100530</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH5Rt7NWcAENOmg.jpg', 'type': 'photo', 'id': '2053168329557176321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HH5RuJzXsAITDNC.jpg', 'type': 'photo', 'id': '2053168333474738178'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2653,500 +2667,3040 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2053162375499403688</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n">
-        <v>46152.58333333334</v>
+        <v>46152.38068287037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2053414750998941703</t>
+          <t>2053921015097696546</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2053414748482396213</t>
+          <t>2053348429305184435</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2053414748482396213</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053348429305184435</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
+        <is>
+          <t>@naser8581 يرجى التحقق من بريدك الالكتروني حيث قام فريقنا بمراسلتك.</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1778391389000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2053341306580066658</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>46152.40033564815</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2053921015097696546</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2053368822678122695</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2053368822678122695</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_EGY تم الرد على طلب المعلومات وتم تزويدهم بها سابقاً
+نامل معالجة الاشكالية</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1778396251000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2053348429305184435</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46152.4566087963</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2053921015097696546</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2053374720087646697</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053374720087646697</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>@naser8581 شكراً لتأكيدك, سيتم التحقق والرد عليك في أقرب وقت ممكن.</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1778397657000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2053368822678122695</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46152.47288194444</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2053921015097696546</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2053921015097696546</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2053921015097696546</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_EGY @DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+لم يتم حل الاشكالية حتى تاريخه
+المطلوب تزويدي بايصال الحوالة لسداد مديونية امكان لمتابعة انهاء اجراءاتها وتزويدكم بالمخالصة ليتم فك الحجز عن التمويل</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1778527904000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2053374720087646697</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46153.98037037037</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://x.com/s3yrah/status/2053841488275280097</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2053841488275280097</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2053841488275280097</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/s3yrah/status/2053841488275280097</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Green Pulse</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1778508943000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'name': 'Sarrah Sumagang', 'screenName': 's3yrah', 'followersCount': 738, 'favouritesCount': 21410, 'friendsCount': 229, 'description': "Saved by grace ❤ Exploring God's wonderful creations. 🌎 Proverbs 3:5-6 📖 IG: @s3yrah\nhttps://t.co/rj0tqaH252"}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46153.76091435185</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://x.com/hussdajani/status/2053845125072035999</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/hussdajani/status/2053845125072035999</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE what is wrong with your app please? This started happening after the update you did on the app today. https://t.co/YEUKI3foTf</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1778509811000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIC5QQ3XMAA1okT.jpg', 'type': 'photo', 'id': '2053845119137165312'}]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'name': 'Hussein M. Dajani - CCXP', 'screenName': 'hussdajani', 'followersCount': 3963, 'favouritesCount': 2556, 'friendsCount': 2084, 'description': 'Dad | C-suite executive I UAE Golden Visa Holder I KSA Premium Residency Holder! Views my own'}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
+        <v>46153.77096064815</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://x.com/hussdajani/status/2053845125072035999</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2053845842230997471</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053845842230997471</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>@hussdajani Hello Hussein, we have replied to your message in private.</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1778509982000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46153.77293981481</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://x.com/hussdajani/status/2053846278493053211</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2053846278493053211</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2053846278493053211</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/hussdajani/status/2053846278493053211</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I saw your reply and didn’t understand anything from it. Please revert back with explanation.</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1778510086000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2053845125072035999</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'Hussein M. Dajani - CCXP', 'screenName': 'hussdajani', 'followersCount': 3963, 'favouritesCount': 2556, 'friendsCount': 2084, 'description': 'Dad | C-suite executive I UAE Golden Visa Holder I KSA Premium Residency Holder! Views my own'}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2053845842230997471</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46153.77414351852</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/khushbuag88/status/2053832735450640496</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2053832735450640496</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2053832735450640496</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/khushbuag88/status/2053832735450640496</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Green Pulse @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1778506857000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 17, 'favouritesCount': 506, 'friendsCount': 96, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46153.73677083333</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://x.com/Almalchannel/status/2053834422399754268</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2053834422399754268</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2053834422399754268</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/Almalchannel/status/2053834422399754268</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>بينما بنوك عالمية تشدّد الإقراض وتضغط الفرامل خوفًا من التباطؤ والمخاطر، تمضي البنوك الإماراتية في الاتجاه المعاكس.
+نمو الإقراض في Emirates NBD بنحو 4% ليس مجرد رقم، بل انعكاس لاقتصاد فعلي نشط، وسيولة مستقرة، وطلب حقيقي من قطاعات مثل العقار، التجارة، والشركات.
+الفرق هنا ليس في الجرأة، بل في البيئة الاقتصادية: استقرار، ثقة، وتمويل موجّه للنمو لا للمخاطرة.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1778507259000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2053834422399754268</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053834289452904448/img/MguqTB7gNhDjnQUB.jpg', 'type': 'video', 'id': '2053834289452904448'}]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'قناة المال | Almal Channel', 'screenName': 'Almalchannel', 'followersCount': 55825, 'favouritesCount': 4669, 'friendsCount': 691, 'description': 'قناة اقتصادية.. هدفنا أن نبسّط المال للعرب'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="n">
+        <v>46153.74142361111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://x.com/Almalchannel/status/2053834422399754268</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2053834422399754268</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2053474043043652051</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/Almalchannel/status/2053474043043652051</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>النمسا… تشتغل على طاقة إماراتية 🇦🇪🇦🇹
+أكثر من 8.2 مليار دولار من أدنوك 🛢️ إلى مشاريع الهيدروجين مع مصدر 🍀
+النتيجة؟  طاقة توصل لفيينا والمطار وحتى الشاحنات 🚛🛃
+هذه مش استثمارات هذه طاقة تشغل أوروبا ⚡️
+Austria is running on Emirati energy 🇦🇪🇦🇹
+From multi-billion investments led by Adnoc 🛢️
+to future-focused hydrogen projects with Masdar 🍀
+This isn’t just an investment
+It’s fueling Europe’s future ⚡️
+#الإمارات #أبوظبي
+#Austria #UAE</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1778421338000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2053474043043652051</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053473922365145088/img/43kOADY-XP6G7ixh.jpg', 'type': 'video', 'id': '2053473922365145088'}]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'قناة المال | Almal Channel', 'screenName': 'Almalchannel', 'followersCount': 55825, 'favouritesCount': 4669, 'friendsCount': 691, 'description': 'قناة اقتصادية.. هدفنا أن نبسّط المال للعرب'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>17</v>
+      </c>
+      <c r="M43" t="n">
+        <v>29</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>65845</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
+        <v>46152.74696759259</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053814281309765800</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2053814281309765800</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2053814281309765800</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053814281309765800</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Life comes in moments. We back them all.
+With Emirates NBD personal loans, get the financial backing you need for every plan. 
+Apply now: https://t.co/fVmF0SZobH https://t.co/dlN4WNjCJe</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1778502457000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2053814281309765800</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HICdNAJXcAAtONl.jpg', 'type': 'video', 'id': '2053814241820352512'}]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="n">
+        <v>46153.68584490741</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053823138442432845</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2053823138442432845</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2054048923551981605</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2054048923551981605</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/xYw9GxVrjg</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1778558400000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2054048923551981605</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053804044641071104/img/_lohyEnt8g6jRqry.jpg', 'type': 'video', 'id': '2053804044641071104'}]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>46154.33333333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795100220936545</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>You set up a UAE freezone company. Got the license. Opened the corporate bank account.
+Now you're staring at revenue thinking: "How do I actually pay myself?"
+Most people get this wrong. Here's how it works:</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1778497884000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
+        <v>46153.63291666667</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2053795114573856838</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795114573856838</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Two paths to get money out of your UAE company:
+1. Pay yourself a salary (you're an employee of your own company)
+2. Take dividend distributions (profit payouts as shareholder)
+Most solo founders should use both. Here's why.</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1778497887000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46153.63295138889</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2053795128570159513</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795128570159513</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>The salary route: create an employment contract with yourself as sole employee.
+Your salary goes through WPS (Wage Protection System) into your personal UAE bank account.
+Mandatory for mainland. Optional for solo freezone companies, but smart to do anyway.</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1778497890000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2053795114573856838</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46153.63298611111</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2053795142965096729</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795142965096729</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Why bother with a salary if it's optional?
+A regular salary creates a clean, documented income trail.
+When you need a mortgage, car loan, or credit card in the UAE, banks want consistent salary deposits. Not random transfers.</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1778497894000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2053795128570159513</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46153.63303240741</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2053795157036908986</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795157036908986</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>The dividend route: once your company has profit after expenses and the 9% corporate tax on profits above AED 375,000, you distribute dividends to yourself.
+No additional tax on dividends in the UAE.
+Corporate profit becomes personal wealth with zero second layer of taxation.</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1778497897000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2053795142965096729</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46153.63306712963</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2053795171419234684</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795171419234684</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>The optimal structure for most solo founders making $10k-$50k/month:
+Set a modest monthly salary (AED 15,000-30,000).
+Accumulate profit in the corporate account.
+Do quarterly dividend distributions.
+Clean. Documented. Tax-efficient.</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1778497901000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2053795157036908986</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46153.63311342592</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2053795185541423579</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795185541423579</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>The number one mistake: mixing personal and corporate funds.
+Treat your corporate account like a personal wallet and it gets frozen. UAE banks monitor this aggressively.
+Two separate accounts. Corporate for business. Personal for salary and dividends. No exceptions.</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1778497904000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2053795171419234684</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46153.63314814815</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>For your personal account:
+Traditional banks (Emirates NBD, ADCB) for full-service banking, credit cards, and loans.
+Neobanks (Wio, YAP) for fast onboarding if you mainly need it for receiving salary.
+Most founders end up with one of each eventually.</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1778497907000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2053795185541423579</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46153.63318287037</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795199613321219</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2053795213701959865</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/zola_app/status/2053795213701959865</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>The setup most people miss: company, visa, corporate bank, and personal bank are all connected.
+Get the order wrong, you waste weeks. Get the banking wrong, you can't pay yourself properly.
+This is infrastructure, not paperwork. Treat it that way.</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1778497911000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2053795100220936545</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'Zola', 'screenName': 'zola_app', 'followersCount': 9, 'favouritesCount': 13, 'friendsCount': 10, 'description': 'Start &amp; scale your business in the UAE 🇦🇪 Company setup, visas &amp; banking made simple. Get your personalized setup'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2053795199613321219</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46153.63322916667</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053805479164354726</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2053805479164354726</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2053805479164354726</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053805479164354726</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Enjoy professional portfolio management through personalised strategies aligned with your financial goals. Gain from our market expertise and experience the freedom that comes with trusted oversight. Learn more https://t.co/6LXBeMI61r
+#EmiratesNBD #DiscretionaryPortfolioManagement</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1778500358000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2053805479164354726</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053805445995798528/img/c27aaWeGoU3cb8oc.jpg', 'type': 'video', 'id': '2053805445995798528'}]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>46153.66155092593</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731859016651241</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731843292213253</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ندعمك مع نمو أعمالك وتوسعها. تتيح لك باقة الأعمال الذهبية من الإمارات الإسلامي الاستفادة من مدير علاقة خاص بك، وتسعير تفضيلي على منتجات التمويل والتجارة، وغيرها المزيد. https://t.co/ls1cnTTsKC</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1778482802000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBSObPXcAAEOf6.jpg', 'type': 'photo', 'id': '2053731837864800256'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBSOlwXoAEdwYz.jpg', 'type': 'photo', 'id': '2053731840687579137'}]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>46153.45835648148</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731859016651241</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2053731855044637139</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731855044637139</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>لمعرفة المزيد، تفضل بزيارة:
 https://t.co/9lFTBHae18</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1778407201000</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2053414744829100530</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="F57" t="n">
+        <v>1778482805000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46153.45839120371</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731859016651241</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731859016651241</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Supporting you as your business grows. Emirates Islamic Business Gold package offers you a dedicated Relationship Manager, exclusive pricing on financing and trade products, and much more.</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1778482806000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2053414744829100530</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46152.58334490741</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2053414750998941703</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2053414750998941703</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Supporting you as your business grows. Emirates Islamic Business Gold package offers you a dedicated Relationship Manager, exclusive pricing on financing and trade products, and up to 75 free counter transactions every month to handle higher branch activity with ease.</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1778407201000</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2053414744829100530</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2053731855044637139</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46153.45840277777</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731859016651241</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2053731860664959393</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053731860664959393</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Learn more: https://t.co/jPBUeB7EVE</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1778482806000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2053731859016651241</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46153.45840277777</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777142312296529</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777135513240054</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>تقدّم لك باقة الأعمال البلاتينية أعلى مستويات الخدمات المصرفية للأعمال. تستفيد من مدير علاقة خاص بك، وتسعير حصري على خدمات التمويل والتجارة، وأسعار صرف تفضيلية للمعاملات الدولية، ومعاملات غير محدودة مجانية في الفروع للتعامل مع حجم معاملاتك المرتفع بكل سهولة. https://t.co/dlZpqZjHUk</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1778493601000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBBBL5WAAAi9jA.jpg', 'type': 'photo', 'id': '2053712918709927936'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBBBYoXUAARxxp.jpg', 'type': 'photo', 'id': '2053712922128371712'}]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>46153.58334490741</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777142312296529</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2053777139778851242</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777139778851242</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>لمعرفة المزيد، تفضل بزيارة:
+https://t.co/B6sdnIA8sC</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1778493602000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>46153.58335648148</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777142312296529</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777142312296529</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Offering the ultimate in business banking. Emirates Islamic Business Platinum package offers you a dedicated Relationship Manager, exclusive pricing on financing and trade services,</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1778493602000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2053414748482396213</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>46152.58334490741</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053414750998941703</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2053414750998941703</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2053414752643096586</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053414752643096586</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Learn more: https://t.co/jPBUeB7EVE</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1778407202000</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2053414744829100530</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2053777139778851242</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>46153.58335648148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777142312296529</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2053777144174518408</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777144174518408</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>special FX rates on your international transactions, and unlimited free counter transactions to handle high‑volume activity with ease.
+Learn more: https://t.co/pQnUfwSeaR</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1778493603000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2053414750998941703</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>46152.58335648148</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2053373220359639274</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2053373220359639274</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>The Middle East Specialised Cables Company (MESC), has announced that it has obtained sharia-compliant funding worth SAR110 million ($29.3 million) from the UAE's Emirates Islamic Bank.
-Read more on https://t.co/Iohw3gs4cT
-#GINews #Manufacturer #Cables #SaudiArabia https://t.co/NKwJQGHxFX</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1778397300000</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2053373220359639274</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH7z7BpaQAAtDg9.jpg', 'type': 'photo', 'id': '2053346675507478528'}]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 107, 'favouritesCount': 18, 'friendsCount': 187, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2053777142312296529</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>46153.58336805556</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/aboodan_94/status/2053771459810509113</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2053771459810509113</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2053771459810509113</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/aboodan_94/status/2053771459810509113</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اريد التقديم على كاشير هل يمكنكم اعطائي ايميل للتقديم ؟</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1778492247000</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'Aboodan', 'screenName': 'aboodan_94', 'followersCount': 1, 'favouritesCount': 4, 'friendsCount': 35, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>46153.56767361111</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://x.com/aboodan_94/status/2053771459810509113</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2053771459810509113</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2053820083604951148</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053820083604951148</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>@aboodan_94 شكراً لتواصلك معنا. إذا كنت مهتم بالانضمام إلى فريق الإمارات الإسلامي، يرجى زيارة: https://t.co/FlooXOG1Yl
+أو يمكنك الإطلاع على الشواغر المتوفرة على صفحتنا في اللينكد إن. سيتم التواصل معك مباشرةً في حال تم اختيارك للوظيفة الشاغرة. شكراً!</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1778503840000</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2053731843292213253</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2053771459810509113</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>46153.70185185185</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053765437930782783</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2053765437930782783</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2053731947965198593</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/foodilty/status/2053731947965198593</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>@emiratesislamic for withdrawal that I did for my credit card by mistake, I am keep receiving more fees, that are not clear anywhere, those fees should appear on the ATM before accepting the withdrawal, I sent email and called and no solution, I can’t trust anymore my own bank.</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1778482827000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2053731947965198593</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'Inés', 'screenName': 'foodilty', 'followersCount': 0, 'favouritesCount': 1, 'friendsCount': 22, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>46153.45864583334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053765437930782783</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2053765437930782783</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2053765437930782783</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053765437930782783</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>@foodilty Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1778490812000</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2053731947965198593</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2053731947965198593</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>46153.55106481481</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053777135513240054</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2053831398839251331</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://x.com/RahulCholakkal3/status/2053831398839251331</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Why am gett two statement? I just paid just few days back and again its come another today why ?</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1778506538000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'Rahul Cholakkal', 'screenName': 'RahulCholakkal3', 'followersCount': 23, 'favouritesCount': 212, 'friendsCount': 43, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2053777135513240054</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>46153.73307870371</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053738917132698102</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2053738917132698102</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2053262874999415084</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://x.com/W42RW/status/2053262874999415084</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم ممكن تردون خاص</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1778370991000</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2053262874999415084</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'Saud Alanazi', 'screenName': 'W42RW', 'followersCount': 2, 'favouritesCount': 2, 'friendsCount': 19, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
+        <v>46152.16424768518</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053738917132698102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2053738917132698102</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2053738917132698102</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053738917132698102</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>@W42RW عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1778484489000</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2053262874999415084</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" s="2" t="n">
-        <v>46152.46875</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://x.com/GulfIndustryOn/status/2053373220359639274</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2053373220359639274</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2053471367086112970</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/GulfIndustryOn/status/2053471367086112970</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>The UAE Ministry of Industry and Advanced Technology, Emirates Development Bank &amp;amp; ADNOC have signed a memorandum of understanding.
-Read more on https://t.co/XL01aIrdJ2
-#GINews #MoU #IndustrialFund #Abudhabi https://t.co/aPwODIhqKU</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1778420700000</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2053471367086112970</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HH8-Fd6a8AEY5E8.jpg', 'type': 'photo', 'id': '2053428218754166785'}]</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 107, 'favouritesCount': 18, 'friendsCount': 187, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2053262874999415084</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>46153.47788194445</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052705068227432806</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1778238000000</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2052643891250188290/pu/img/G6rzIGTvL3xY2TTb.jpg', 'type': 'video', 'id': '2052643891250188290'}]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
         <v>2</v>
       </c>
-      <c r="M37" t="n">
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" s="2" t="n">
+        <v>46150.625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2052705073373839474</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن https://t.co/9VLrqeVE7Q
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1778238001000</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="2" t="n">
-        <v>46152.73958333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2053384545815163241</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2053384545815163241</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Big goals don’t happen all at once.
-They take shape through small, consistent steps.
-When there’s a clear direction, every step starts to feel more meaningful.
-And over time, those steps quietly turn into real progress.
-#Finwell #FinancialWellbeing #EmiratesIslamic https://t.co/F28Rc1z9vt</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1778400000000</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2053384545815163241</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2053176394633338886/pu/img/i7ZqY7HdP86qLlpS.jpg', 'type': 'video', 'id': '2053176394633338886'}]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" s="2" t="n">
-        <v>46152.5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053384545815163241</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2053384545815163241</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2053052358729376236</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2053052358729376236</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ادفع أعمالك إلى مستوى أعلى مع خدمات مصرفية مصممة لك. توفّر لك الباقة المميزة للأعمال من الإمارات الإسلامي مزايا مجمعة للمعاملات، وأسعار ربح تنافسية على حلول التمويل، وقنوات رقمية مريحة لتتفرغ لنمو عملك بدلاً من الأعمال الإدارية.
-https://t.co/r83TOi6WkA https://t.co/tVFefsmql9</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1778320800000</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2053052358729376236</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzI9nSWUAI55Gj.jpg', 'type': 'photo', 'id': '2052736491017621506'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHzI9zAXIAQacLI.jpg', 'type': 'photo', 'id': '2052736494163402756'}]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18502, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" s="2" t="n">
-        <v>46151.58333333334</v>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>46150.62501157408</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2052705076490150108</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052705076490150108</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.
+Apply now
+https://t.co/8qeNDgv9OP</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1778238002000</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2052705073373839474</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>46150.62502314815</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2053194406094946347</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://x.com/aashiash/status/2053194406094946347</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I am unable to login into my EI app. The app demands biometric signin when its not been setup.. and I cant set it up because i CANT login!!!</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1778354667000</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{'name': 'Aashi Ash', 'screenName': 'aashiash', 'followersCount': 177, 'favouritesCount': 43652, 'friendsCount': 665, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2052705076490150108</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>46151.9753125</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2053754654870130716</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2053754654870130716</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>@aashiash Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1778488241000</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18507, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2053194406094946347</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>46153.52130787037</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,47 +517,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
+          <t>https://x.com/ZydIqbal/status/2054302575562793341</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2053946052726936040</t>
+          <t>2054302575562793341</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2053820075002438016</t>
+          <t>2054218815886503947</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053820075002438016</t>
+          <t>https://x.com/ZydIqbal/status/2054218815886503947</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>الحياة مليئة باللحظات. ونحن ندعمها كلّها.
-مع القروض الشخصية من بنك الإمارات دبي الوطني، احصل على الدعم المالي الذي تحتاجه لكل خططك.
-  https://t.co/HiEGCc4hi9 :قدّم الآن https://t.co/NCigHqexuW</t>
+          <t>@EmiratesNBD_KSA
+22749958464
+22753488638
+22754650253
+22754840453
+اربع شكاوي، و لسا ما اتحلت المشكلة ؟! ... من الجمعة تجيني رسايل انه اتحلت المشكلة و ماتحلت و البطاقة لسا مبلكة    و الموضوع كله انه ما تم تجديد الهوية في التطبيق وهي كانت صالحة ... سوء تطبيق و سوء خدمة العملاء https://t.co/xHAN3eIzTd</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1778503838000</v>
+        <v>1778598905000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2053820075002438016</t>
+          <t>2054218815886503947</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HICiePKXoAAhklU.jpg', 'type': 'video', 'id': '2053820035664097280'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIINIINXYAEgjDT.jpg', 'type': 'photo', 'id': '2054218813328023553'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Zaid Iqbal', 'screenName': 'ZydIqbal', 'followersCount': 210, 'favouritesCount': 744, 'friendsCount': 324, 'description': ''}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,60 +577,60 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46153.70182870371</v>
+        <v>46154.80214120371</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
+          <t>https://x.com/ZydIqbal/status/2054302575562793341</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2053946052726936040</t>
+          <t>2054302575562793341</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2053946052726936040</t>
+          <t>2054221342367531256</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2053946052726936040</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2054221342367531256</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE رد فريقكم و ارسلت لهم و ما ردو الاشكال ناوين تحلونه ولا مستمرين بلتجاهل؟؟؟؟ https://t.co/OCh03ntFpy</t>
+          <t>@ZydIqbal مرحبا ,تم إرسال رقمك للفريق المختص و سيتم التواصل معك فى أسرع وقت, شكرا.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1778533874000</v>
+        <v>1778599508000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2053820075002438016</t>
+          <t>2054218815886503947</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIEVCEybQAAk5j6.jpg', 'type': 'photo', 'id': '2053946030446821376'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17486, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -640,51 +643,50 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2053820075002438016</t>
+          <t>2054218815886503947</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46154.04946759259</v>
+        <v>46154.80912037037</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/ZydIqbal/status/2054302575562793341</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054302575562793341</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054302575562793341</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+          <t>https://x.com/ZydIqbal/status/2054302575562793341</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
-I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
+          <t>@EmiratesNBD_KSA احتاج فك البلوك ... اكتفيت بالتواصل ... زودتوها</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777882561000</v>
+        <v>1778618875000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054218815886503947</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -694,11 +696,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'Zaid Iqbal', 'screenName': 'ZydIqbal', 'followersCount': 210, 'favouritesCount': 744, 'friendsCount': 324, 'description': ''}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -711,46 +713,51 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2054221342367531256</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n">
-        <v>46146.51112268519</v>
+        <v>46155.03327546296</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/ATwhh38853/status/2054396400968810680</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054396400968810680</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2051219105496150060</t>
+          <t>2054396400968810680</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051219105496150060</t>
+          <t>https://x.com/ATwhh38853/status/2054396400968810680</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@FF1991Whooo We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007505 in the subject line.</t>
+          <t>حفلة موسيقية مميزة تحييها صوت مصر الفنانة أنغام في الرياض على مسرح محمد عبده أرينا by ENBD 🎶❤️
+30 مايو 🗓️</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777883719000</v>
+        <v>1778641245000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054396400968810680</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -760,152 +767,154 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': '\u200fمنصة قولدن تيكت 🏟️', 'screenName': 'ATwhh38853', 'followersCount': 1818, 'favouritesCount': 1103, 'friendsCount': 304, 'description': 'نوفر لكم| تذاكر الحفلات الموسيقية• مباريات © تذاكر حفلات \n أسعارنا مميزة مناسبه لجميع المنصات 📥\nاستلم تذكرتك بكل أمان وثقة  📩 تواصل دايركت'}</t>
         </is>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2051214248865656992</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46146.52452546296</v>
+        <v>46155.2921875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/ATwhh38853/status/2054396400968810680</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054396400968810680</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2052657495840285062</t>
+          <t>2054410643931885670</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2052657495840285062</t>
+          <t>https://x.com/ATwhh38853/status/2054410643931885670</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE No difference! Had sent an email right after this, usual 'escalated to the team' was the reply.
-Next payment due is 10 May, bcz you'll will drag this &amp;amp; I'll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y'all!!</t>
+          <t>🎶✨ ليلة لا تُنسى 
+📍 أبوظبي — سبيس 42 أرينا
+🗓️ السبت | 16 مايو
+استعدوا لأمسية مليئة بالإحساس والرومانسية مع أجمل أغاني تامر عاشور 🎼💙
+ تنتظركم في أبوظبي 🇦🇪🔥
+ احجزوا مقاعدكم الآن قبل نفاد التذاكر
+https://t.co/DcidivtCqU
+#دوري_أدنوك_للمحترفين https://t.co/IqEKf6Rd21</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1778226658000</v>
+        <v>1778644641000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054410643931885670</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIK7l9xXsAAj9d4.jpg', 'type': 'photo', 'id': '2054410640945557504'}]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': '\u200fمنصة قولدن تيكت 🏟️', 'screenName': 'ATwhh38853', 'followersCount': 1818, 'favouritesCount': 1103, 'friendsCount': 304, 'description': 'نوفر لكم| تذاكر الحفلات الموسيقية• مباريات © تذاكر حفلات \n أسعارنا مميزة مناسبه لجميع المنصات 📥\nاستلم تذكرتك بكل أمان وثقة  📩 تواصل دايركت'}</t>
         </is>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2051219105496150060</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46150.49372685186</v>
+        <v>46155.33149305556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/FintechGate1/status/2054323032286466295</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054323032286466295</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2052659227227754933</t>
+          <t>2054323032286466295</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052659227227754933</t>
+          <t>https://x.com/FintechGate1/status/2054323032286466295</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@FF1991Whooo We are extremely sorry for the delay and our team will review your email and help you out accordingly and update you on urgent basis.</t>
+          <t>Network International and Emirates NBD extend long-standing processing partnership
+https://t.co/rjk5RE2WOF  | التفاصيل
+@EmiratesNBD_AE
+#fintech_gate
+#Network_International #Emirates_NBD https://t.co/4dzxSXlqzI</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1778227070000</v>
+        <v>1778623753000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054323032286466295</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIJr6TTX0AAa6u1.jpg', 'type': 'photo', 'id': '2054323029392478208'}]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 532, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -918,64 +927,63 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2052657495840285062</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46150.49849537037</v>
+        <v>46155.0897337963</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/FintechGate1/status/2054323032286466295</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054323032286466295</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2053439591856889966</t>
+          <t>2054331958864257265</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053439591856889966</t>
+          <t>https://x.com/FintechGate1/status/2054331958864257265</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Today is the due date, I logged in to the app and I cant even find the card instead showing a negative 100 balance! I cant keep running behind this. Please clear them all so I can just get out of this trouble!!</t>
+          <t>إيرادات «فودافون» ترتفع إلى 40.5 مليار يورو خلال العام المالي المنتهي في مارس 2026         
+                                                                                  https://t.co/3v7Q3VRR9g | التفاصيل 
+#fintech_gate
+#فودافون #العام_المالي https://t.co/pwZ9Q7QUlN</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1778413124000</v>
+        <v>1778625881000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054331958864257265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIJ0B7FWwAAH70O.jpg', 'type': 'photo', 'id': '2054331956423213056'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 532, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -988,190 +996,193 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2052659227227754933</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46152.65189814815</v>
+        <v>46155.11436342593</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/o_nagomah/status/2054285776305725588</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054285776305725588</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2053439958275301610</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053439958275301610</t>
+          <t>https://x.com/RotanaLive/status/2054277712093528566</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@FF1991Whooo We have already replied to you email, and also we are following up with our team to resolve your issue and will update you email as soon as possible.</t>
+          <t>ليلة العيد غير .. 
+إذا كانت مع صوت مصر 🫶🏼
+📍 الرياض -  مسرح محمد عبده أرينا by ENBD
+🗓️ 30 مايو
+تُطرح التذاكر يوم الجمعة 15 مايو الساعة 4 مساءً https://t.co/hRru89NmZA ✨
+@Turki_alalshikh 
+@Angham  
+@GEA_SA 
+@Mabdoarena 
+@flowardCo 
+@EmiratesNBD_KSA 
+#روتانا_لايف https://t.co/rahed2HplV</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1778413211000</v>
+        <v>1778612947000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2054277583328436224/img/NXP8iWMmIR3sBzfv.jpg', 'type': 'video', 'id': '2054277583328436224'}]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 194694, 'favouritesCount': 7177, 'friendsCount': 153, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2053439591856889966</t>
-        </is>
-      </c>
+          <t>13088</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>46152.65290509259</v>
+        <v>46154.96466435185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/o_nagomah/status/2054285776305725588</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054285776305725588</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2053744584279416892</t>
+          <t>2054285776305725588</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053744584279416892</t>
+          <t>https://x.com/o_nagomah/status/2054285776305725588</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE NO! they sent email saying all the amount will be reversed and updated which I trusted and waited. And today just a few mins ago I recived this email! For a less than 20AED all this started, and now youre adding overdue again and again. Ive been chasing y'all for the longest! https://t.co/64ln3qwfCh</t>
+          <t>@RotanaLive @Turki_alalshikh @Angham @GEA_SA @Mabdoarena @flowardCo @EmiratesNBD_KSA نبيها بالخبر</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1778485840000</v>
+        <v>1778614870000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIBd0M3a8AAltBX.jpg', 'type': 'photo', 'id': '2053744581469204480'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': '🪷', 'screenName': 'o_nagomah', 'followersCount': 667, 'favouritesCount': 34296, 'friendsCount': 283, 'description': '🤍🇸🇦@angham'}</t>
         </is>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>152</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2053439958275301610</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46153.49351851852</v>
+        <v>46154.98692129629</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/o_nagomah/status/2054285718176854018</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054285718176854018</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2053771047145460107</t>
+          <t>2054285718176854018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053771047145460107</t>
+          <t>https://x.com/o_nagomah/status/2054285718176854018</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@FF1991Whooo Apologies for any inconvenience caused. Please share with us the same via email conversation. We certainly review it and assist you accordingly.</t>
+          <t>@RotanaLive @Turki_alalshikh @Angham @GEA_SA @Mabdoarena @flowardCo @EmiratesNBD_KSA منتظظظرررييين💜💜</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1778492149000</v>
+        <v>1778614856000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1181,11 +1192,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': '🪷', 'screenName': 'o_nagomah', 'followersCount': 667, 'favouritesCount': 34296, 'friendsCount': 283, 'description': '🤍🇸🇦@angham'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1198,51 +1209,50 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2053744584279416892</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46153.56653935185</v>
+        <v>46154.98675925926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/iik_h1/status/2054283494369419586</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054283494369419586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2053786818806734879</t>
+          <t>2054283494369419586</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053786818806734879</t>
+          <t>https://x.com/iik_h1/status/2054283494369419586</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE HAVE ALREADY SENT AN EMAIL the moment I received this, &amp;amp; till now there's no response.  WHY ARE YOU ASKING TO CONTACT IF THERE'S NO ACTION BEEN TAKING RATHER MAKING IT WORSE FOR US?
-You promised about waiving the amount &amp;amp; to check the app later, &amp;amp; the next day I get this email?</t>
+          <t>@RotanaLive @Turki_alalshikh @Angham @GEA_SA @Mabdoarena @flowardCo @EmiratesNBD_KSA اهم شي اللسته يا روتانا نبي خليجي اكثر من حفلة الخبر العام</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1778495909000</v>
+        <v>1778614326000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1252,11 +1262,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'K', 'screenName': 'iik_h1', 'followersCount': 1328, 'favouritesCount': 7469, 'friendsCount': 85, 'description': ''}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1265,54 +1275,54 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>269</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2053771047145460107</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46153.61005787037</v>
+        <v>46154.980625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/Sen8_w/status/2054279882834657422</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054279882834657422</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2053790086836183455</t>
+          <t>2054279882834657422</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053790086836183455</t>
+          <t>https://x.com/Sen8_w/status/2054279882834657422</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@FF1991Whooo Hello, kindly note that our team is working on replying to the email as soon as possible.</t>
+          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @Angham @GEA_SA @Mabdoarena @flowardCo @EmiratesNBD_KSA والخبر ؟</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1778496688000</v>
+        <v>1778613465000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1322,67 +1332,67 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'N', 'screenName': 'Sen8_w', 'followersCount': 1, 'favouritesCount': 100, 'friendsCount': 49, 'description': 'As♥️'}</t>
         </is>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>195</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2053786818806734879</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46153.61907407407</v>
+        <v>46154.97065972222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/33lir_/status/2054278402736095542</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054278402736095542</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2053830887448748503</t>
+          <t>2054278402736095542</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053830887448748503</t>
+          <t>https://x.com/33lir_/status/2054278402736095542</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Ive been trusting this 'as soon as possible' and then you've kept on addinh overdue charges on it. Seriously for a AED20 something, bcz of your team's irresponsible behaviour its gone with AED400+ Why would you want to make customers run behind y'all??</t>
+          <t>@RotanaLive @Turki_alalshikh @Angham @GEA_SA @Mabdoarena @flowardCo @EmiratesNBD_KSA و الخبر متى؟</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1778506416000</v>
+        <v>1778613112000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1392,11 +1402,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'البدر', 'screenName': '33lir_', 'followersCount': 205, 'favouritesCount': 5666, 'friendsCount': 177, 'description': '#Angham'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1405,136 +1415,143 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>210</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2053790086836183455</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46153.73166666667</v>
+        <v>46154.96657407407</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/RotanaLive/status/2054277712093528566</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054277712093528566</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2053842145887260736</t>
+          <t>2054237056772051433</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053842145887260736</t>
+          <t>https://x.com/RotanaLive/status/2054237056772051433</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@FF1991Whooo Apologies for any inconvenience caused. We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
+          <t>ليلة العيد غير .. 
+إذا كانت مع صوت مصر 🫶🏼
+الفنانة #أنغام تلتقي جمهورها 
+في ليلة من أجمل ليالي عيد الأضحى 🤩♥️
+📍 الرياض -  مسرح محمد عبده أرينا by ENBD
+🗓️ 30 مايو
+تُطرح التذاكر يوم الجمعة 15 مايو الساعة 4 مساءً https://t.co/eNS2lG59KG ✨
+@Turki_alalshikh 
+@Angham  
+@GEA_SA 
+@Mabdoarena 
+@flowardCo 
+@EmiratesNBD_KSA 
+#روتانا_لايف</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1778509100000</v>
+        <v>1778603254000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054237056772051433</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIIaj7KWkAAa_Uw.jpg', 'type': 'photo', 'id': '2054233584513224704'}]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 194693, 'favouritesCount': 7177, 'friendsCount': 153, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2053830887448748503</t>
-        </is>
-      </c>
+          <t>22306</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>46153.76273148148</v>
+        <v>46154.85247685185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/naturefairyjm/status/2054272698159616007</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2053881673440428301</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053881673440428301</t>
+          <t>https://x.com/naturefairyjm/status/2054272698159616007</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE And this is what I received now!
-What are you guys upto?
-Delaying the process and increasing the customer's overdue wherein they dont even have an overdue. And then closing the issue by saying its resolved, while I can still see my app showing same negative aswl the overdue! https://t.co/Fhjouj0rk6</t>
+          <t>@EmiratesNBD_AE money was sent to me from the uk using my Iban multiple times before but this time, I didn’t receive it. When I cross checked the Iban used from the payment account I noticed there was an extra zero. I’ve received money from the same account in the past before.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1778518524000</v>
+        <v>1778611752000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDaf0WakAAxOe_.jpg', 'type': 'photo', 'id': '2053881670244405248'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'jimins', 'screenName': 'naturefairyjm', 'followersCount': 1, 'favouritesCount': 1704, 'friendsCount': 8, 'description': '2seok deez nuts'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1551,50 +1568,46 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2053842145887260736</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" s="2" t="n">
-        <v>46153.87180555556</v>
+        <v>46154.95083333334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/naturefairyjm/status/2054272698159616007</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2053890991636062391</t>
+          <t>2054412320084795471</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053890991636062391</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2054412320084795471</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@FF1991Whooo Hello, we will check your request and reply to the email as soon as possible.</t>
+          <t>@naturefairyjm Hi jimins, Thanks for writing to us, we have replied privately please check</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1778520746000</v>
+        <v>1778645040000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1604,11 +1617,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174674, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1619,67 +1632,62 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2053881673440428301</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46153.89752314815</v>
+        <v>46155.33611111111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/naturefairyjm/status/2054272698159616007</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054272698159616007</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2053893546001018992</t>
+          <t>2054282907540127790</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053893546001018992</t>
+          <t>https://x.com/naturefairyjm/status/2054282907540127790</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE What are you trying to do?
-It's as simple as to waive off the amount that occurred bcz of your team's negligence, &amp;amp; also the amount that got addea a day a before bcz you delayed the process &amp;amp; you mentioned that not to worry &amp;amp; it will be waived off. I've email proof of all this! https://t.co/XsVNWNGv1I</t>
+          <t>I never stopped 💃I finish 300 page books in 5-6 hrs</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1778521355000</v>
+        <v>1778614186000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054282907540127790</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDlS4RaAAAxPfu.jpg', 'type': 'photo', 'id': '2053893542586744832'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HIDlS64a8AAvQVF.jpg', 'type': 'photo', 'id': '2053893543287255040'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'jimins', 'screenName': 'naturefairyjm', 'followersCount': 1, 'favouritesCount': 1704, 'friendsCount': 8, 'description': '2seok deez nuts'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1692,123 +1700,115 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2053890991636062391</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>46153.90457175926</v>
+        <v>46154.97900462963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/Turki_alalshikh/status/2054233434487144552</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054233434487144552</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2053895589192950144</t>
+          <t>2054233434487144552</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053895589192950144</t>
+          <t>https://x.com/Turki_alalshikh/status/2054233434487144552</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@FF1991Whooo Hello, kindly note that we can only reply via email as we are not able to disclose any of your financial details through a social media public platform.</t>
+          <t>حفلة موسيقية مميزة تحييها صوت مصر الفنانة أنغام في الرياض على مسرح محمد عبده أرينا by ENBD 🎶❤️
+30 مايو 🗓️
+التذاكر تطرح قريباً 🎟️ https://t.co/Xrez1nKGfz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1778521842000</v>
+        <v>1778602391000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2054233434487144552</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HIIaaylWIAEByhQ.jpg', 'type': 'photo', 'id': '2054233427591700481'}]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'TURKI ALALSHIKH', 'screenName': 'Turki_alalshikh', 'followersCount': 7355345, 'favouritesCount': 25822, 'friendsCount': 393, 'description': 'A personal account that reflects a personal opinion … could be right could be wrong.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>884</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2053893546001018992</t>
-        </is>
-      </c>
+          <t>203088</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>46153.91020833333</v>
+        <v>46154.84248842593</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2053945581698207970</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2053945581698207970</t>
+          <t>https://x.com/khaja_moin/status/2053207767746326594</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exactly!
-The emails you're sending each day is not connected!
-1 day you said you will check, next day you said it'll be waived off, then you send an email saying it's solved, &amp;amp; then again you sent email saying I need to lodge a new compalint! 
-Customers are getting drained out!</t>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1778533761000</v>
+        <v>1778357853000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1818,11 +1818,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Flavours Footprints', 'screenName': 'FF1991Whooo', 'followersCount': 2, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39859, 'friendsCount': 695, 'description': '🤫'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1835,121 +1835,116 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2053895589192950144</t>
-        </is>
-      </c>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46154.04815972222</v>
+        <v>46152.0121875</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2054012648761835613</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2053823138442432845</t>
+          <t>2053208001905860832</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053823138442432845</t>
+          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech-savvy Um Allawi turns dinner talk into a smart sustainability lesson with the ENBD X carbon calculator, because every transaction tells two stories: one about you and one about the planet.
-Track your carbon footprint, make smarter spending choices, and discover how every dirham can support a more sustainable future.
-What is the name of the ENBD X carbon calculator? Comment below for a chance to win AED 500.
-تحوّل أم علاوي المُلِمّة بالتقنيات الحديثة أحاديث المائدة إلى درس ذكي في الاستدامة من خلال حاسبة البصمة الكربونية في ENBD X لأن كل معاملة تروي قصتين: واحدة عنك، وأخرى عن الكوكب.
-تابع بصمتك الكربونية، واتخذ قرارات إنفاق أكثر ذكاءً، واكتشف كيف يمكن لكل درهم أن يدعم مستقبلًا أكثر استدامة.
-ما اسم حاسبة البصمة الكربونية في ENBD X؟ شارك إجابتك في التعليقات لتحصل على فرصة للفوز بـ 500 درهم.</t>
+          <t>@EmiratesNBD_KSA نرجو من Emirates NBD التعامل مع شكاوى العملاء بشكل أفضل وحل المشكلة بأسرع وقت.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1778504569000</v>
+        <v>1778357909000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2053823138442432845</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2053823018510512129/img/s9nsGhTTq-0KywPV.jpg', 'type': 'video', 'id': '2053823018510512129'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39859, 'friendsCount': 695, 'description': '🤫'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2053207767746326594</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="n">
-        <v>46153.71028935185</v>
+        <v>46152.01283564815</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2054012648761835613</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2054012648761835613</t>
+          <t>2053340099002135039</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/mnsadiq84/status/2054012648761835613</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053340099002135039</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Green Pulse</t>
+          <t>@khaja_moin نحن آسفون لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1010667 في موضوع الرسالة.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1778549751000</v>
+        <v>1778389403000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2053823138442432845</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1959,11 +1954,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'naveed sadiq', 'screenName': 'mnsadiq84', 'followersCount': 223, 'favouritesCount': 140333, 'friendsCount': 189, 'description': '😊'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17486, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1974,60 +1969,62 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2053823138442432845</t>
+          <t>2053208001905860832</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46154.23322916667</v>
+        <v>46152.37734953704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053495606555889902</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
+          <t>https://x.com/khaja_moin/status/2053495606555889902</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>@EmiratesNBD_KSA Email sent, kindly resolve the dispute at the earliest.</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777780354000</v>
+        <v>1778426479000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamTYXgAAT-o_.jpg', 'type': 'photo', 'id': '2050785556909490176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamj9XMAAx1Ze.jpg', 'type': 'photo', 'id': '2050785561359626240'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39859, 'friendsCount': 695, 'description': '🤫'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2037,53 +2034,57 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2077</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2053340099002135039</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n">
-        <v>46145.3281712963</v>
+        <v>46152.80646990741</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2051188760185049183</t>
+          <t>2053495978028662970</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2053495978028662970</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+          <t>@khaja_moin Thanks for the confirmation and surely our team will review and reply your email s soon as possible.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777876484000</v>
+        <v>1778426567000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2093,11 +2094,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Mahmoud Moawad', 'screenName': 'mahmoudmoawad00', 'followersCount': 5, 'favouritesCount': 1513, 'friendsCount': 274, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17486, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2110,50 +2111,50 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053495606555889902</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46146.44078703703</v>
+        <v>46152.80748842593</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2051204201930190866</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051204201930190866</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@mahmoudmoawad00 We are sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1007406 in the subject line.</t>
+          <t>@EmiratesNBD_KSA . أشعر بخيبة أمل كبيرة من طريقة تعامل البنك مع هذه المشكلة، وسأقوم بإلغاء جميع بطاقات الائتمان الخاصة بي مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777880165000</v>
+        <v>1778598157000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2163,7 +2164,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'KM', 'screenName': 'khaja_moin', 'followersCount': 359, 'favouritesCount': 39859, 'friendsCount': 695, 'description': '🤫'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2180,50 +2181,50 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>55</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2051188760185049183</t>
+          <t>2053495978028662970</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46146.48339120371</v>
+        <v>46154.7934837963</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/khaja_moin/status/2054215678316392676</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054215963801797045</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2054215963801797045</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE It has been 6 days since I last received an email from your support team, and there is still no update. The problem remains unresolved</t>
+          <t>@khaja_moin مرحباً, تم إرسال متابعة علي طلبك, و سيتم التواصل معك في أقرب وقت ممكن.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1778522330000</v>
+        <v>1778598225000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2233,11 +2234,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Mahmoud Moawad', 'screenName': 'mahmoudmoawad00', 'followersCount': 5, 'favouritesCount': 1513, 'friendsCount': 274, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17486, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2250,110 +2251,40 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2051204201930190866</t>
+          <t>2054215678316392676</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46153.91585648148</v>
+        <v>46154.79427083334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/mahmoudmoawad00/status/2053897635736731778</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2053897635736731778</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2053898727593476195</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2053898727593476195</t>
+          <t>https://x.com/naser8581/status/2053051787704164789</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>@mahmoudmoawad00 Hello, we will check and update you via email as soon as possible.</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1778522590000</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2050785564182392905</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174668, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2053897635736731778</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>46153.91886574074</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2053921015097696546</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2053051787704164789</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/naser8581/status/2053051787704164789</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
 أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
@@ -2361,8 +2292,74 @@
 لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>1778320664000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 1, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>46151.58175925926</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2054202513771942061</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2053060206704177587</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053060206704177587</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@naser8581 نحن آسفون جدًا لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1010403 في موضوع الرسالة.</t>
+        </is>
+      </c>
       <c r="F28" t="n">
-        <v>1778320664000</v>
+        <v>1778322671000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2376,7 +2373,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2974, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2393,42 +2390,47 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2053051787704164789</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="n">
-        <v>46151.58175925926</v>
+        <v>46151.60498842593</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2053060206704177587</t>
+          <t>2053161447048249627</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2053060206704177587</t>
+          <t>https://x.com/naser8581/status/2053161447048249627</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@naser8581 نحن آسفون جدًا لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1010403 في موضوع الرسالة.</t>
+          <t>@EmiratesNBD_EGY تم ارسال ايميل بذلك 
+نامل المعالجة وافادتي برقم ايصال سداد المديونية</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1778322671000</v>
+        <v>1778346809000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2442,7 +2444,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 1, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2459,47 +2461,46 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>53</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2053051787704164789</t>
+          <t>2053060206704177587</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46151.60498842593</v>
+        <v>46151.88436342592</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2053161447048249627</t>
+          <t>2053162375499403688</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053161447048249627</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053162375499403688</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_EGY تم ارسال ايميل بذلك 
-نامل المعالجة وافادتي برقم ايصال سداد المديونية</t>
+          <t>@naser8581 سيقوم فريقنا بمراجعة بريدك الإلكتروني والرد عليك في أقرب وقت ممكن. شكرًا لك.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1778346809000</v>
+        <v>1778347030000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2513,7 +2514,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2974, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2530,46 +2531,47 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>46</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2053060206704177587</t>
+          <t>2053161447048249627</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46151.88436342592</v>
+        <v>46151.8869212963</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2053162375499403688</t>
+          <t>2053341306580066658</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2053162375499403688</t>
+          <t>https://x.com/naser8581/status/2053341306580066658</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@naser8581 سيقوم فريقنا بمراجعة بريدك الإلكتروني والرد عليك في أقرب وقت ممكن. شكرًا لك.</t>
+          <t>@EmiratesNBD_EGY تم الرد على الايميل 
+كرماً الاطلاع بشكل عاجل</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1778347030000</v>
+        <v>1778389691000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2583,7 +2585,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 1, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2600,47 +2602,46 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2053161447048249627</t>
+          <t>2053162375499403688</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46151.8869212963</v>
+        <v>46152.38068287037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2053341306580066658</t>
+          <t>2053348429305184435</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053341306580066658</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053348429305184435</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_EGY تم الرد على الايميل 
-كرماً الاطلاع بشكل عاجل</t>
+          <t>@naser8581 يرجى التحقق من بريدك الالكتروني حيث قام فريقنا بمراسلتك.</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1778389691000</v>
+        <v>1778391389000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2654,7 +2655,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2974, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2671,46 +2672,47 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2053162375499403688</t>
+          <t>2053341306580066658</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46152.38068287037</v>
+        <v>46152.40033564815</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2053348429305184435</t>
+          <t>2053368822678122695</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2053348429305184435</t>
+          <t>https://x.com/naser8581/status/2053368822678122695</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@naser8581 يرجى التحقق من بريدك الالكتروني حيث قام فريقنا بمراسلتك.</t>
+          <t>@EmiratesNBD_EGY تم الرد على طلب المعلومات وتم تزويدهم بها سابقاً
+نامل معالجة الاشكالية</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1778391389000</v>
+        <v>1778396251000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2724,7 +2726,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2973, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
+          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 1, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2741,47 +2743,46 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2053341306580066658</t>
+          <t>2053348429305184435</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46152.40033564815</v>
+        <v>46152.4566087963</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053921015097696546</t>
+          <t>https://x.com/naser8581/status/2054202513771942061</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2053921015097696546</t>
+          <t>2054202513771942061</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2053368822678122695</t>
+          <t>2053374720087646697</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/naser8581/status/2053368822678122695</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2053374720087646697</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_EGY تم الرد على طلب المعلومات وتم تزويدهم بها سابقاً
-نامل معالجة الاشكالية</t>
+          <t>@naser8581 شكراً لتأكيدك, سيتم التحقق والرد عليك في أقرب وقت ممكن.</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1778396251000</v>
+        <v>1778397657000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'NASSER', 'screenName': 'naser8581', 'followersCount': 134, 'favouritesCount': 5, 'friendsCount': 0, 'description': 'الحمدلله دائماً وابداً ،،،'}</t>